--- a/multiset_202604/fmo_300k/plot/singleset_64bd.xlsx
+++ b/multiset_202604/fmo_300k/plot/singleset_64bd.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9001FEA7-8890-4738-A0CD-7014D1AC6139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E74CC9C4-AEE8-49A9-825E-8A3E489222D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2040" yWindow="3440" windowWidth="19200" windowHeight="10140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3310" yWindow="2200" windowWidth="19200" windowHeight="10140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -366,5798 +366,5798 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1">
-        <v>5.063243368044572E-20</v>
+        <v>6.855446027944998E-20</v>
       </c>
       <c r="B1">
-        <v>5.191481829283761E-20</v>
+        <v>7.0501778627414927E-20</v>
       </c>
       <c r="C1">
-        <v>4.8153756940020843E-20</v>
+        <v>6.4819258377021371E-20</v>
       </c>
       <c r="D1">
-        <v>1.0000000000000031</v>
+        <v>1.000000000000002</v>
       </c>
       <c r="E1">
-        <v>5.0261695726875242E-20</v>
+        <v>6.798174506287472E-20</v>
       </c>
       <c r="F1">
-        <v>4.9797466665748323E-20</v>
+        <v>6.7288240166329034E-20</v>
       </c>
       <c r="G1">
-        <v>5.1114938139917309E-20</v>
+        <v>6.9283152038722165E-20</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>5.0468949206691849E-5</v>
+        <v>4.8550396395742783E-5</v>
       </c>
       <c r="B2">
-        <v>2.4931787599058009E-5</v>
+        <v>3.1018677231246017E-5</v>
       </c>
       <c r="C2">
-        <v>1.9261213099147399E-5</v>
+        <v>1.9297824830509089E-5</v>
       </c>
       <c r="D2">
-        <v>0.99478065773311453</v>
+        <v>0.99472547000261957</v>
       </c>
       <c r="E2">
-        <v>5.0303103737283734E-3</v>
+        <v>5.0832473484112616E-3</v>
       </c>
       <c r="F2">
-        <v>1.9073564211999399E-5</v>
+        <v>1.8552946040592979E-5</v>
       </c>
       <c r="G2">
-        <v>7.5296379076428063E-5</v>
+        <v>7.3862804490519129E-5</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>2.0878602046954241E-4</v>
+        <v>2.010875345957701E-4</v>
       </c>
       <c r="B3">
-        <v>9.6593705868412428E-5</v>
+        <v>1.1366444671900931E-4</v>
       </c>
       <c r="C3">
-        <v>8.4142807017997074E-5</v>
+        <v>8.224357984314208E-5</v>
       </c>
       <c r="D3">
-        <v>0.9791796509909253</v>
+        <v>0.97908562709270042</v>
       </c>
       <c r="E3">
-        <v>2.006737456639629E-2</v>
+        <v>2.0139197066302409E-2</v>
       </c>
       <c r="F3">
-        <v>7.3980668491299323E-5</v>
+        <v>7.7188374675834907E-5</v>
       </c>
       <c r="G3">
-        <v>2.8947124087970959E-4</v>
+        <v>3.0099190518027478E-4</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>4.6240174588921132E-4</v>
+        <v>4.5283393590846361E-4</v>
       </c>
       <c r="B4">
-        <v>2.2367420246396019E-4</v>
+        <v>2.4699550740114802E-4</v>
       </c>
       <c r="C4">
-        <v>2.060900449777904E-4</v>
+        <v>2.0280639706995269E-4</v>
       </c>
       <c r="D4">
-        <v>0.95375784920928919</v>
+        <v>0.95363783275050062</v>
       </c>
       <c r="E4">
-        <v>4.4505361296000433E-2</v>
+        <v>4.4600341405095487E-2</v>
       </c>
       <c r="F4">
-        <v>1.7666013470439809E-4</v>
+        <v>1.8077410963140679E-4</v>
       </c>
       <c r="G4">
-        <v>6.6796336671532688E-4</v>
+        <v>6.7841589441005646E-4</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>8.0611237127100894E-4</v>
+        <v>7.9496983872847943E-4</v>
       </c>
       <c r="B5">
-        <v>4.0145194443630492E-4</v>
+        <v>4.3005753025435889E-4</v>
       </c>
       <c r="C5">
-        <v>4.0625086305894271E-4</v>
+        <v>4.016095432792543E-4</v>
       </c>
       <c r="D5">
-        <v>0.91941098918629982</v>
+        <v>0.91928078836087979</v>
       </c>
       <c r="E5">
-        <v>7.7450751997109768E-2</v>
+        <v>7.7553213313416497E-2</v>
       </c>
       <c r="F5">
-        <v>3.3221657969119363E-4</v>
+        <v>3.3599186727603468E-4</v>
       </c>
       <c r="G5">
-        <v>1.192227058174159E-3</v>
+        <v>1.2033695461689811E-3</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>1.228583625149948E-3</v>
+        <v>1.215493932488312E-3</v>
       </c>
       <c r="B6">
-        <v>6.2709136292170872E-4</v>
+        <v>6.61815600315762E-4</v>
       </c>
       <c r="C6">
-        <v>7.1020686755845987E-4</v>
+        <v>7.0386195475235407E-4</v>
       </c>
       <c r="D6">
-        <v>0.87732491212755848</v>
+        <v>0.87719723840099861</v>
       </c>
       <c r="E6">
-        <v>0.1176996760443416</v>
+        <v>0.1177994810997377</v>
       </c>
       <c r="F6">
-        <v>5.4915449443682443E-4</v>
+        <v>5.5094853085241769E-4</v>
       </c>
       <c r="G6">
-        <v>1.8603754780822631E-3</v>
+        <v>1.871160480867728E-3</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>1.7142562585085661E-3</v>
+        <v>1.6998192180619561E-3</v>
       </c>
       <c r="B7">
-        <v>9.0028528881401059E-4</v>
+        <v>9.4129120761159873E-4</v>
       </c>
       <c r="C7">
-        <v>1.143710878525891E-3</v>
+        <v>1.1362506293255961E-3</v>
       </c>
       <c r="D7">
-        <v>0.82890738181896417</v>
+        <v>0.82878773622897794</v>
       </c>
       <c r="E7">
-        <v>0.16383934940088299</v>
+        <v>0.16392634362352421</v>
       </c>
       <c r="F7">
-        <v>8.3476238974519647E-4</v>
+        <v>8.3439055814262778E-4</v>
       </c>
       <c r="G7">
-        <v>2.6602539645815769E-3</v>
+        <v>2.674168534366886E-3</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>2.2455107633530869E-3</v>
+        <v>2.2311824225756159E-3</v>
       </c>
       <c r="B8">
-        <v>1.2215187805341421E-3</v>
+        <v>1.2679198263745529E-3</v>
       </c>
       <c r="C8">
-        <v>1.7306462895374649E-3</v>
+        <v>1.7228678092450281E-3</v>
       </c>
       <c r="D8">
-        <v>0.77571536669879859</v>
+        <v>0.77560674944486308</v>
       </c>
       <c r="E8">
-        <v>0.21430641915175361</v>
+        <v>0.21437591562534261</v>
       </c>
       <c r="F8">
-        <v>1.1966476150545059E-3</v>
+        <v>1.1938744795199261E-3</v>
       </c>
       <c r="G8">
-        <v>3.5838907009979369E-3</v>
+        <v>3.6014903920891859E-3</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>2.8043709349933679E-3</v>
+        <v>2.791478886037378E-3</v>
       </c>
       <c r="B9">
-        <v>1.59040024776455E-3</v>
+        <v>1.641673519474324E-3</v>
       </c>
       <c r="C9">
-        <v>2.490032708741451E-3</v>
+        <v>2.4826389960516219E-3</v>
       </c>
       <c r="D9">
-        <v>0.71938187637746265</v>
+        <v>0.71928177550431294</v>
       </c>
       <c r="E9">
-        <v>0.26747603834596739</v>
+        <v>0.2675284437354396</v>
       </c>
       <c r="F9">
-        <v>1.6409615518935829E-3</v>
+        <v>1.635044229771523E-3</v>
       </c>
       <c r="G9">
-        <v>4.6163198331808453E-3</v>
+        <v>4.6389451289282017E-3</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>3.3720679535747021E-3</v>
+        <v>3.3619779274695841E-3</v>
       </c>
       <c r="B10">
-        <v>2.0078112215554189E-3</v>
+        <v>2.0630940479150648E-3</v>
       </c>
       <c r="C10">
-        <v>3.4334423894102611E-3</v>
+        <v>3.427154073047146E-3</v>
       </c>
       <c r="D10">
-        <v>0.66154695793561691</v>
+        <v>0.66145362584112333</v>
       </c>
       <c r="E10">
-        <v>0.32172986532721121</v>
+        <v>0.32176466612376498</v>
       </c>
       <c r="F10">
-        <v>2.169785866634571E-3</v>
+        <v>2.160404051675648E-3</v>
       </c>
       <c r="G10">
-        <v>5.7400693060209044E-3</v>
+        <v>5.7690779350227147E-3</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>3.9303803351077764E-3</v>
+        <v>3.9243134562368049E-3</v>
       </c>
       <c r="B11">
-        <v>2.4750233257261911E-3</v>
+        <v>2.5332012673820749E-3</v>
       </c>
       <c r="C11">
-        <v>4.5638444535170356E-3</v>
+        <v>4.5594410415933477E-3</v>
       </c>
       <c r="D11">
-        <v>0.60379539876200239</v>
+        <v>0.60370855097512544</v>
       </c>
       <c r="E11">
-        <v>0.3755194683892894</v>
+        <v>0.37553434983769418</v>
       </c>
       <c r="F11">
-        <v>2.7812664368337021E-3</v>
+        <v>2.7685068894476739E-3</v>
       </c>
       <c r="G11">
-        <v>6.9346182975378017E-3</v>
+        <v>6.9716365325352206E-3</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>4.4624865540748926E-3</v>
+        <v>4.4613377427138211E-3</v>
       </c>
       <c r="B12">
-        <v>2.9936189726431951E-3</v>
+        <v>3.0532920026872488E-3</v>
       </c>
       <c r="C12">
-        <v>5.8754351902676732E-3</v>
+        <v>5.8740079910638782E-3</v>
       </c>
       <c r="D12">
-        <v>0.54760417108974047</v>
+        <v>0.54752257561878792</v>
       </c>
       <c r="E12">
-        <v>0.42741719384396187</v>
+        <v>0.42741087727467197</v>
       </c>
       <c r="F12">
-        <v>3.4695029183637359E-3</v>
+        <v>3.453598388830382E-3</v>
       </c>
       <c r="G12">
-        <v>8.1775914309527315E-3</v>
+        <v>8.2243109812612861E-3</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>4.953936726726396E-3</v>
+        <v>4.9582094401018949E-3</v>
       </c>
       <c r="B13">
-        <v>3.5652912053667041E-3</v>
+        <v>3.624718094050646E-3</v>
       </c>
       <c r="C13">
-        <v>7.3544214830499203E-3</v>
+        <v>7.3572905880745811E-3</v>
       </c>
       <c r="D13">
-        <v>0.49430020139847741</v>
+        <v>0.49422173157845362</v>
       </c>
       <c r="E13">
-        <v>0.4761565951285871</v>
+        <v>0.47612911653901568</v>
       </c>
       <c r="F13">
-        <v>4.2241819962205223E-3</v>
+        <v>4.2055472328777436E-3</v>
       </c>
       <c r="G13">
-        <v>9.4453720615896592E-3</v>
+        <v>9.5033865274341996E-3</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>5.3934725499967719E-3</v>
+        <v>5.4030460814500341E-3</v>
       </c>
       <c r="B14">
-        <v>4.1914894670863822E-3</v>
+        <v>4.2487149087693816E-3</v>
       </c>
       <c r="C14">
-        <v>8.980598502719591E-3</v>
+        <v>8.9893060101940876E-3</v>
       </c>
       <c r="D14">
-        <v>0.44502910381014688</v>
+        <v>0.44495242405878138</v>
       </c>
       <c r="E14">
-        <v>0.52066029418773541</v>
+        <v>0.52061140808359829</v>
       </c>
       <c r="F14">
-        <v>5.0308901002869087E-3</v>
+        <v>5.0101062330950739E-3</v>
       </c>
       <c r="G14">
-        <v>1.071415138203104E-2</v>
+        <v>1.078499462412421E-2</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>5.7735152109378313E-3</v>
+        <v>5.7874616780855849E-3</v>
       </c>
       <c r="B15">
-        <v>4.8729547298065603E-3</v>
+        <v>4.9260579436613671E-3</v>
       </c>
       <c r="C15">
-        <v>1.072968698097896E-2</v>
+        <v>1.074580254415718E-2</v>
       </c>
       <c r="D15">
-        <v>0.40073322087012681</v>
+        <v>0.40065714191247143</v>
       </c>
       <c r="E15">
-        <v>0.56005740445997443</v>
+        <v>0.55998777952658452</v>
       </c>
       <c r="F15">
-        <v>5.8720400981672402E-3</v>
+        <v>5.8496462107065546E-3</v>
       </c>
       <c r="G15">
-        <v>1.196117765001393E-2</v>
+        <v>1.2046110184338359E-2</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>6.0906117958215841E-3</v>
+        <v>6.1081794795828691E-3</v>
       </c>
       <c r="B16">
-        <v>5.6092780051503876E-3</v>
+        <v>5.656737571000256E-3</v>
       </c>
       <c r="C16">
-        <v>1.257560920994477E-2</v>
+        <v>1.2600251619382691E-2</v>
       </c>
       <c r="D16">
-        <v>0.36213906801089302</v>
+        <v>0.36206200381474801</v>
       </c>
       <c r="E16">
-        <v>0.59369301631126559</v>
+        <v>0.59360327742190167</v>
       </c>
       <c r="F16">
-        <v>6.7271136039897461E-3</v>
+        <v>6.7041001776973214E-3</v>
       </c>
       <c r="G16">
-        <v>1.316530306294556E-2</v>
+        <v>1.326544991569876E-2</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>6.3456357783590487E-3</v>
+        <v>6.3664194481831337E-3</v>
       </c>
       <c r="B17">
-        <v>6.398456645114038E-3</v>
+        <v>6.4393335169329654E-3</v>
       </c>
       <c r="C17">
-        <v>1.4492880660085699E-2</v>
+        <v>1.4526700175113811E-2</v>
       </c>
       <c r="D17">
-        <v>0.32975248259294682</v>
+        <v>0.32967059968021079</v>
       </c>
       <c r="E17">
-        <v>0.62112728420010455</v>
+        <v>0.6210200928716475</v>
       </c>
       <c r="F17">
-        <v>7.5746152681087546E-3</v>
+        <v>7.5519311891365142E-3</v>
       </c>
       <c r="G17">
-        <v>1.430864485528623E-2</v>
+        <v>1.4424923118788589E-2</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>6.5436355100437294E-3</v>
+        <v>6.5674499456621193E-3</v>
       </c>
       <c r="B18">
-        <v>7.2364469987765724E-3</v>
+        <v>7.2705058656668837E-3</v>
       </c>
       <c r="C18">
-        <v>1.6458718721273888E-2</v>
+        <v>1.6501818816111541E-2</v>
       </c>
       <c r="D18">
-        <v>0.30386154660249881</v>
+        <v>0.30377017338249412</v>
       </c>
       <c r="E18">
-        <v>0.64212920079351599</v>
+        <v>0.64200873972734274</v>
       </c>
       <c r="F18">
-        <v>8.393412382092777E-3</v>
+        <v>8.3718044764183857E-3</v>
       </c>
       <c r="G18">
-        <v>1.537703899180551E-2</v>
+        <v>1.550950778633221E-2</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>6.6931671513542432E-3</v>
+        <v>6.7201262715005016E-3</v>
       </c>
       <c r="B19">
-        <v>8.1168880761459776E-3</v>
+        <v>8.1449205333450451E-3</v>
       </c>
       <c r="C19">
-        <v>1.845432675373871E-2</v>
+        <v>1.8506226852965369E-2</v>
       </c>
       <c r="D19">
-        <v>0.28454268209924599</v>
+        <v>0.28443366896519662</v>
       </c>
       <c r="E19">
-        <v>0.65666866807796354</v>
+        <v>0.6565430712563961</v>
       </c>
       <c r="F19">
-        <v>9.1637943028066281E-3</v>
+        <v>9.1439227640357432E-3</v>
       </c>
       <c r="G19">
-        <v>1.63604735387574E-2</v>
+        <v>1.6508063356573351E-2</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>6.8057051866053262E-3</v>
+        <v>6.8364361290835897E-3</v>
       </c>
       <c r="B20">
-        <v>9.0308877333959287E-3</v>
+        <v>9.0548156154440923E-3</v>
       </c>
       <c r="C20">
-        <v>2.0465551423339251E-2</v>
+        <v>2.0525506175385431E-2</v>
       </c>
       <c r="D20">
-        <v>0.27167394666644751</v>
+        <v>0.27153531401100278</v>
       </c>
       <c r="E20">
-        <v>0.66490191396127152</v>
+        <v>0.66478310901304172</v>
       </c>
       <c r="F20">
-        <v>9.8689791919237737E-3</v>
+        <v>9.8513996215618439E-3</v>
       </c>
       <c r="G20">
-        <v>1.7253015837025699E-2</v>
+        <v>1.741341943449308E-2</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>6.8949907728437301E-3</v>
+        <v>6.9307375712064339E-3</v>
       </c>
       <c r="B21">
-        <v>9.9671422586558641E-3</v>
+        <v>9.9898986750066397E-3</v>
       </c>
       <c r="C21">
-        <v>2.248311915229121E-2</v>
+        <v>2.2550379912606489E-2</v>
       </c>
       <c r="D21">
-        <v>0.2649516271923415</v>
+        <v>0.26477003800141369</v>
       </c>
       <c r="E21">
-        <v>0.66715425178601151</v>
+        <v>0.66705495554414362</v>
       </c>
       <c r="F21">
-        <v>1.0496489466776679E-2</v>
+        <v>1.0481488777150119E-2</v>
       </c>
       <c r="G21">
-        <v>1.8052379371086461E-2</v>
+        <v>1.822250151850344E-2</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>6.9763621621380138E-3</v>
+        <v>7.0189274300747244E-3</v>
       </c>
       <c r="B22">
-        <v>1.091204316327187E-2</v>
+        <v>1.09375781316179E-2</v>
       </c>
       <c r="C22">
-        <v>2.45024102539089E-2</v>
+        <v>2.45766218858668E-2</v>
       </c>
       <c r="D22">
-        <v>0.26390991651803031</v>
+        <v>0.26367477167107478</v>
       </c>
       <c r="E22">
-        <v>0.66389999197148974</v>
+        <v>0.66382963125164163</v>
       </c>
       <c r="F22">
-        <v>1.1038862129698859E-2</v>
+        <v>1.1026657317364481E-2</v>
       </c>
       <c r="G22">
-        <v>1.8760413801469079E-2</v>
+        <v>1.8935812312358479E-2</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>7.0658715222335321E-3</v>
+        <v>7.1173686745264839E-3</v>
       </c>
       <c r="B23">
-        <v>1.184989230491211E-2</v>
+        <v>1.1883359462146749E-2</v>
       </c>
       <c r="C23">
-        <v>2.65232323543662E-2</v>
+        <v>2.6604530003913791E-2</v>
       </c>
       <c r="D23">
-        <v>0.26794698319739801</v>
+        <v>0.26765321539799158</v>
       </c>
       <c r="E23">
-        <v>0.65573731667768442</v>
+        <v>0.65569928858428728</v>
       </c>
       <c r="F23">
-        <v>1.1494540812804399E-2</v>
+        <v>1.148510763816175E-2</v>
       </c>
       <c r="G23">
-        <v>1.9382163130609361E-2</v>
+        <v>1.955713023897241E-2</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>7.1786346930521657E-3</v>
+        <v>7.241971234288506E-3</v>
       </c>
       <c r="B24">
-        <v>1.276386501106011E-2</v>
+        <v>1.281120073276093E-2</v>
       </c>
       <c r="C24">
-        <v>2.854875102599036E-2</v>
+        <v>2.8637841280540768E-2</v>
       </c>
       <c r="D24">
-        <v>0.27635638807097562</v>
+        <v>0.2760027623421234</v>
       </c>
       <c r="E24">
-        <v>0.64335955642450626</v>
+        <v>0.64335228709642822</v>
       </c>
       <c r="F24">
-        <v>1.186814028371537E-2</v>
+        <v>1.1861240625384441E-2</v>
       </c>
       <c r="G24">
-        <v>1.9924664490687301E-2</v>
+        <v>2.0092696688493929E-2</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>7.3286194811012272E-3</v>
+        <v>7.4074317068413952E-3</v>
       </c>
       <c r="B25">
-        <v>1.363639349097154E-2</v>
+        <v>1.3704162401557959E-2</v>
       </c>
       <c r="C25">
-        <v>3.0584303273371E-2</v>
+        <v>3.0682425323960639E-2</v>
       </c>
       <c r="D25">
-        <v>0.28835423376772862</v>
+        <v>0.28794309368112708</v>
       </c>
       <c r="E25">
-        <v>0.62752943376261716</v>
+        <v>0.62754694687213142</v>
       </c>
       <c r="F25">
-        <v>1.2170012178698141E-2</v>
+        <v>1.2165137342274609E-2</v>
       </c>
       <c r="G25">
-        <v>2.0397004045514019E-2</v>
+        <v>2.0550802672123319E-2</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>7.5280800753676899E-3</v>
+        <v>7.6264393735443704E-3</v>
       </c>
       <c r="B26">
-        <v>1.445010644855849E-2</v>
+        <v>1.454531456944751E-2</v>
       </c>
       <c r="C26">
-        <v>3.2636132304821278E-2</v>
+        <v>3.2744950985856877E-2</v>
       </c>
       <c r="D26">
-        <v>0.30311029063249351</v>
+        <v>0.30264552062793543</v>
       </c>
       <c r="E26">
-        <v>0.60905057767884074</v>
+        <v>0.60908497937000627</v>
       </c>
       <c r="F26">
-        <v>1.241533127437768E-2</v>
+        <v>1.241173169796253E-2</v>
       </c>
       <c r="G26">
-        <v>2.080948158552574E-2</v>
+        <v>2.0941063375243499E-2</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>7.7871932357877318E-3</v>
+        <v>7.9090885776518741E-3</v>
       </c>
       <c r="B27">
-        <v>1.5188915644414699E-2</v>
+        <v>1.531862835127804E-2</v>
       </c>
       <c r="C27">
-        <v>3.4710395092663202E-2</v>
+        <v>3.483174299882439E-2</v>
       </c>
       <c r="D27">
-        <v>0.31977683152999381</v>
+        <v>0.31926217154511788</v>
       </c>
       <c r="E27">
-        <v>0.5887412878442948</v>
+        <v>0.58878512583536868</v>
       </c>
       <c r="F27">
-        <v>1.262266444091798E-2</v>
+        <v>1.2619651894745841E-2</v>
       </c>
       <c r="G27">
-        <v>2.1172712211938411E-2</v>
+        <v>2.1273590797023841E-2</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>8.1135298474313989E-3</v>
+        <v>8.2624942271140728E-3</v>
       </c>
       <c r="B28">
-        <v>1.583906282056553E-2</v>
+        <v>1.6009884914818369E-2</v>
       </c>
       <c r="C28">
-        <v>3.6812172607156149E-2</v>
+        <v>3.6947767654511743E-2</v>
       </c>
       <c r="D28">
-        <v>0.33751645188197382</v>
+        <v>0.33695351783060762</v>
       </c>
       <c r="E28">
-        <v>0.5674093265064365</v>
+        <v>0.56745763665467708</v>
       </c>
       <c r="F28">
-        <v>1.281295580922286E-2</v>
+        <v>1.280991455669213E-2</v>
       </c>
       <c r="G28">
-        <v>2.149650052721688E-2</v>
+        <v>2.155878416158119E-2</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>8.5112677229615893E-3</v>
+        <v>8.6905321759483227E-3</v>
       </c>
       <c r="B29">
-        <v>1.6390256267930819E-2</v>
+        <v>1.6607480550330161E-2</v>
       </c>
       <c r="C29">
-        <v>3.8944365650288033E-2</v>
+        <v>3.9095795625075973E-2</v>
       </c>
       <c r="D29">
-        <v>0.35552810577381622</v>
+        <v>0.35491492450893142</v>
       </c>
       <c r="E29">
-        <v>0.5458292136499785</v>
+        <v>0.54588003067512481</v>
       </c>
       <c r="F29">
-        <v>1.3007893089191159E-2</v>
+        <v>1.300428816906227E-2</v>
       </c>
       <c r="G29">
-        <v>2.1788897845833301E-2</v>
+        <v>2.1806948295538711E-2</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>8.9813626888808618E-3</v>
+        <v>9.1938426165211994E-3</v>
       </c>
       <c r="B30">
-        <v>1.6836708632855201E-2</v>
+        <v>1.710318000199422E-2</v>
       </c>
       <c r="C30">
-        <v>4.1107027810193472E-2</v>
+        <v>4.1275776958066467E-2</v>
       </c>
       <c r="D30">
-        <v>0.37306972914903191</v>
+        <v>0.37240113034826761</v>
       </c>
       <c r="E30">
-        <v>0.52472106518567052</v>
+        <v>0.52477458888839879</v>
       </c>
       <c r="F30">
-        <v>1.3227604918072179E-2</v>
+        <v>1.322379783012847E-2</v>
       </c>
       <c r="G30">
-        <v>2.2056501615286779E-2</v>
+        <v>2.2027683356631859E-2</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>9.5217816289111627E-3</v>
+        <v>9.7698452871137348E-3</v>
       </c>
       <c r="B31">
-        <v>1.7177316460470899E-2</v>
+        <v>1.749268796083913E-2</v>
       </c>
       <c r="C31">
-        <v>4.3297304441925408E-2</v>
+        <v>4.3484550521582087E-2</v>
       </c>
       <c r="D31">
-        <v>0.38947892316010108</v>
+        <v>0.38874635615094022</v>
       </c>
       <c r="E31">
-        <v>0.50473027264158921</v>
+        <v>0.50478990651858791</v>
       </c>
       <c r="F31">
-        <v>1.348983806490903E-2</v>
+        <v>1.348766699974314E-2</v>
       </c>
       <c r="G31">
-        <v>2.2304563602097059E-2</v>
+        <v>2.2228986561204801E-2</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>1.012775911011332E-2</v>
+        <v>1.0413028284535679E-2</v>
       </c>
       <c r="B32">
-        <v>1.7415144889125309E-2</v>
+        <v>1.7775780330314871E-2</v>
       </c>
       <c r="C32">
-        <v>4.5509465312372648E-2</v>
+        <v>4.5715725350000791E-2</v>
       </c>
       <c r="D32">
-        <v>0.4041897062499703</v>
+        <v>0.40338187666166958</v>
       </c>
       <c r="E32">
-        <v>0.48641220342096908</v>
+        <v>0.48648319548129793</v>
       </c>
       <c r="F32">
-        <v>1.380922680960647E-2</v>
+        <v>1.381221883551407E-2</v>
       </c>
       <c r="G32">
-        <v>2.2536494207826548E-2</v>
+        <v>2.2418175056665539E-2</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>1.079197465715705E-2</v>
+        <v>1.1115284729182891E-2</v>
       </c>
       <c r="B33">
-        <v>1.7557077113109401E-2</v>
+        <v>1.795636917553315E-2</v>
       </c>
       <c r="C33">
-        <v>4.7735207946479737E-2</v>
+        <v>4.7960149694283097E-2</v>
       </c>
       <c r="D33">
-        <v>0.41674484277866891</v>
+        <v>0.41584830839231718</v>
       </c>
       <c r="E33">
-        <v>0.47021929085769598</v>
+        <v>0.4703087446271601</v>
       </c>
       <c r="F33">
-        <v>1.4196829222064991E-2</v>
+        <v>1.420981601503051E-2</v>
       </c>
       <c r="G33">
-        <v>2.2754777424826789E-2</v>
+        <v>2.260132736651593E-2</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>1.150491183129224E-2</v>
+        <v>1.186637734125311E-2</v>
       </c>
       <c r="B34">
-        <v>1.7613390897325429E-2</v>
+        <v>1.8042330262304781E-2</v>
       </c>
       <c r="C34">
-        <v>4.9964220061586233E-2</v>
+        <v>5.0206664249078652E-2</v>
       </c>
       <c r="D34">
-        <v>0.42680299834638452</v>
+        <v>0.42580422763103021</v>
       </c>
       <c r="E34">
-        <v>0.45649354182409307</v>
+        <v>0.4566088445630837</v>
       </c>
       <c r="F34">
-        <v>1.4659371848387691E-2</v>
+        <v>1.4688487917730661E-2</v>
       </c>
       <c r="G34">
-        <v>2.2961565190939021E-2</v>
+        <v>2.2783068035533881E-2</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>1.2255508294532111E-2</v>
+        <v>1.26545653197842E-2</v>
       </c>
       <c r="B35">
-        <v>1.7597034983488909E-2</v>
+        <v>1.804501248124955E-2</v>
       </c>
       <c r="C35">
-        <v>5.2184557542275641E-2</v>
+        <v>5.244288716094634E-2</v>
       </c>
       <c r="D35">
-        <v>0.43414172553107072</v>
+        <v>0.43303018239813568</v>
       </c>
       <c r="E35">
-        <v>0.44546353362074709</v>
+        <v>0.44560831813940699</v>
       </c>
       <c r="F35">
-        <v>1.5198876603757591E-2</v>
+        <v>1.5251886631413971E-2</v>
       </c>
       <c r="G35">
-        <v>2.3158763424120651E-2</v>
+        <v>2.2967147869063068E-2</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>1.303167093769343E-2</v>
+        <v>1.34671645109464E-2</v>
       </c>
       <c r="B36">
-        <v>1.7522783800770259E-2</v>
+        <v>1.7978522565423889E-2</v>
       </c>
       <c r="C36">
-        <v>5.4383621074896929E-2</v>
+        <v>5.4656096433738817E-2</v>
       </c>
       <c r="D36">
-        <v>0.43865698756046162</v>
+        <v>0.43742682883479789</v>
       </c>
       <c r="E36">
-        <v>0.43724296008075259</v>
+        <v>0.4374152036435181</v>
       </c>
       <c r="F36">
-        <v>1.581440844247195E-2</v>
+        <v>1.589967536309116E-2</v>
       </c>
       <c r="G36">
-        <v>2.3347568102947389E-2</v>
+        <v>2.3156508648495711E-2</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>1.382076252728124E-2</v>
+        <v>1.4291166302351711E-2</v>
       </c>
       <c r="B37">
-        <v>1.7406242784589319E-2</v>
+        <v>1.785883510629941E-2</v>
       </c>
       <c r="C37">
-        <v>5.6548767284510873E-2</v>
+        <v>5.6833922913288017E-2</v>
       </c>
       <c r="D37">
-        <v>0.44035911055295351</v>
+        <v>0.43900812221761959</v>
       </c>
       <c r="E37">
-        <v>0.43183321479412251</v>
+        <v>0.43202709695535768</v>
       </c>
       <c r="F37">
-        <v>1.6502721332397701E-2</v>
+        <v>1.6627987735512922E-2</v>
       </c>
       <c r="G37">
-        <v>2.352918072413536E-2</v>
+        <v>2.335286876957916E-2</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>1.4610004812946621E-2</v>
+        <v>1.5113764070857381E-2</v>
       </c>
       <c r="B38">
-        <v>1.726304811462781E-2</v>
+        <v>1.7702843542992151E-2</v>
       </c>
       <c r="C38">
-        <v>5.8668345820064249E-2</v>
+        <v>5.8965023157105501E-2</v>
       </c>
       <c r="D38">
-        <v>0.43936457922360722</v>
+        <v>0.43789125960662528</v>
       </c>
       <c r="E38">
-        <v>0.42913018609976089</v>
+        <v>0.42934036857446323</v>
       </c>
       <c r="F38">
-        <v>1.7258657091134069E-2</v>
+        <v>1.7430054564491669E-2</v>
       </c>
       <c r="G38">
-        <v>2.3705178837844121E-2</v>
+        <v>2.3556686483474951E-2</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>1.5386998401548989E-2</v>
+        <v>1.5922769751617431E-2</v>
       </c>
       <c r="B39">
-        <v>1.7108068888998951E-2</v>
+        <v>1.752749881652382E-2</v>
       </c>
       <c r="C39">
-        <v>6.0732357349046591E-2</v>
+        <v>6.1039816515207367E-2</v>
       </c>
       <c r="D39">
-        <v>0.43588435319048552</v>
+        <v>0.43428406337227032</v>
       </c>
       <c r="E39">
-        <v>0.42893509564599358</v>
+        <v>0.42916123288451402</v>
       </c>
       <c r="F39">
-        <v>1.807587445054663E-2</v>
+        <v>1.8297027954157181E-2</v>
       </c>
       <c r="G39">
-        <v>2.3877252073369361E-2</v>
+        <v>2.3767590705717941E-2</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>1.6140238349280741E-2</v>
+        <v>1.670701024684031E-2</v>
       </c>
       <c r="B40">
-        <v>1.695448303815186E-2</v>
+        <v>1.7348898279285339E-2</v>
       </c>
       <c r="C40">
-        <v>6.2732805971320735E-2</v>
+        <v>6.3050964748356655E-2</v>
       </c>
       <c r="D40">
-        <v>0.43020929144083653</v>
+        <v>0.42847040730627561</v>
       </c>
       <c r="E40">
-        <v>0.43096916143193509</v>
+        <v>0.43121927396284671</v>
       </c>
       <c r="F40">
-        <v>1.894745200928025E-2</v>
+        <v>1.921879202940753E-2</v>
       </c>
       <c r="G40">
-        <v>2.404656775918651E-2</v>
+        <v>2.398465342701589E-2</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>1.6859495962826401E-2</v>
+        <v>1.7456606250888219E-2</v>
       </c>
       <c r="B41">
-        <v>1.681328959021159E-2</v>
+        <v>1.7181490660466741E-2</v>
       </c>
       <c r="C41">
-        <v>6.4664284057788915E-2</v>
+        <v>6.4993756829094057E-2</v>
       </c>
       <c r="D41">
-        <v>0.42269315155599813</v>
+        <v>0.42079363002300679</v>
       </c>
       <c r="E41">
-        <v>0.43488987344164648</v>
+        <v>0.43518328622128472</v>
       </c>
       <c r="F41">
-        <v>1.9866066191653049E-2</v>
+        <v>2.0184659830341831E-2</v>
       </c>
       <c r="G41">
-        <v>2.4213839199872429E-2</v>
+        <v>2.420657018491475E-2</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>1.7536142357510661E-2</v>
+        <v>1.816330116051092E-2</v>
       </c>
       <c r="B42">
-        <v>1.6693203882285849E-2</v>
+        <v>1.703744234651277E-2</v>
       </c>
       <c r="C42">
-        <v>6.6524318690980508E-2</v>
+        <v>6.6866367372106439E-2</v>
       </c>
       <c r="D42">
-        <v>0.41373335107557829</v>
+        <v>0.41163888671469551</v>
       </c>
       <c r="E42">
-        <v>0.44030898188417589</v>
+        <v>0.44067811244127919</v>
       </c>
       <c r="F42">
-        <v>2.082418219599098E-2</v>
+        <v>2.118397890181694E-2</v>
       </c>
       <c r="G42">
-        <v>2.437981991347021E-2</v>
+        <v>2.4431911063099901E-2</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>1.816340163879308E-2</v>
+        <v>1.882068902455615E-2</v>
       </c>
       <c r="B43">
-        <v>1.6600713560699351E-2</v>
+        <v>1.6926240128964789E-2</v>
       </c>
       <c r="C43">
-        <v>6.8313367488745821E-2</v>
+        <v>6.8669786288628035E-2</v>
       </c>
       <c r="D43">
-        <v>0.40375058136731728</v>
+        <v>0.4014153864038626</v>
       </c>
       <c r="E43">
-        <v>0.44681245312821699</v>
+        <v>0.44730199016816591</v>
       </c>
       <c r="F43">
-        <v>2.1814138747324231E-2</v>
+        <v>2.220663638456832E-2</v>
       </c>
       <c r="G43">
-        <v>2.4545344068907071E-2</v>
+        <v>2.4659271601257519E-2</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>1.8736478919004911E-2</v>
+        <v>1.9424265456913701E-2</v>
       </c>
       <c r="B44">
-        <v>1.6540237981539311E-2</v>
+        <v>1.6854555314152281E-2</v>
       </c>
       <c r="C44">
-        <v>7.0034436871187253E-2</v>
+        <v>7.0407505729610603E-2</v>
       </c>
       <c r="D44">
-        <v>0.3931691865747341</v>
+        <v>0.39053928165116281</v>
       </c>
       <c r="E44">
-        <v>0.45398086794408637</v>
+        <v>0.45464361278362919</v>
       </c>
       <c r="F44">
-        <v>2.2827920887853459E-2</v>
+        <v>2.3243437736848869E-2</v>
       </c>
       <c r="G44">
-        <v>2.4710870821580012E-2</v>
+        <v>2.488734132769042E-2</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>1.9252541860169739E-2</v>
+        <v>1.997139884527915E-2</v>
       </c>
       <c r="B45">
-        <v>1.6514292998414701E-2</v>
+        <v>1.682626913575026E-2</v>
       </c>
       <c r="C45">
-        <v>7.1692637323713448E-2</v>
+        <v>7.2085120967986402E-2</v>
       </c>
       <c r="D45">
-        <v>0.38239888969570462</v>
+        <v>0.37941752674819978</v>
       </c>
       <c r="E45">
-        <v>0.46140806639651571</v>
+        <v>0.46229837089544568</v>
       </c>
       <c r="F45">
-        <v>2.385709028759431E-2</v>
+        <v>2.4286301649956168E-2</v>
       </c>
       <c r="G45">
-        <v>2.4876481437900579E-2</v>
+        <v>2.5115011757385931E-2</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>1.9710516441713989E-2</v>
+        <v>2.046127726126518E-2</v>
       </c>
       <c r="B46">
-        <v>1.6523554150159919E-2</v>
+        <v>1.6842647696066151E-2</v>
       </c>
       <c r="C46">
-        <v>7.3294878786930598E-2</v>
+        <v>7.3709819457138684E-2</v>
       </c>
       <c r="D46">
-        <v>0.37181873031984769</v>
+        <v>0.36843322593233602</v>
       </c>
       <c r="E46">
-        <v>0.46871691956311851</v>
+        <v>0.46988336905041422</v>
       </c>
       <c r="F46">
-        <v>2.489326013872141E-2</v>
+        <v>2.532825182889414E-2</v>
       </c>
       <c r="G46">
-        <v>2.5042140599494538E-2</v>
+        <v>2.5341408773901172E-2</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>2.0111114466567621E-2</v>
+        <v>2.0894813240951889E-2</v>
       </c>
       <c r="B47">
-        <v>1.656720932488822E-2</v>
+        <v>1.6902677809632831E-2</v>
       </c>
       <c r="C47">
-        <v>7.4848831802248661E-2</v>
+        <v>7.5289807070895859E-2</v>
       </c>
       <c r="D47">
-        <v>0.36176445414336911</v>
+        <v>0.35793304843486501</v>
       </c>
       <c r="E47">
-        <v>0.47557221631260049</v>
+        <v>0.4770503973128235</v>
       </c>
       <c r="F47">
-        <v>2.5928505712752958E-2</v>
+        <v>2.6363356426669041E-2</v>
       </c>
       <c r="G47">
-        <v>2.5207668237589399E-2</v>
+        <v>2.556589970417375E-2</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>2.0456693949071261E-2</v>
+        <v>2.127447195332674E-2</v>
       </c>
       <c r="B48">
-        <v>1.6643272335435721E-2</v>
+        <v>1.7003493461987731E-2</v>
       </c>
       <c r="C48">
-        <v>7.6362421700199898E-2</v>
+        <v>7.6833799455626323E-2</v>
       </c>
       <c r="D48">
-        <v>0.35251964554870369</v>
+        <v>0.34821699227535241</v>
       </c>
       <c r="E48">
-        <v>0.48168976076982972</v>
+        <v>0.4834964533673074</v>
       </c>
       <c r="F48">
-        <v>2.6955397269563919E-2</v>
+        <v>2.7386627032857821E-2</v>
       </c>
       <c r="G48">
-        <v>2.5372808427197319E-2</v>
+        <v>2.5788162453556428E-2</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>2.0750911818350901E-2</v>
+        <v>2.1604052034621461E-2</v>
       </c>
       <c r="B49">
-        <v>1.6748749470511699E-2</v>
+        <v>1.7140817175994791E-2</v>
       </c>
       <c r="C49">
-        <v>7.7843793437890149E-2</v>
+        <v>7.8350573324738562E-2</v>
       </c>
       <c r="D49">
-        <v>0.3443107175682853</v>
+        <v>0.33953061750407199</v>
       </c>
       <c r="E49">
-        <v>0.48684149062857451</v>
+        <v>0.48897181233346271</v>
       </c>
       <c r="F49">
-        <v>2.796709272064056E-2</v>
+        <v>2.839390295318266E-2</v>
       </c>
       <c r="G49">
-        <v>2.5537244355736219E-2</v>
+        <v>2.6008224673934849E-2</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>2.0998496165861351E-2</v>
+        <v>2.1888438904100669E-2</v>
       </c>
       <c r="B50">
-        <v>1.6879900265545769E-2</v>
+        <v>1.7309369557607469E-2</v>
       </c>
       <c r="C50">
-        <v>7.9300946450725066E-2</v>
+        <v>7.9848542120338428E-2</v>
       </c>
       <c r="D50">
-        <v>0.33730499324417762</v>
+        <v>0.33205982058269362</v>
       </c>
       <c r="E50">
-        <v>0.49085758347699282</v>
+        <v>0.49328559836974017</v>
       </c>
       <c r="F50">
-        <v>2.895753335904341E-2</v>
+        <v>2.9381757962497791E-2</v>
       </c>
       <c r="G50">
-        <v>2.5700547037660029E-2</v>
+        <v>2.622647250303288E-2</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>2.1205000802100971E-2</v>
+        <v>2.2133325601153789E-2</v>
       </c>
       <c r="B51">
-        <v>1.703246901168598E-2</v>
+        <v>1.750321985728084E-2</v>
       </c>
       <c r="C51">
-        <v>8.0741424336507092E-2</v>
+        <v>8.1335394028313593E-2</v>
       </c>
       <c r="D51">
-        <v>0.33161131744760991</v>
+        <v>0.32592840541456458</v>
       </c>
       <c r="E51">
-        <v>0.49362595274732651</v>
+        <v>0.49630856798825468</v>
       </c>
       <c r="F51">
-        <v>2.9921637965252691E-2</v>
+        <v>3.0347508037217311E-2</v>
       </c>
       <c r="G51">
-        <v>2.586219768952841E-2</v>
+        <v>2.6443579073222569E-2</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>2.137654869195978E-2</v>
+        <v>2.234493967871223E-2</v>
       </c>
       <c r="B52">
-        <v>1.7201878539506499E-2</v>
+        <v>1.7716103397509869E-2</v>
       </c>
       <c r="C52">
-        <v>8.2172085237764203E-2</v>
+        <v>8.2817852067257391E-2</v>
       </c>
       <c r="D52">
-        <v>0.32728264152094327</v>
+        <v>0.32119840196558203</v>
       </c>
       <c r="E52">
-        <v>0.49508969956152898</v>
+        <v>0.4979730335311357</v>
       </c>
       <c r="F52">
-        <v>3.0855472774367239E-2</v>
+        <v>3.1289302359469522E-2</v>
       </c>
       <c r="G52">
-        <v>2.6021673673923221E-2</v>
+        <v>2.6660367000341571E-2</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>2.15195925238898E-2</v>
+        <v>2.252979739488525E-2</v>
       </c>
       <c r="B53">
-        <v>1.738339840753652E-2</v>
+        <v>1.7941736796414129E-2</v>
       </c>
       <c r="C53">
-        <v>8.3598937084788522E-2</v>
+        <v>8.4301585935222412E-2</v>
       </c>
       <c r="D53">
-        <v>0.32431995496789778</v>
+        <v>0.31787284470315141</v>
       </c>
       <c r="E53">
-        <v>0.49524321598614751</v>
+        <v>0.49827016846760491</v>
       </c>
       <c r="F53">
-        <v>3.1756360257511038E-2</v>
+        <v>3.22061777810888E-2</v>
       </c>
       <c r="G53">
-        <v>2.6178540772207281E-2</v>
+        <v>2.6877688921645701E-2</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>2.1640702756476341E-2</v>
+        <v>2.2694482780308379E-2</v>
       </c>
       <c r="B54">
-        <v>1.7572304389217658E-2</v>
+        <v>1.8174106319262699E-2</v>
       </c>
       <c r="C54">
-        <v>8.5027038857101014E-2</v>
+        <v>8.5791220717171573E-2</v>
       </c>
       <c r="D54">
-        <v>0.32267706347063069</v>
+        <v>0.3159006681115929</v>
       </c>
       <c r="E54">
-        <v>0.4941274684672699</v>
+        <v>0.497245144981524</v>
       </c>
       <c r="F54">
-        <v>3.2622903167027317E-2</v>
+        <v>3.3098055033323789E-2</v>
       </c>
       <c r="G54">
-        <v>2.6332518892292059E-2</v>
+        <v>2.7096322056825359E-2</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>2.1746387868368369E-2</v>
+        <v>2.2845448259694329E-2</v>
       </c>
       <c r="B55">
-        <v>1.7764041622746581E-2</v>
+        <v>1.8407694082067369E-2</v>
       </c>
       <c r="C55">
-        <v>8.6460442784336011E-2</v>
+        <v>8.7290393249364037E-2</v>
       </c>
       <c r="D55">
-        <v>0.32226590599622251</v>
+        <v>0.31518333402540483</v>
       </c>
       <c r="E55">
-        <v>0.49182479229925219</v>
+        <v>0.49499055670103281</v>
       </c>
       <c r="F55">
-        <v>3.3454907422532917E-2</v>
+        <v>3.3965694563681641E-2</v>
       </c>
       <c r="G55">
-        <v>2.6483522006538852E-2</v>
+        <v>2.7316879118769889E-2</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>2.1842938264739091E-2</v>
+        <v>2.2988828391239311E-2</v>
       </c>
       <c r="B56">
-        <v>1.7954377265608029E-2</v>
+        <v>1.863763316536508E-2</v>
       </c>
       <c r="C56">
-        <v>8.7902156230725531E-2</v>
+        <v>8.8801829761250145E-2</v>
       </c>
       <c r="D56">
-        <v>0.32296235319084199</v>
+        <v>0.31558285045679491</v>
       </c>
       <c r="E56">
-        <v>0.48845326261976668</v>
+        <v>0.49163850201936282</v>
       </c>
       <c r="F56">
-        <v>3.4253220702172467E-2</v>
+        <v>3.4810616797958098E-2</v>
       </c>
       <c r="G56">
-        <v>2.663169172614523E-2</v>
+        <v>2.7539739408042069E-2</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>2.1936289055259489E-2</v>
+        <v>2.3130281930917158E-2</v>
       </c>
       <c r="B57">
-        <v>1.8139545280313859E-2</v>
+        <v>1.8859806878997451E-2</v>
       </c>
       <c r="C57">
-        <v>8.935413559194999E-2</v>
+        <v>9.0327423618078911E-2</v>
       </c>
       <c r="D57">
-        <v>0.32461258657508979</v>
+        <v>0.31693079008779212</v>
       </c>
       <c r="E57">
-        <v>0.48416051212310801</v>
+        <v>0.48735169619771301</v>
       </c>
       <c r="F57">
-        <v>3.5019524439499523E-2</v>
+        <v>3.5634982001054277E-2</v>
       </c>
       <c r="G57">
-        <v>2.67774069347585E-2</v>
+        <v>2.7765019285452681E-2</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>2.2031895298232771E-2</v>
+        <v>2.3274873779147661E-2</v>
       </c>
       <c r="B58">
-        <v>1.8316367935920619E-2</v>
+        <v>1.907091671596646E-2</v>
       </c>
       <c r="C58">
-        <v>9.0817343213189405E-2</v>
+        <v>9.1868300935731631E-2</v>
       </c>
       <c r="D58">
-        <v>0.32704015582807178</v>
+        <v>0.31903785754976172</v>
       </c>
       <c r="E58">
-        <v>0.47911689704150162</v>
+        <v>0.48231405140438</v>
       </c>
       <c r="F58">
-        <v>3.5756112154442979E-2</v>
+        <v>3.6441417337949207E-2</v>
       </c>
       <c r="G58">
-        <v>2.69212285286357E-2</v>
+        <v>2.7992582277066021E-2</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>2.2134625451985121E-2</v>
+        <v>2.3426989297627269E-2</v>
       </c>
       <c r="B59">
-        <v>1.8482322060061059E-2</v>
+        <v>1.926853147839952E-2</v>
       </c>
       <c r="C59">
-        <v>9.2291836831502133E-2</v>
+        <v>9.3424871199910262E-2</v>
       </c>
       <c r="D59">
-        <v>0.33005371150594037</v>
+        <v>0.32170354300333281</v>
       </c>
       <c r="E59">
-        <v>0.47350801613444637</v>
+        <v>0.47672119272551478</v>
       </c>
       <c r="F59">
-        <v>3.6465677932149547E-2</v>
+        <v>3.7232800535109023E-2</v>
       </c>
       <c r="G59">
-        <v>2.7063810083915039E-2</v>
+        <v>2.822207176009818E-2</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>2.224866924712272E-2</v>
+        <v>2.3590276026207439E-2</v>
       </c>
       <c r="B60">
-        <v>1.8635558704618499E-2</v>
+        <v>1.945111246318176E-2</v>
       </c>
       <c r="C60">
-        <v>9.3776843988356354E-2</v>
+        <v>9.4996887119783616E-2</v>
       </c>
       <c r="D60">
-        <v>0.33345523763552259</v>
+        <v>0.32472543116970348</v>
       </c>
       <c r="E60">
-        <v>0.46752674089885171</v>
+        <v>0.47077131857685228</v>
       </c>
       <c r="F60">
-        <v>3.7151113194490819E-2</v>
+        <v>3.801202784017526E-2</v>
       </c>
       <c r="G60">
-        <v>2.720583633104779E-2</v>
+        <v>2.8452946804101781E-2</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>2.2377461570145449E-2</v>
+        <v>2.3767617119221832E-2</v>
       </c>
       <c r="B61">
-        <v>1.87749121558436E-2</v>
+        <v>1.9618003007706709E-2</v>
       </c>
       <c r="C61">
-        <v>9.5270800432794872E-2</v>
+        <v>9.6583530906280135E-2</v>
       </c>
       <c r="D61">
-        <v>0.33704843827242092</v>
+        <v>0.32790777294866841</v>
       </c>
       <c r="E61">
-        <v>0.46136506917349801</v>
+        <v>0.46465675721709171</v>
       </c>
       <c r="F61">
-        <v>3.7815330186317463E-2</v>
+        <v>3.8781799838733977E-2</v>
       </c>
       <c r="G61">
-        <v>2.734798820895468E-2</v>
+        <v>2.868451896232126E-2</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>2.252364241381585E-2</v>
+        <v>2.3961136136125889E-2</v>
       </c>
       <c r="B62">
-        <v>1.889988593661299E-2</v>
+        <v>1.976937854567561E-2</v>
       </c>
       <c r="C62">
-        <v>9.6771398862050911E-2</v>
+        <v>9.818351307523876E-2</v>
       </c>
       <c r="D62">
-        <v>0.34064685917027909</v>
+        <v>0.33106896228489879</v>
       </c>
       <c r="E62">
-        <v>0.45520620348388091</v>
+        <v>0.45855657096311458</v>
       </c>
       <c r="F62">
-        <v>3.8461095290848929E-2</v>
+        <v>3.954444256421237E-2</v>
       </c>
       <c r="G62">
-        <v>2.749091484250225E-2</v>
+        <v>2.8915996430736789E-2</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>2.2689047336551429E-2</v>
+        <v>2.4172227575872809E-2</v>
       </c>
       <c r="B63">
-        <v>1.901061979211361E-2</v>
+        <v>1.990616234192303E-2</v>
       </c>
       <c r="C63">
-        <v>9.8275680367988255E-2</v>
+        <v>9.9795166758996801E-2</v>
       </c>
       <c r="D63">
-        <v>0.34408137899762919</v>
+        <v>0.33404761477095141</v>
       </c>
       <c r="E63">
-        <v>0.44921721358188399</v>
+        <v>0.45263052548710231</v>
       </c>
       <c r="F63">
-        <v>3.9090854466787617E-2</v>
+        <v>4.0301773309221141E-2</v>
       </c>
       <c r="G63">
-        <v>2.7635205457041331E-2</v>
+        <v>2.914652975593874E-2</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>2.2874724382378739E-2</v>
+        <v>2.4401605192378311E-2</v>
       </c>
       <c r="B64">
-        <v>1.9107842852143501E-2</v>
+        <v>2.0029913090178771E-2</v>
       </c>
       <c r="C64">
-        <v>9.9780150360869166E-2</v>
+        <v>0.10141652031664911</v>
       </c>
       <c r="D64">
-        <v>0.34720666000648293</v>
+        <v>0.33670703614045783</v>
       </c>
       <c r="E64">
-        <v>0.44354267605038739</v>
+        <v>0.44701464902548732</v>
       </c>
       <c r="F64">
-        <v>3.9706586927101807E-2</v>
+        <v>4.1055023159827127E-2</v>
       </c>
       <c r="G64">
-        <v>2.778135942064398E-2</v>
+        <v>2.9375253075027152E-2</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>2.3080977024392008E-2</v>
+        <v>2.4649360535969288E-2</v>
       </c>
       <c r="B65">
-        <v>1.919280596121983E-2</v>
+        <v>2.0142690791075769E-2</v>
       </c>
       <c r="C65">
-        <v>0.10128090247049409</v>
+        <v>0.1030453365351081</v>
       </c>
       <c r="D65">
-        <v>0.34990620562324609</v>
+        <v>0.3389379858588692</v>
       </c>
       <c r="E65">
-        <v>0.43829963476204647</v>
+        <v>0.44181848310340749</v>
       </c>
       <c r="F65">
-        <v>4.0309716588721872E-2</v>
+        <v>4.1804822512857019E-2</v>
       </c>
       <c r="G65">
-        <v>2.7929757569896439E-2</v>
+        <v>2.9601320662715681E-2</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>2.330742821332531E-2</v>
+        <v>2.4915030074031529E-2</v>
       </c>
       <c r="B66">
-        <v>1.9267191654365481E-2</v>
+        <v>2.0246909334813809E-2</v>
       </c>
       <c r="C66">
-        <v>0.1027737459301503</v>
+        <v>0.1046791112201719</v>
       </c>
       <c r="D66">
-        <v>0.3520957999314529</v>
+        <v>0.34065978740701652</v>
       </c>
       <c r="E66">
-        <v>0.43357412020169522</v>
+        <v>0.43712397819736792</v>
       </c>
       <c r="F66">
-        <v>4.0901072938333352E-2</v>
+        <v>4.2551240685731608E-2</v>
       </c>
       <c r="G66">
-        <v>2.8080641130679269E-2</v>
+        <v>2.9823943080872231E-2</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>2.3553102567771499E-2</v>
+        <v>2.5197671261707431E-2</v>
       </c>
       <c r="B67">
-        <v>1.9333006703746651E-2</v>
+        <v>2.0345180990315952E-2</v>
       </c>
       <c r="C67">
-        <v>0.10425434040096029</v>
+        <v>0.10631504616391479</v>
       </c>
       <c r="D67">
-        <v>0.35372508586480028</v>
+        <v>0.34181999481314351</v>
       </c>
       <c r="E67">
-        <v>0.42941947549242959</v>
+        <v>0.43298582869802038</v>
       </c>
       <c r="F67">
-        <v>4.1480887297493822E-2</v>
+        <v>4.3293855847943707E-2</v>
       </c>
       <c r="G67">
-        <v>2.8234101672812491E-2</v>
+        <v>3.0042422224954748E-2</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>2.3816524025824189E-2</v>
+        <v>2.5495946704864578E-2</v>
       </c>
       <c r="B68">
-        <v>1.9392461596145289E-2</v>
+        <v>2.044015683485035E-2</v>
       </c>
       <c r="C68">
-        <v>0.10571833679442789</v>
+        <v>0.1079500193222263</v>
       </c>
       <c r="D68">
-        <v>0.3547771827569729</v>
+        <v>0.3423929164414104</v>
       </c>
       <c r="E68">
-        <v>0.42585659161371109</v>
+        <v>0.42943295199591142</v>
       </c>
       <c r="F68">
-        <v>4.2048827297321581E-2</v>
+        <v>4.4031834361180543E-2</v>
       </c>
       <c r="G68">
-        <v>2.839007591558524E-2</v>
+        <v>3.0256174339566681E-2</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>2.4095824630675479E-2</v>
+        <v>2.5808214436392071E-2</v>
       </c>
       <c r="B69">
-        <v>1.9447839855014502E-2</v>
+        <v>2.053437546198171E-2</v>
       </c>
       <c r="C69">
-        <v>0.1071615147681194</v>
+        <v>0.1095805724185684</v>
       </c>
       <c r="D69">
-        <v>0.35526642535126352</v>
+        <v>0.34237731315676723</v>
       </c>
       <c r="E69">
-        <v>0.4228759842305681</v>
+        <v>0.42647077424895569</v>
       </c>
       <c r="F69">
-        <v>4.2604071624199727E-2</v>
+        <v>4.4764017897785127E-2</v>
       </c>
       <c r="G69">
-        <v>2.854833954016615E-2</v>
+        <v>3.046473237955457E-2</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>2.4388859809826011E-2</v>
+        <v>2.613261740343131E-2</v>
       </c>
       <c r="B70">
-        <v>1.9501362951682331E-2</v>
+        <v>2.063013545650005E-2</v>
       </c>
       <c r="C70">
-        <v>0.10857991117129639</v>
+        <v>0.11120293205166799</v>
       </c>
       <c r="D70">
-        <v>0.35523447273865177</v>
+        <v>0.3417935546289137</v>
       </c>
       <c r="E70">
-        <v>0.42044147410865618</v>
+        <v>0.42408400868037371</v>
       </c>
       <c r="F70">
-        <v>4.3145416860676113E-2</v>
+        <v>4.5489021198093511E-2</v>
       </c>
       <c r="G70">
-        <v>2.8708502359207699E-2</v>
+        <v>3.0667730581030402E-2</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>2.4693326369436011E-2</v>
+        <v>2.6467171885835489E-2</v>
       </c>
       <c r="B71">
-        <v>1.955506019828529E-2</v>
+        <v>2.0729400237147661E-2</v>
       </c>
       <c r="C71">
-        <v>0.10996993792071739</v>
+        <v>0.11281306847074279</v>
       </c>
       <c r="D71">
-        <v>0.35474514262280099</v>
+        <v>0.34068045225590271</v>
       </c>
       <c r="E71">
-        <v>0.41849511788244109</v>
+        <v>0.42223968488409103</v>
       </c>
       <c r="F71">
-        <v>4.3671404573863482E-2</v>
+        <v>4.6205336065667298E-2</v>
       </c>
       <c r="G71">
-        <v>2.887001043244837E-2</v>
+        <v>3.086488620060894E-2</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>2.5006877902117509E-2</v>
+        <v>2.6809852412391141E-2</v>
       </c>
       <c r="B72">
-        <v>1.961065300091162E-2</v>
+        <v>2.0833732789472072E-2</v>
       </c>
       <c r="C72">
-        <v>0.1113284884698738</v>
+        <v>0.1144067806676697</v>
       </c>
       <c r="D72">
-        <v>0.35387836943194961</v>
+        <v>0.33909193530831711</v>
       </c>
       <c r="E72">
-        <v>0.41696299377656509</v>
+        <v>0.42089028069470719</v>
       </c>
       <c r="F72">
-        <v>4.4180459738898462E-2</v>
+        <v>4.6911431089664481E-2</v>
       </c>
       <c r="G72">
-        <v>2.9032157679677349E-2</v>
+        <v>3.1055987037780199E-2</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>2.532723072584948E-2</v>
+        <v>2.7158669436135811E-2</v>
       </c>
       <c r="B73">
-        <v>1.966946115179783E-2</v>
+        <v>2.094425395451454E-2</v>
       </c>
       <c r="C73">
-        <v>0.1126530302943094</v>
+        <v>0.115979807791754</v>
       </c>
       <c r="D73">
-        <v>0.35272370131059771</v>
+        <v>0.33709367231229143</v>
       </c>
       <c r="E73">
-        <v>0.41576143432774437</v>
+        <v>0.41997687063233041</v>
       </c>
       <c r="F73">
-        <v>4.4671034478546479E-2</v>
+        <v>4.7605843142964809E-2</v>
       </c>
       <c r="G73">
-        <v>2.9194107711167181E-2</v>
+        <v>3.124088272999995E-2</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>2.5652252700678582E-2</v>
+        <v>2.7511733216263531E-2</v>
       </c>
       <c r="B74">
-        <v>1.9732337031829389E-2</v>
+        <v>2.1061619066624251E-2</v>
       </c>
       <c r="C74">
-        <v>0.11394167989079571</v>
+        <v>0.1175279525772991</v>
       </c>
       <c r="D74">
-        <v>0.3513737736350252</v>
+        <v>0.33475970702777991</v>
       </c>
       <c r="E74">
-        <v>0.41480328211905287</v>
+        <v>0.41943224513573862</v>
       </c>
       <c r="F74">
-        <v>4.514174738871287E-2</v>
+        <v>4.8287263279488887E-2</v>
       </c>
       <c r="G74">
-        <v>2.9354927233912271E-2</v>
+        <v>3.1419479696798563E-2</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>2.5980028502763191E-2</v>
+        <v>2.7867299336032679E-2</v>
       </c>
       <c r="B75">
-        <v>1.9799633023149941E-2</v>
+        <v>2.1186012893852971E-2</v>
       </c>
       <c r="C75">
-        <v>0.1151932546690466</v>
+        <v>0.11904721232799841</v>
       </c>
       <c r="D75">
-        <v>0.34991821139843399</v>
+        <v>0.33216915562519561</v>
       </c>
       <c r="E75">
-        <v>0.41400373341680952</v>
+        <v>0.41918396753727449</v>
       </c>
       <c r="F75">
-        <v>4.5591505752583042E-2</v>
+        <v>4.8954612727981697E-2</v>
       </c>
       <c r="G75">
-        <v>2.9513633237218569E-2</v>
+        <v>3.1591739551672438E-2</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>2.630889931405303E-2</v>
+        <v>2.82237976272245E-2</v>
       </c>
       <c r="B76">
-        <v>1.9871204903089398E-2</v>
+        <v>2.1317168746390568E-2</v>
       </c>
       <c r="C76">
-        <v>0.1164072963893967</v>
+        <v>0.12053390613430311</v>
       </c>
       <c r="D76">
-        <v>0.34843837918319659</v>
+        <v>0.32940300944021772</v>
       </c>
       <c r="E76">
-        <v>0.41328537115545932</v>
+        <v>0.41915733991788701</v>
       </c>
       <c r="F76">
-        <v>4.6019597351449518E-2</v>
+        <v>4.9607099199949711E-2</v>
       </c>
       <c r="G76">
-        <v>2.9669251703375039E-2</v>
+        <v>3.1757678934022059E-2</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>2.6637480334367161E-2</v>
+        <v>2.8579847980144339E-2</v>
       </c>
       <c r="B77">
-        <v>1.994645090952506E-2</v>
+        <v>2.1454415454828759E-2</v>
       </c>
       <c r="C77">
-        <v>0.11758405948275941</v>
+        <v>0.1219847927139892</v>
       </c>
       <c r="D77">
-        <v>0.3470033039393069</v>
+        <v>0.32654109865773329</v>
       </c>
       <c r="E77">
-        <v>0.41258208197082491</v>
+        <v>0.41927823550527721</v>
       </c>
       <c r="F77">
-        <v>4.6425741923317693E-2</v>
+        <v>5.0244241789276931E-2</v>
       </c>
       <c r="G77">
-        <v>2.982088143987921E-2</v>
+        <v>3.1917367898758299E-2</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>2.696466117798859E-2</v>
+        <v>2.8934269330248369E-2</v>
       </c>
       <c r="B78">
-        <v>2.0024382227108561E-2</v>
+        <v>2.1596751006916291E-2</v>
       </c>
       <c r="C78">
-        <v>0.1187244601772537</v>
+        <v>0.1233971734232287</v>
       </c>
       <c r="D78">
-        <v>0.34566695356605659</v>
+        <v>0.32365928700583008</v>
       </c>
       <c r="E78">
-        <v>0.41184169115258751</v>
+        <v>0.41947573260257881</v>
       </c>
       <c r="F78">
-        <v>4.681009699078123E-2</v>
+        <v>5.0865861450107963E-2</v>
       </c>
       <c r="G78">
-        <v>2.996775470821425E-2</v>
+        <v>3.2070925181096187E-2</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>2.7289593231700951E-2</v>
+        <v>2.9286083475391751E-2</v>
       </c>
       <c r="B79">
-        <v>2.0103717527237511E-2</v>
+        <v>2.1742937062352561E-2</v>
       </c>
       <c r="C79">
-        <v>0.11982998734115891</v>
+        <v>0.1247689759720365</v>
       </c>
       <c r="D79">
-        <v>0.34446689290913279</v>
+        <v>0.32082698790013209</v>
       </c>
       <c r="E79">
-        <v>0.41102730115814301</v>
+        <v>0.41968446574528501</v>
       </c>
       <c r="F79">
-        <v>4.7173220546519082E-2</v>
+        <v>5.1472039323481378E-2</v>
       </c>
       <c r="G79">
-        <v>3.0109287286105801E-2</v>
+        <v>3.2218510521326793E-2</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>2.7611666923750191E-2</v>
+        <v>2.9634516053497512E-2</v>
       </c>
       <c r="B80">
-        <v>2.0182991480821789E-2</v>
+        <v>2.1891604521414889E-2</v>
       </c>
       <c r="C80">
-        <v>0.12090258207142961</v>
+        <v>0.1260988156563754</v>
       </c>
       <c r="D80">
-        <v>0.34342420209773289</v>
+        <v>0.31810509071825999</v>
       </c>
       <c r="E80">
-        <v>0.41011744558750668</v>
+        <v>0.41984660146484287</v>
       </c>
       <c r="F80">
-        <v>4.7516000203281852E-2</v>
+        <v>5.2063056306131922E-2</v>
       </c>
       <c r="G80">
-        <v>3.0245111635484691E-2</v>
+        <v>3.2360315279481452E-2</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>2.793048214987091E-2</v>
+        <v>2.997899450840583E-2</v>
       </c>
       <c r="B81">
-        <v>2.0260666416830959E-2</v>
+        <v>2.204135996545268E-2</v>
       </c>
       <c r="C81">
-        <v>0.1219444960531519</v>
+        <v>0.12738603152109429</v>
       </c>
       <c r="D81">
-        <v>0.34254446085204948</v>
+        <v>0.31554437987624878</v>
       </c>
       <c r="E81">
-        <v>0.40910524132004999</v>
+        <v>0.41991336087602782</v>
       </c>
       <c r="F81">
-        <v>4.7839563110648013E-2</v>
+        <v>5.263931907073046E-2</v>
       </c>
       <c r="G81">
-        <v>3.037509009739723E-2</v>
+        <v>3.2496554182048457E-2</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>2.8245815265155311E-2</v>
+        <v>3.0319143506260599E-2</v>
       </c>
       <c r="B82">
-        <v>2.0335236894260408E-2</v>
+        <v>2.2190882452029711E-2</v>
       </c>
       <c r="C82">
-        <v>0.1229581398838684</v>
+        <v>0.12863070034097071</v>
       </c>
       <c r="D82">
-        <v>0.34181958231431531</v>
+        <v>0.31318452586696732</v>
       </c>
       <c r="E82">
-        <v>0.40799673688873561</v>
+        <v>0.4198460134075257</v>
       </c>
       <c r="F82">
-        <v>4.8145180529696449E-2</v>
+        <v>5.3201274062246277E-2</v>
       </c>
       <c r="G82">
-        <v>3.049930822397294E-2</v>
+        <v>3.2627460364000722E-2</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>2.8557585721759971E-2</v>
+        <v>3.0654778366091599E-2</v>
       </c>
       <c r="B83">
-        <v>2.0405319495120471E-2</v>
+        <v>2.2339002191551181E-2</v>
       </c>
       <c r="C83">
-        <v>0.123945933507301</v>
+        <v>0.12983363343777721</v>
       </c>
       <c r="D83">
-        <v>0.34123029754511103</v>
+        <v>0.31105372014568872</v>
       </c>
       <c r="E83">
-        <v>0.40680863501042552</v>
+        <v>0.41961625925684592</v>
       </c>
       <c r="F83">
-        <v>4.843417746139126E-2</v>
+        <v>5.3749324223127143E-2</v>
       </c>
       <c r="G83">
-        <v>3.0618051258893209E-2</v>
+        <v>3.2753282378913888E-2</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>2.8865825300539091E-2</v>
+        <v>3.098589685546042E-2</v>
       </c>
       <c r="B84">
-        <v>2.0469723344036149E-2</v>
+        <v>2.248475523725765E-2</v>
       </c>
       <c r="C84">
-        <v>0.12491017151144521</v>
+        <v>0.1309963544691681</v>
       </c>
       <c r="D84">
-        <v>0.34074911205965619</v>
+        <v>0.30916897192542109</v>
       </c>
       <c r="E84">
-        <v>0.40556554643176113</v>
+        <v>0.4192059757187816</v>
       </c>
       <c r="F84">
-        <v>4.8707852840561942E-2</v>
+        <v>5.4283765317455338E-2</v>
       </c>
       <c r="G84">
-        <v>3.0731768511994322E-2</v>
+        <v>3.2874280476457428E-2</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>2.9170652044262831E-2</v>
+        <v>3.1312667422322291E-2</v>
       </c>
       <c r="B85">
-        <v>2.05274999943479E-2</v>
+        <v>2.2627410441611082E-2</v>
       </c>
       <c r="C85">
-        <v>0.12585291457946479</v>
+        <v>0.1321210480736511</v>
       </c>
       <c r="D85">
-        <v>0.34034355672362909</v>
+        <v>0.30753700043739529</v>
       </c>
       <c r="E85">
-        <v>0.40429693218144619</v>
+        <v>0.41860640788288761</v>
       </c>
       <c r="F85">
-        <v>4.8967413536626182E-2</v>
+        <v>5.4804744919429042E-2</v>
       </c>
       <c r="G85">
-        <v>3.0841030940208361E-2</v>
+        <v>3.2990720822696627E-2</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>2.947224936269557E-2</v>
+        <v>3.1635415189801397E-2</v>
       </c>
       <c r="B86">
-        <v>2.057797328939397E-2</v>
+        <v>2.276646875857339E-2</v>
       </c>
       <c r="C86">
-        <v>0.1267759147809768</v>
+        <v>0.13321046945010609</v>
       </c>
       <c r="D86">
-        <v>0.33997953751289001</v>
+        <v>0.30615556599534077</v>
       </c>
       <c r="E86">
-        <v>0.40303391453732629</v>
+        <v>0.41781696499453769</v>
       </c>
       <c r="F86">
-        <v>4.9213924167144561E-2</v>
+        <v>5.5312246415651543E-2</v>
       </c>
       <c r="G86">
-        <v>3.0946486349579541E-2</v>
+        <v>3.310286919599028E-2</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>2.9770849337317409E-2</v>
+        <v>3.1954602462076237E-2</v>
       </c>
       <c r="B87">
-        <v>2.062075079439538E-2</v>
+        <v>2.290163740749775E-2</v>
       </c>
       <c r="C87">
-        <v>0.12768057700381619</v>
+        <v>0.13426781271401661</v>
       </c>
       <c r="D87">
-        <v>0.33962456343748842</v>
+        <v>0.3050150363318721</v>
       </c>
       <c r="E87">
-        <v>0.40180616970728789</v>
+        <v>0.4168438253918379</v>
       </c>
       <c r="F87">
-        <v>4.9448274339392563E-2</v>
+        <v>5.5806099515321603E-2</v>
       </c>
       <c r="G87">
-        <v>3.1048815380311869E-2</v>
+        <v>3.3210986177368139E-2</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>3.0066718222521369E-2</v>
+        <v>3.227080369017872E-2</v>
       </c>
       <c r="B88">
-        <v>2.065571880147803E-2</v>
+        <v>2.3032786621096469E-2</v>
       </c>
       <c r="C88">
-        <v>0.12856795314610531</v>
+        <v>0.13529654532876051</v>
       </c>
       <c r="D88">
-        <v>0.3392506172541036</v>
+        <v>0.30410000196448422</v>
       </c>
       <c r="E88">
-        <v>0.40063913792879358</v>
+        <v>0.41569852084390269</v>
       </c>
       <c r="F88">
-        <v>4.9671164458965911E-2</v>
+        <v>5.6286014967169493E-2</v>
       </c>
       <c r="G88">
-        <v>3.114869018803814E-2</v>
+        <v>3.3315326584413683E-2</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>3.0360142120893829E-2</v>
+        <v>3.2584672798871193E-2</v>
       </c>
       <c r="B89">
-        <v>2.06830228677649E-2</v>
+        <v>2.3159899000491809E-2</v>
       </c>
       <c r="C89">
-        <v>0.12943876180181971</v>
+        <v>0.13630022427506119</v>
       </c>
       <c r="D89">
-        <v>0.3388364434636697</v>
+        <v>0.30339082732943567</v>
       </c>
       <c r="E89">
-        <v>0.39955178278945719</v>
+        <v>0.41439659827036007</v>
       </c>
       <c r="F89">
-        <v>4.9883110138595248E-2</v>
+        <v>5.6751635014185377E-2</v>
       </c>
       <c r="G89">
-        <v>3.1246736817807839E-2</v>
+        <v>3.3416143311606111E-2</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>3.0651411750736029E-2</v>
+        <v>3.2896906983522857E-2</v>
       </c>
       <c r="B90">
-        <v>2.070303639769001E-2</v>
+        <v>2.3283020278335408E-2</v>
       </c>
       <c r="C90">
-        <v>0.130293425594455</v>
+        <v>0.13728231114237671</v>
       </c>
       <c r="D90">
-        <v>0.33836906797531868</v>
+        <v>0.30286509652903121</v>
       </c>
       <c r="E90">
-        <v>0.39855509194548722</v>
+        <v>0.41295638394343948</v>
       </c>
       <c r="F90">
-        <v>5.0084464078720872E-2</v>
+        <v>5.7202588016940163E-2</v>
       </c>
       <c r="G90">
-        <v>3.1343502257592727E-2</v>
+        <v>3.3513693106353347E-2</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>3.0940806541844449E-2</v>
+        <v>3.3208208439036983E-2</v>
       </c>
       <c r="B91">
-        <v>2.0716320212578701E-2</v>
+        <v>2.340221905939029E-2</v>
       </c>
       <c r="C91">
-        <v>0.13113212057573309</v>
+        <v>0.13824600297174161</v>
       </c>
       <c r="D91">
-        <v>0.33784443301177741</v>
+        <v>0.30249895872517968</v>
       </c>
       <c r="E91">
-        <v>0.39765143966174582</v>
+        <v>0.41139783002144398</v>
       </c>
       <c r="F91">
-        <v>5.0275452346435962E-2</v>
+        <v>5.7638539295807471E-2</v>
       </c>
       <c r="G91">
-        <v>3.1439427649882327E-2</v>
+        <v>3.3608241487410782E-2</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>3.1228578753318751E-2</v>
+        <v>3.3519249815065419E-2</v>
       </c>
       <c r="B92">
-        <v>2.072357617913894E-2</v>
+        <v>2.3517558388345822E-2</v>
       </c>
       <c r="C92">
-        <v>0.13195483504367861</v>
+        <v>0.13919409315316031</v>
       </c>
       <c r="D92">
-        <v>0.33726712416126592</v>
+        <v>0.30226839570082242</v>
       </c>
       <c r="E92">
-        <v>0.39683483663622832</v>
+        <v>0.40974141066822711</v>
       </c>
       <c r="F92">
-        <v>5.0456219917931318E-2</v>
+        <v>5.8059228843925517E-2</v>
       </c>
       <c r="G92">
-        <v>3.1534829308449287E-2</v>
+        <v>3.370006343045949E-2</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>3.1514938630837062E-2</v>
+        <v>3.3830647121368407E-2</v>
       </c>
       <c r="B93">
-        <v>2.072559798757562E-2</v>
+        <v>2.3629080527141539E-2</v>
       </c>
       <c r="C93">
-        <v>0.1327614360850731</v>
+        <v>0.14012887555509859</v>
       </c>
       <c r="D93">
-        <v>0.33664927124864308</v>
+        <v>0.30215042167746292</v>
       </c>
       <c r="E93">
-        <v>0.39609198645468752</v>
+        <v>0.40800704040966213</v>
       </c>
       <c r="F93">
-        <v>5.0626880029611812E-2</v>
+        <v>5.846449589834022E-2</v>
       </c>
       <c r="G93">
-        <v>3.1629889563572523E-2</v>
+        <v>3.3789438810919253E-2</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>3.1800041426818679E-2</v>
+        <v>3.4142942664140967E-2</v>
       </c>
       <c r="B94">
-        <v>2.0723221778318271E-2</v>
+        <v>2.3736801578519359E-2</v>
       </c>
       <c r="C94">
-        <v>0.13355174129696451</v>
+        <v>0.14105209922354719</v>
       </c>
       <c r="D94">
-        <v>0.33600880666121252</v>
+        <v>0.30212420757136349</v>
       </c>
       <c r="E94">
-        <v>0.39540396795713689</v>
+        <v>0.40621301689537992</v>
       </c>
       <c r="F94">
-        <v>5.0787561910449412E-2</v>
+        <v>5.8854289305531111E-2</v>
       </c>
       <c r="G94">
-        <v>3.172465896909496E-2</v>
+        <v>3.3876642761522573E-2</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>3.208397719950374E-2</v>
+        <v>3.4456598458493047E-2</v>
       </c>
       <c r="B95">
-        <v>2.0717279120302679E-2</v>
+        <v>2.3840712727865952E-2</v>
       </c>
       <c r="C95">
-        <v>0.13432559099450631</v>
+        <v>0.14196497396775501</v>
       </c>
       <c r="D95">
-        <v>0.33536734072686469</v>
+        <v>0.30217209088563779</v>
       </c>
       <c r="E95">
-        <v>0.39474828972234077</v>
+        <v>0.40437502184021962</v>
       </c>
       <c r="F95">
-        <v>5.0938451645450328E-2</v>
+        <v>5.9228669008660383E-2</v>
       </c>
       <c r="G95">
-        <v>3.1819070591045107E-2</v>
+        <v>3.3961933111371363E-2</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>3.2366764348495267E-2</v>
+        <v>3.4771997543029738E-2</v>
       </c>
       <c r="B96">
-        <v>2.0708554997059911E-2</v>
+        <v>2.394078568689384E-2</v>
       </c>
       <c r="C96">
-        <v>0.13508291445223369</v>
+        <v>0.1428682183958995</v>
       </c>
       <c r="D96">
-        <v>0.33474794491913928</v>
+        <v>0.3022804037980058</v>
       </c>
       <c r="E96">
-        <v>0.39410103437661109</v>
+        <v>0.40250525220638061</v>
       </c>
       <c r="F96">
-        <v>5.1079821251270328E-2</v>
+        <v>5.9587804095452959E-2</v>
       </c>
       <c r="G96">
-        <v>3.1912965655186573E-2</v>
+        <v>3.4045538274340537E-2</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>3.2648347531219007E-2</v>
+        <v>3.5089451548956867E-2</v>
       </c>
       <c r="B97">
-        <v>2.0697753503567989E-2</v>
+        <v>2.4036979598166631E-2</v>
       </c>
       <c r="C97">
-        <v>0.1358237838686123</v>
+        <v>0.14376213806926591</v>
       </c>
       <c r="D97">
-        <v>0.33417311124840021</v>
+        <v>0.30244002811143178</v>
       </c>
       <c r="E97">
-        <v>0.39343883344239328</v>
+        <v>0.40061178353448468</v>
       </c>
       <c r="F97">
-        <v>5.1212042442127279E-2</v>
+        <v>5.9931970702504681E-2</v>
       </c>
       <c r="G97">
-        <v>3.2006127963688971E-2</v>
+        <v>3.4127648435195883E-2</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>3.2928600422425007E-2</v>
+        <v>3.5409209742347868E-2</v>
       </c>
       <c r="B98">
-        <v>2.068547380754783E-2</v>
+        <v>2.4129248839074378E-2</v>
       </c>
       <c r="C98">
-        <v>0.13654845149785</v>
+        <v>0.1446467212704978</v>
       </c>
       <c r="D98">
-        <v>0.33366308778843312</v>
+        <v>0.30264657734152162</v>
       </c>
       <c r="E98">
-        <v>0.3927404795971432</v>
+        <v>0.39869827925007789</v>
       </c>
       <c r="F98">
-        <v>5.1335584048832789E-2</v>
+        <v>6.026155147511409E-2</v>
       </c>
       <c r="G98">
-        <v>3.2098322837759881E-2</v>
+        <v>3.4208412081366928E-2</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>3.3207333432878933E-2</v>
+        <v>3.5731467212793418E-2</v>
       </c>
       <c r="B99">
-        <v>2.0672197893176661E-2</v>
+        <v>2.421755073650636E-2</v>
       </c>
       <c r="C99">
-        <v>0.13725736789604881</v>
+        <v>0.14552174156269779</v>
       </c>
       <c r="D99">
-        <v>0.33323469661135158</v>
+        <v>0.30290012386862858</v>
       </c>
       <c r="E99">
-        <v>0.39198807484682557</v>
+        <v>0.39676414532337878</v>
       </c>
       <c r="F99">
-        <v>5.145099380275156E-2</v>
+        <v>6.0577033604265931E-2</v>
       </c>
       <c r="G99">
-        <v>3.2189335516973103E-2</v>
+        <v>3.4287937691734528E-2</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>3.3484305835634692E-2</v>
+        <v>3.6056371253082441E-2</v>
       </c>
       <c r="B100">
-        <v>2.0658290207530749E-2</v>
+        <v>2.4301852961779471E-2</v>
       </c>
       <c r="C100">
-        <v>0.13795118187996</v>
+        <v>0.14638685664450371</v>
       </c>
       <c r="D100">
-        <v>0.33290064544411718</v>
+        <v>0.30320443012254622</v>
       </c>
       <c r="E100">
-        <v>0.39116770516631888</v>
+        <v>0.39480518208161391</v>
       </c>
       <c r="F100">
-        <v>5.1558867128227603E-2</v>
+        <v>6.0879006056089549E-2</v>
       </c>
       <c r="G100">
-        <v>3.2279004338226419E-2</v>
+        <v>3.4366300880389548E-2</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>3.3759241231516343E-2</v>
+        <v>3.6384024620341078E-2</v>
       </c>
       <c r="B101">
-        <v>2.064400785843467E-2</v>
+        <v>2.438213910208822E-2</v>
       </c>
       <c r="C101">
-        <v>0.13863072571151919</v>
+        <v>0.1472416948131639</v>
       </c>
       <c r="D101">
-        <v>0.33266926888362602</v>
+        <v>0.30356570460388971</v>
       </c>
       <c r="E101">
-        <v>0.39026970344204659</v>
+        <v>0.39281472799387718</v>
       </c>
       <c r="F101">
-        <v>5.1659807913219287E-2</v>
+        <v>6.1168154258718722E-2</v>
       </c>
       <c r="G101">
-        <v>3.2367244959626451E-2</v>
+        <v>3.4443554607916392E-2</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>3.4031844976882317E-2</v>
+        <v>3.6714485537344743E-2</v>
       </c>
       <c r="B102">
-        <v>2.062951889135194E-2</v>
+        <v>2.4458412396425759E-2</v>
       </c>
       <c r="C102">
-        <v>0.13929699108089319</v>
+        <v>0.14808592096768841</v>
       </c>
       <c r="D102">
-        <v>0.33254459185333951</v>
+        <v>0.30399096535262582</v>
       </c>
       <c r="E102">
-        <v>0.38928860185989</v>
+        <v>0.3907852204175124</v>
       </c>
       <c r="F102">
-        <v>5.1754387686835511E-2</v>
+        <v>6.1445253617145007E-2</v>
       </c>
       <c r="G102">
-        <v>3.2454063650800419E-2</v>
+        <v>3.4519741711266767E-2</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>3.4301822073324037E-2</v>
+        <v>3.7047764308203557E-2</v>
       </c>
       <c r="B103">
-        <v>2.061492545347151E-2</v>
+        <v>2.4530697861997311E-2</v>
       </c>
       <c r="C103">
-        <v>0.13995110187466209</v>
+        <v>0.1489192774032041</v>
       </c>
       <c r="D103">
-        <v>0.33252659634971832</v>
+        <v>0.3044861587894373</v>
       </c>
       <c r="E103">
-        <v>0.38822288525626558</v>
+        <v>0.3887100335224265</v>
       </c>
       <c r="F103">
-        <v>5.1843109923342443E-2</v>
+        <v>6.1711160386748523E-2</v>
       </c>
       <c r="G103">
-        <v>3.2539559069221791E-2</v>
+        <v>3.4594907727985999E-2</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>3.4568894004939378E-2</v>
+        <v>3.7383816780858489E-2</v>
       </c>
       <c r="B104">
-        <v>2.0600288498864749E-2</v>
+        <v>2.4599043832450831E-2</v>
       </c>
       <c r="C104">
-        <v>0.1405942887556561</v>
+        <v>0.1497415975721767</v>
       </c>
       <c r="D104">
-        <v>0.33261158558345749</v>
+        <v>0.30505424050988073</v>
       </c>
       <c r="E104">
-        <v>0.38707464470695668</v>
+        <v>0.38658538892486771</v>
       </c>
       <c r="F104">
-        <v>5.1926384841285332E-2</v>
+        <v>6.1966799910542547E-2</v>
       </c>
       <c r="G104">
-        <v>3.2623913608833759E-2</v>
+        <v>3.4669112469220983E-2</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>3.4832813223135382E-2</v>
+        <v>3.7722535351693717E-2</v>
       </c>
       <c r="B105">
-        <v>2.0585651188847021E-2</v>
+        <v>2.4663523714511752E-2</v>
       </c>
       <c r="C105">
-        <v>0.14122786818035329</v>
+        <v>0.15055279500639709</v>
       </c>
       <c r="D105">
-        <v>0.33279256659170559</v>
+        <v>0.30569346829048449</v>
       </c>
       <c r="E105">
-        <v>0.38584920632807729</v>
+        <v>0.38441208840918278</v>
       </c>
       <c r="F105">
-        <v>5.2004518176237448E-2</v>
+        <v>6.2213150850941777E-2</v>
       </c>
       <c r="G105">
-        <v>3.2707376311629108E-2</v>
+        <v>3.4742438376804921E-2</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>3.5093374087195067E-2</v>
+        <v>3.8063738498310337E-2</v>
       </c>
       <c r="B106">
-        <v>2.0571058921572419E-2</v>
+        <v>2.4724238583920581E-2</v>
       </c>
       <c r="C106">
-        <v>0.14185322568849371</v>
+        <v>0.1513528346650713</v>
       </c>
       <c r="D106">
-        <v>0.33305960344707591</v>
+        <v>0.3063961557203852</v>
       </c>
       <c r="E106">
-        <v>0.38455478251540132</v>
+        <v>0.38219681348524998</v>
       </c>
       <c r="F106">
-        <v>5.2077715154662182E-2</v>
+        <v>6.2451224399335481E-2</v>
       </c>
       <c r="G106">
-        <v>3.2790240185594878E-2</v>
+        <v>3.4814994647730073E-2</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>3.5350419315814577E-2</v>
+        <v>3.8407160626202377E-2</v>
       </c>
       <c r="B107">
-        <v>2.0556574804711999E-2</v>
+        <v>2.478132075988532E-2</v>
       </c>
       <c r="C107">
-        <v>0.1424718012083063</v>
+        <v>0.15214169502423949</v>
       </c>
       <c r="D107">
-        <v>0.33340012183237361</v>
+        <v>0.30714806805139322</v>
       </c>
       <c r="E107">
-        <v>0.38320216734287571</v>
+        <v>0.3799527998583655</v>
       </c>
       <c r="F107">
-        <v>5.2146098505530307E-2</v>
+        <v>6.2682039162437836E-2</v>
       </c>
       <c r="G107">
-        <v>3.2872816990394571E-2</v>
+        <v>3.4886916517492018E-2</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>3.5603841554494142E-2</v>
+        <v>3.875244467210219E-2</v>
       </c>
       <c r="B108">
-        <v>2.0542290407587191E-2</v>
+        <v>2.483493790769702E-2</v>
       </c>
       <c r="C108">
-        <v>0.14308507267532919</v>
+        <v>0.15291933129161059</v>
       </c>
       <c r="D108">
-        <v>0.33379916870176068</v>
+        <v>0.30792851623597373</v>
       </c>
       <c r="E108">
-        <v>0.3818044767165264</v>
+        <v>0.37769981719216711</v>
       </c>
       <c r="F108">
-        <v>5.2209737658262388E-2</v>
+        <v>6.2906592434187725E-2</v>
       </c>
       <c r="G108">
-        <v>3.2955412286049791E-2</v>
+        <v>3.4958360266259147E-2</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>3.5853580048841337E-2</v>
+        <v>3.9099139340798159E-2</v>
       </c>
       <c r="B109">
-        <v>2.0528332120706719E-2</v>
+        <v>2.4885296241426848E-2</v>
       </c>
       <c r="C109">
-        <v>0.14369453437863339</v>
+        <v>0.153685649006226</v>
       </c>
       <c r="D109">
-        <v>0.33423964643648041</v>
+        <v>0.30871107604023529</v>
       </c>
       <c r="E109">
-        <v>0.38037691894463799</v>
+        <v>0.37546351441892611</v>
       </c>
       <c r="F109">
-        <v>5.2268684852280083E-2</v>
+        <v>6.3125829962734525E-2</v>
       </c>
       <c r="G109">
-        <v>3.3038303218414049E-2</v>
+        <v>3.5029494989671839E-2</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>3.6099613005506348E-2</v>
+        <v>3.9446703321124647E-2</v>
       </c>
       <c r="B110">
-        <v>2.051486382358898E-2</v>
+        <v>2.493264137423461E-2</v>
       </c>
       <c r="C110">
-        <v>0.1443016674903787</v>
+        <v>0.15444049212495869</v>
       </c>
       <c r="D110">
-        <v>0.33470255047082481</v>
+        <v>0.30946477763251301</v>
       </c>
       <c r="E110">
-        <v>0.37893657104331752</v>
+        <v>0.3732742752800402</v>
       </c>
       <c r="F110">
-        <v>5.232301331683898E-2</v>
+        <v>6.3340617365376065E-2</v>
       </c>
       <c r="G110">
-        <v>3.3121720849546329E-2</v>
+        <v>3.5100492901751962E-2</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>3.6341946584943198E-2</v>
+        <v>3.9794516547733888E-2</v>
       </c>
       <c r="B111">
-        <v>2.0502086401540921E-2</v>
+        <v>2.4977255145956431E-2</v>
       </c>
       <c r="C111">
-        <v>0.1449079017345668</v>
+        <v>0.15518364721806399</v>
       </c>
       <c r="D111">
-        <v>0.33516724379990592</v>
+        <v>0.31015559906507412</v>
       </c>
       <c r="E111">
-        <v>0.37750213058395482</v>
+        <v>0.37116574659283408</v>
       </c>
       <c r="F111">
-        <v>5.2372852632800553E-2</v>
+        <v>6.3551716503759473E-2</v>
       </c>
       <c r="G111">
-        <v>3.3205838262280601E-2</v>
+        <v>3.5171518926591303E-2</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>3.6580602003710411E-2</v>
+        <v>4.0141898170853223E-2</v>
       </c>
       <c r="B112">
-        <v>2.0490234515746799E-2</v>
+        <v>2.5019448033216669E-2</v>
       </c>
       <c r="C112">
-        <v>0.14551456879015809</v>
+        <v>0.15591485841957409</v>
       </c>
       <c r="D112">
-        <v>0.33561180196113699</v>
+        <v>0.31074812929845852</v>
       </c>
       <c r="E112">
-        <v>0.37609361054530738</v>
+        <v>0.36917317523837812</v>
       </c>
       <c r="F112">
-        <v>5.2418417359806048E-2</v>
+        <v>6.3759769768712726E-2</v>
       </c>
       <c r="G112">
-        <v>3.3290764824136211E-2</v>
+        <v>3.5242721070805928E-2</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>3.6815602356277087E-2</v>
+        <v>4.0488129409739497E-2</v>
       </c>
       <c r="B113">
-        <v>2.047957063318542E-2</v>
+        <v>2.5059547402294331E-2</v>
       </c>
       <c r="C113">
-        <v>0.14612284967659889</v>
+        <v>0.1566338469404541</v>
       </c>
       <c r="D113">
-        <v>0.33601345891201317</v>
+        <v>0.31120730509812772</v>
       </c>
       <c r="E113">
-        <v>0.37473194601184728</v>
+        <v>0.36733165576738119</v>
       </c>
       <c r="F113">
-        <v>5.2460025984113652E-2</v>
+        <v>6.3965293675262228E-2</v>
       </c>
       <c r="G113">
-        <v>3.3376546425984643E-2</v>
+        <v>3.5314221706732263E-2</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>3.7046960957064022E-2</v>
+        <v>4.0832479468061109E-2</v>
       </c>
       <c r="B114">
-        <v>2.047037642133382E-2</v>
+        <v>2.509788335575908E-2</v>
       </c>
       <c r="C114">
-        <v>0.14673371956007469</v>
+        <v>0.15734032800242109</v>
       </c>
       <c r="D114">
-        <v>0.33634917698725297</v>
+        <v>0.31150015086302563</v>
       </c>
       <c r="E114">
-        <v>0.373438486518955</v>
+        <v>0.36567436542290582</v>
       </c>
       <c r="F114">
-        <v>5.249810880511515E-2</v>
+        <v>6.4168681872035699E-2</v>
       </c>
       <c r="G114">
-        <v>3.3463170750197058E-2</v>
+        <v>3.538611101579598E-2</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>3.7274672648144651E-2</v>
+        <v>4.1174232214394133E-2</v>
       </c>
       <c r="B115">
-        <v>2.0462941768720041E-2</v>
+        <v>2.5134774086970259E-2</v>
       </c>
       <c r="C115">
-        <v>0.14734789426366171</v>
+        <v>0.15803402220802379</v>
       </c>
       <c r="D115">
-        <v>0.3365963524383106</v>
+        <v>0.31159745515707449</v>
       </c>
       <c r="E115">
-        <v>0.37223435814608868</v>
+        <v>0.36423085917965259</v>
       </c>
       <c r="F115">
-        <v>5.2533204468722623E-2</v>
+        <v>6.4370214779707127E-2</v>
       </c>
       <c r="G115">
-        <v>3.3550576266340178E-2</v>
+        <v>3.5458442374176252E-2</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>3.7498709006836779E-2</v>
+        <v>4.1512712038933662E-2</v>
       </c>
       <c r="B116">
-        <v>2.0457552043414418E-2</v>
+        <v>2.5170512761581939E-2</v>
       </c>
       <c r="C116">
-        <v>0.14796578299948521</v>
+        <v>0.1587146619681285</v>
       </c>
       <c r="D116">
-        <v>0.33673365157324409</v>
+        <v>0.31147530824041192</v>
       </c>
       <c r="E116">
-        <v>0.37113969501066479</v>
+        <v>0.36302550135146361</v>
       </c>
       <c r="F116">
-        <v>5.2565945948654977E-2</v>
+        <v>6.4570072745328486E-2</v>
       </c>
       <c r="G116">
-        <v>3.3638663417710678E-2</v>
+        <v>3.5531230894167078E-2</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>3.7719017878868652E-2</v>
+        <v>4.1847307137454007E-2</v>
       </c>
       <c r="B117">
-        <v>2.0454474659129199E-2</v>
+        <v>2.5205357413602129E-2</v>
       </c>
       <c r="C117">
-        <v>0.14858745151464459</v>
+        <v>0.15938199364477809</v>
       </c>
       <c r="D117">
-        <v>0.3367419521072465</v>
+        <v>0.3111164187340299</v>
       </c>
       <c r="E117">
-        <v>0.37017275971890978</v>
+        <v>0.36207611856571231</v>
       </c>
       <c r="F117">
-        <v>5.2597037713430203E-2</v>
+        <v>6.4768349689016042E-2</v>
       </c>
       <c r="G117">
-        <v>3.3727306407757847E-2</v>
+        <v>3.5604454815400928E-2</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>3.7935527102900962E-2</v>
+        <v>4.2177489245226393E-2</v>
       </c>
       <c r="B118">
-        <v>2.0453946182346399E-2</v>
+        <v>2.5239524162238791E-2</v>
       </c>
       <c r="C118">
-        <v>0.14921259898118541</v>
+        <v>0.16003577944755279</v>
       </c>
       <c r="D118">
-        <v>0.33660534282025878</v>
+        <v>0.310511120095878</v>
       </c>
       <c r="E118">
-        <v>0.36934899413487782</v>
+        <v>0.36139296190411968</v>
       </c>
       <c r="F118">
-        <v>5.2627226500509147E-2</v>
+        <v>6.4965065166531985E-2</v>
       </c>
       <c r="G118">
-        <v>3.3816364277920792E-2</v>
+        <v>3.5678059978441118E-2</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>3.8148151882695491E-2</v>
+        <v>4.2502829137897657E-2</v>
       </c>
       <c r="B119">
-        <v>2.0456161162720709E-2</v>
+        <v>2.527318340124517E-2</v>
       </c>
       <c r="C119">
-        <v>0.14984055061526561</v>
+        <v>0.16067580122356709</v>
       </c>
       <c r="D119">
-        <v>0.33631211512645037</v>
+        <v>0.30965798924265342</v>
       </c>
       <c r="E119">
-        <v>0.36868006225178168</v>
+        <v>0.36097805558638041</v>
       </c>
       <c r="F119">
-        <v>5.2657268565175601E-2</v>
+        <v>6.5160174823394174E-2</v>
       </c>
       <c r="G119">
-        <v>3.3905690395912777E-2</v>
+        <v>3.5751966584863792E-2</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>3.8356804899441287E-2</v>
+        <v>4.2823007538555322E-2</v>
       </c>
       <c r="B120">
-        <v>2.0461263518784509E-2</v>
+        <v>2.5306458091866942E-2</v>
       </c>
       <c r="C120">
-        <v>0.15047026652840209</v>
+        <v>0.16130186841052291</v>
       </c>
       <c r="D120">
-        <v>0.33585566739119621</v>
+        <v>0.30856402229281832</v>
       </c>
       <c r="E120">
-        <v>0.36817296148688428</v>
+        <v>0.36082498642505151</v>
       </c>
       <c r="F120">
-        <v>5.268789633805411E-2</v>
+        <v>6.5353579358682704E-2</v>
       </c>
       <c r="G120">
-        <v>3.3995139837231923E-2</v>
+        <v>3.5826077882511582E-2</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>3.8561408056440843E-2</v>
+        <v>4.3137821370705182E-2</v>
       </c>
       <c r="B121">
-        <v>2.0469340842479779E-2</v>
+        <v>2.533942349542033E-2</v>
       </c>
       <c r="C121">
-        <v>0.15110036586013781</v>
+        <v>0.16191383116550229</v>
       </c>
       <c r="D121">
-        <v>0.33523523957935192</v>
+        <v>0.3072443511962959</v>
       </c>
       <c r="E121">
-        <v>0.3678292838057271</v>
+        <v>0.36091914985896972</v>
       </c>
       <c r="F121">
-        <v>5.2719787264762653E-2</v>
+        <v>6.5545132522645988E-2</v>
       </c>
       <c r="G121">
-        <v>3.408457459108985E-2</v>
+        <v>3.5900290390473211E-2</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>3.8761904714310152E-2</v>
+        <v>4.3447185107927729E-2</v>
       </c>
       <c r="B122">
-        <v>2.0480421528392939E-2</v>
+        <v>2.537210819697178E-2</v>
       </c>
       <c r="C122">
-        <v>0.15172916421673671</v>
+        <v>0.16251159758169731</v>
       </c>
       <c r="D122">
-        <v>0.33445640326297399</v>
+        <v>0.30572153174866168</v>
       </c>
       <c r="E122">
-        <v>0.36764470225499951</v>
+        <v>0.36123842438336418</v>
       </c>
       <c r="F122">
-        <v>5.275353721789372E-2</v>
+        <v>6.5734648231749265E-2</v>
       </c>
       <c r="G122">
-        <v>3.4173866804709491E-2</v>
+        <v>3.5974504749624561E-2</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>3.8958271335124389E-2</v>
+        <v>4.3751127165118163E-2</v>
       </c>
       <c r="B123">
-        <v>2.0494474275860659E-2</v>
+        <v>2.5404496652559231E-2</v>
       </c>
       <c r="C123">
-        <v>0.15235472189794119</v>
+        <v>0.1630951529154695</v>
       </c>
       <c r="D123">
-        <v>0.3335312496151569</v>
+        <v>0.30402447841734842</v>
       </c>
       <c r="E123">
-        <v>0.36760874236817448</v>
+        <v>0.36175420234915051</v>
       </c>
       <c r="F123">
-        <v>5.2789640241864458E-2</v>
+        <v>6.5921906102264338E-2</v>
       </c>
       <c r="G123">
-        <v>3.4262900265875362E-2</v>
+        <v>3.6048636398087072E-2</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>3.9150527622189811E-2</v>
+        <v>4.4049781667894181E-2</v>
       </c>
       <c r="B124">
-        <v>2.051140939036248E-2</v>
+        <v>2.5436533715579562E-2</v>
       </c>
       <c r="C124">
-        <v>0.15297490025343879</v>
+        <v>0.1636645772553284</v>
       </c>
       <c r="D124">
-        <v>0.33247824278345539</v>
+        <v>0.30218715477319419</v>
       </c>
       <c r="E124">
-        <v>0.36770487401319718</v>
+        <v>0.36243267269353219</v>
       </c>
       <c r="F124">
-        <v>5.2828475533700563E-2</v>
+        <v>6.6106654864983391E-2</v>
       </c>
       <c r="G124">
-        <v>3.4351570403648453E-2</v>
+        <v>3.6122625029491318E-2</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>3.9338744386692923E-2</v>
+        <v>4.4343376316427832E-2</v>
       </c>
       <c r="B125">
-        <v>2.053108131565928E-2</v>
+        <v>2.5468131394784769E-2</v>
       </c>
       <c r="C125">
-        <v>0.15358742339489101</v>
+        <v>0.1642200575096997</v>
       </c>
       <c r="D125">
-        <v>0.33132173464998033</v>
+        <v>0.30024714223148291</v>
       </c>
       <c r="E125">
-        <v>0.36791093170422562</v>
+        <v>0.36323623700723739</v>
       </c>
       <c r="F125">
-        <v>5.287030154405388E-2</v>
+        <v>6.6288613528344073E-2</v>
       </c>
       <c r="G125">
-        <v>3.4439783004492283E-2</v>
+        <v>3.6196442012043341E-2</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>3.9523048625653763E-2</v>
+        <v>4.4632217554817173E-2</v>
       </c>
       <c r="B126">
-        <v>2.0553292096282979E-2</v>
+        <v>2.549917755865751E-2</v>
       </c>
       <c r="C126">
-        <v>0.15418994252040399</v>
+        <v>0.16476189137476191</v>
       </c>
       <c r="D126">
-        <v>0.33009116528711729</v>
+        <v>0.29824420082112368</v>
       </c>
       <c r="E126">
-        <v>0.36819984335416001</v>
+        <v>0.36412494756228919</v>
       </c>
       <c r="F126">
-        <v>5.2915255919228188E-2</v>
+        <v>6.6467470359216504E-2</v>
       </c>
       <c r="G126">
-        <v>3.4527452197154612E-2</v>
+        <v>3.6270094769141649E-2</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>3.9703625610568699E-2</v>
+        <v>4.4916674125247122E-2</v>
       </c>
       <c r="B127">
-        <v>2.0577795824783449E-2</v>
+        <v>2.5529546104978849E-2</v>
       </c>
       <c r="C127">
-        <v>0.15478010068608941</v>
+        <v>0.1652904818466982</v>
       </c>
       <c r="D127">
-        <v>0.32881999780282128</v>
+        <v>0.29621890821676727</v>
       </c>
       <c r="E127">
-        <v>0.36854062210729849</v>
+        <v>0.36505788028448211</v>
       </c>
       <c r="F127">
-        <v>5.2963359691429117E-2</v>
+        <v>6.6642881178228155E-2</v>
       </c>
       <c r="G127">
-        <v>3.4614498277021663E-2</v>
+        <v>3.6343628243600642E-2</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>3.9880717937768713E-2</v>
+        <v>4.5197160236372623E-2</v>
       </c>
       <c r="B128">
-        <v>2.0604304309249141E-2</v>
+        <v>2.5559107800295071E-2</v>
       </c>
       <c r="C128">
-        <v>0.15535559595652329</v>
+        <v>0.16580632404746809</v>
       </c>
       <c r="D128">
-        <v>0.32754445399605048</v>
+        <v>0.2942114263941194</v>
       </c>
       <c r="E128">
-        <v>0.36889955739934321</v>
+        <v>0.36599439009757329</v>
       </c>
       <c r="F128">
-        <v>5.3014524793227748E-2</v>
+        <v>6.6814468090797052E-2</v>
       </c>
       <c r="G128">
-        <v>3.4700845607846698E-2</v>
+        <v>3.6417123333372478E-2</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>4.0054621526725211E-2</v>
+        <v>4.5474119056547253E-2</v>
       </c>
       <c r="B129">
-        <v>2.06324942038601E-2</v>
+        <v>2.5587741047575462E-2</v>
       </c>
       <c r="C129">
-        <v>0.15591424087106021</v>
+        <v>0.16630998741406511</v>
       </c>
       <c r="D129">
-        <v>0.32630212773050038</v>
+        <v>0.29226041151974602</v>
       </c>
       <c r="E129">
-        <v>0.36924153132857251</v>
+        <v>0.36689522809354208</v>
       </c>
       <c r="F129">
-        <v>5.3068563833433911E-2</v>
+        <v>6.6981820072493314E-2</v>
       </c>
       <c r="G129">
-        <v>3.4786420505856487E-2</v>
+        <v>3.6490692796024751E-2</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>4.0225678729721423E-2</v>
+        <v>4.5748007131928753E-2</v>
       </c>
       <c r="B130">
-        <v>2.0662015778549109E-2</v>
+        <v>2.5615341938075992E-2</v>
       </c>
       <c r="C130">
-        <v>0.15645401637159101</v>
+        <v>0.16680209662866591</v>
       </c>
       <c r="D130">
-        <v>0.32513055519397771</v>
+        <v>0.29040206077196318</v>
       </c>
       <c r="E130">
-        <v>0.36953138376091588</v>
+        <v>0.3677235216754326</v>
       </c>
       <c r="F130">
-        <v>5.312520100385857E-2</v>
+        <v>6.7144496677579324E-2</v>
       </c>
       <c r="G130">
-        <v>3.4871149161380947E-2</v>
+        <v>3.6564475176353292E-2</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>4.0394268829351272E-2</v>
+        <v>4.6019280123065519E-2</v>
       </c>
       <c r="B131">
-        <v>2.069250328512821E-2</v>
+        <v>2.5641832928261821E-2</v>
       </c>
       <c r="C131">
-        <v>0.15697311876337419</v>
+        <v>0.16728331460440199</v>
       </c>
       <c r="D131">
-        <v>0.32406581617565522</v>
+        <v>0.28866928282093568</v>
       </c>
       <c r="E131">
-        <v>0.3697352539592107</v>
+        <v>0.36844562697169558</v>
       </c>
       <c r="F131">
-        <v>5.3184083242532827E-2</v>
+        <v>6.7302035278848774E-2</v>
       </c>
       <c r="G131">
-        <v>3.4954955744746448E-2</v>
+        <v>3.6638627272789492E-2</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>4.0560796385518939E-2</v>
+        <v>4.6288380170174503E-2</v>
       </c>
       <c r="B132">
-        <v>2.072358667751973E-2</v>
+        <v>2.5667169773333869E-2</v>
       </c>
       <c r="C132">
-        <v>0.15746999856678309</v>
+        <v>0.1677543293808034</v>
       </c>
       <c r="D132">
-        <v>0.32314123007966772</v>
+        <v>0.28709098404994837</v>
       </c>
       <c r="E132">
-        <v>0.36982183630645299</v>
+        <v>0.36903185907147362</v>
       </c>
       <c r="F132">
-        <v>5.3244791085811663E-2</v>
+        <v>6.7453962040913001E-2</v>
       </c>
       <c r="G132">
-        <v>3.50377608982545E-2</v>
+        <v>3.6713315513356597E-2</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>4.0725678077508112E-2</v>
+        <v>4.655572514365474E-2</v>
       </c>
       <c r="B133">
-        <v>2.0754904288337459E-2</v>
+        <v>2.5691346489717829E-2</v>
       </c>
       <c r="C133">
-        <v>0.15794339027780571</v>
+        <v>0.1682158459900634</v>
       </c>
       <c r="D133">
-        <v>0.32238619684833408</v>
+        <v>0.28569147313568338</v>
       </c>
       <c r="E133">
-        <v>0.36976350052400259</v>
+        <v>0.36945709608860788</v>
       </c>
       <c r="F133">
-        <v>5.3306849154598782E-2</v>
+        <v>6.7599806215813615E-2</v>
       </c>
       <c r="G133">
-        <v>3.511948082941211E-2</v>
+        <v>3.678870693645888E-2</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>4.0889328811456682E-2</v>
+        <v>4.6821700036378519E-2</v>
       </c>
       <c r="B134">
-        <v>2.0786116021586701E-2</v>
+        <v>2.5714398360195241E-2</v>
       </c>
       <c r="C134">
-        <v>0.15839233221666821</v>
+        <v>0.1686685832589721</v>
       </c>
       <c r="D134">
-        <v>0.32182521870458147</v>
+        <v>0.2844899974961812</v>
       </c>
       <c r="E134">
-        <v>0.36953724082499528</v>
+        <v>0.36970124417462158</v>
       </c>
       <c r="F134">
-        <v>5.3369736260416453E-2</v>
+        <v>6.7739116716546199E-2</v>
       </c>
       <c r="G134">
-        <v>3.520002716029319E-2</v>
+        <v>3.6864959957110303E-2</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>4.1052147952063613E-2</v>
+        <v>4.7086650672309383E-2</v>
       </c>
       <c r="B135">
-        <v>2.081691654997412E-2</v>
+        <v>2.573640314154698E-2</v>
       </c>
       <c r="C135">
-        <v>0.15881617603669571</v>
+        <v>0.16911327518657809</v>
       </c>
       <c r="D135">
-        <v>0.32147712521281308</v>
+        <v>0.2835004306365182</v>
       </c>
       <c r="E135">
-        <v>0.36912543105529783</v>
+        <v>0.36974954525400711</v>
       </c>
       <c r="F135">
-        <v>5.3432895437094889E-2</v>
+        <v>6.7871479742788246E-2</v>
       </c>
       <c r="G135">
-        <v>3.527930775605178E-2</v>
+        <v>3.6942215366252973E-2</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>4.1214506482702758E-2</v>
+        <v>4.735087972785082E-2</v>
       </c>
       <c r="B136">
-        <v>2.084704780687582E-2</v>
+        <v>2.5757480834026101E-2</v>
       </c>
       <c r="C136">
-        <v>0.1592145862166518</v>
+        <v>0.1695506757980042</v>
       </c>
       <c r="D136">
-        <v>0.32135451360720119</v>
+        <v>0.28273112895421448</v>
       </c>
       <c r="E136">
-        <v>0.36851637317143099</v>
+        <v>0.36959271050727471</v>
       </c>
       <c r="F136">
-        <v>5.349574417804355E-2</v>
+        <v>6.7996536199607938E-2</v>
       </c>
       <c r="G136">
-        <v>3.5357228537086408E-2</v>
+        <v>3.7020587979014308E-2</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>4.1376735846727158E-2</v>
+        <v>4.7614645056382507E-2</v>
       </c>
       <c r="B137">
-        <v>2.087630981631745E-2</v>
+        <v>2.5777792343909839E-2</v>
       </c>
       <c r="C137">
-        <v>0.15958753071925469</v>
+        <v>0.16998156623041241</v>
       </c>
       <c r="D137">
-        <v>0.32146340889999259</v>
+        <v>0.28218496917624952</v>
       </c>
       <c r="E137">
-        <v>0.36770463318103153</v>
+        <v>0.36922687013241973</v>
       </c>
       <c r="F137">
-        <v>5.3557685284344042E-2</v>
+        <v>6.8113997572924745E-2</v>
       </c>
       <c r="G137">
-        <v>3.543369625233251E-2</v>
+        <v>3.7100159487711552E-2</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>4.1539119095484092E-2</v>
+        <v>4.7878160137097593E-2</v>
       </c>
       <c r="B138">
-        <v>2.090456880527972E-2</v>
+        <v>2.579753742861042E-2</v>
       </c>
       <c r="C138">
-        <v>0.15993526482982989</v>
+        <v>0.17040676223447271</v>
       </c>
       <c r="D138">
-        <v>0.32180314423586898</v>
+        <v>0.28185956553187741</v>
       </c>
       <c r="E138">
-        <v>0.36669116240899402</v>
+        <v>0.36865334244770348</v>
       </c>
       <c r="F138">
-        <v>5.3618118525048282E-2</v>
+        <v>6.8223659282879726E-2</v>
       </c>
       <c r="G138">
-        <v>3.5508622099516218E-2</v>
+        <v>3.7180972937350537E-2</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>4.1701884797486558E-2</v>
+        <v>4.8141596370752167E-2</v>
       </c>
       <c r="B139">
-        <v>2.0931761642274289E-2</v>
+        <v>2.581695205495985E-2</v>
       </c>
       <c r="C139">
-        <v>0.16025831064861731</v>
+        <v>0.17082712014830381</v>
       </c>
       <c r="D139">
-        <v>0.32236645982391238</v>
+        <v>0.28174765144100988</v>
       </c>
       <c r="E139">
-        <v>0.3654832039058804</v>
+        <v>0.36787824020611271</v>
       </c>
       <c r="F139">
-        <v>5.3676453249372313E-2</v>
+        <v>6.8325410719005594E-2</v>
       </c>
       <c r="G139">
-        <v>3.5581925932467083E-2</v>
+        <v>3.7263029059856401E-2</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>4.1865203969026092E-2</v>
+        <v>4.8405086899670768E-2</v>
       </c>
       <c r="B140">
-        <v>2.0957895989218319E-2</v>
+        <v>2.5836305127054478E-2</v>
       </c>
       <c r="C140">
-        <v>0.16055743482010401</v>
+        <v>0.1712435392191537</v>
       </c>
       <c r="D140">
-        <v>0.32313981697997068</v>
+        <v>0.28183759667264419</v>
       </c>
       <c r="E140">
-        <v>0.36409398570364537</v>
+        <v>0.36691194563946578</v>
       </c>
       <c r="F140">
-        <v>5.3732121884426658E-2</v>
+        <v>6.8419241547209145E-2</v>
       </c>
       <c r="G140">
-        <v>3.5653540653615673E-2</v>
+        <v>3.7346284894805071E-2</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>4.2029190085868577E-2</v>
+        <v>4.8668731549698828E-2</v>
       </c>
       <c r="B141">
-        <v>2.0983045979929608E-2</v>
+        <v>2.585589429430871E-2</v>
       </c>
       <c r="C141">
-        <v>0.16083362656026759</v>
+        <v>0.17165695864878411</v>
       </c>
       <c r="D141">
-        <v>0.32410392052803733</v>
+        <v>0.2821140211419364</v>
       </c>
       <c r="E141">
-        <v>0.36254220634558032</v>
+        <v>0.36576849573958842</v>
       </c>
       <c r="F141">
-        <v>5.3784594217290732E-2</v>
+        <v>6.850524416461734E-2</v>
       </c>
       <c r="G141">
-        <v>3.5723416283026208E-2</v>
+        <v>3.7430654461072493E-2</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>4.2193902022252823E-2</v>
+        <v>4.8932602362685193E-2</v>
       </c>
       <c r="B142">
-        <v>2.1007343713320411E-2</v>
+        <v>2.5876040459140329E-2</v>
       </c>
       <c r="C142">
-        <v>0.1610880772521775</v>
+        <v>0.17206834784090599</v>
       </c>
       <c r="D142">
-        <v>0.32523443702651328</v>
+        <v>0.28255846276044888</v>
       </c>
       <c r="E142">
-        <v>0.36085132472796472</v>
+        <v>0.36446492236982547</v>
       </c>
       <c r="F142">
-        <v>5.3833392051905168E-2</v>
+        <v>6.8583612705692035E-2</v>
       </c>
       <c r="G142">
-        <v>3.579152320586864E-2</v>
+        <v>3.7516011501296492E-2</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>4.2359349560716818E-2</v>
+        <v>4.9196749312307143E-2</v>
       </c>
       <c r="B143">
-        <v>2.103096726145889E-2</v>
+        <v>2.5897080566468049E-2</v>
       </c>
       <c r="C143">
-        <v>0.1613221620728342</v>
+        <v>0.17247868987910281</v>
       </c>
       <c r="D143">
-        <v>0.32650288760275059</v>
+        <v>0.28315006016691779</v>
       </c>
       <c r="E143">
-        <v>0.35904867562960557</v>
+        <v>0.36302058738999432</v>
       </c>
       <c r="F143">
-        <v>5.3878103694039198E-2</v>
+        <v>6.8654638873053925E-2</v>
       </c>
       <c r="G143">
-        <v>3.5857854178594217E-2</v>
+        <v>3.7602193812167152E-2</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>4.2525500958728417E-2</v>
+        <v>4.9461205595199981E-2</v>
       </c>
       <c r="B144">
-        <v>2.1054126239579429E-2</v>
+        <v>2.5919358430594539E-2</v>
       </c>
       <c r="C144">
-        <v>0.16153742336224791</v>
+        <v>0.1728889583914682</v>
       </c>
       <c r="D144">
-        <v>0.32787768376156351</v>
+        <v>0.28386622087781099</v>
       </c>
       <c r="E144">
-        <v>0.35716444333859648</v>
+        <v>0.36145654244883019</v>
       </c>
       <c r="F144">
-        <v>5.3918397495281059E-2</v>
+        <v>6.8718705395740182E-2</v>
       </c>
       <c r="G144">
-        <v>3.5922424843994667E-2</v>
+        <v>3.7689008860362513E-2</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>4.2692291931358192E-2</v>
+        <v>4.972599218579498E-2</v>
       </c>
       <c r="B145">
-        <v>2.107704616046464E-2</v>
+        <v>2.5943213572622741E-2</v>
       </c>
       <c r="C145">
-        <v>0.16173555491006539</v>
+        <v>0.1733000893484237</v>
       </c>
       <c r="D145">
-        <v>0.32932526402842061</v>
+        <v>0.28468325805223882</v>
       </c>
       <c r="E145">
-        <v>0.3552305369394399</v>
+        <v>0.35979492947936209</v>
       </c>
       <c r="F145">
-        <v>5.3954033501603493E-2</v>
+        <v>6.877627742673513E-2</v>
       </c>
       <c r="G145">
-        <v>3.5985272528648783E-2</v>
+        <v>3.7776239934819378E-2</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>4.285963536037863E-2</v>
+        <v>4.9991121482148952E-2</v>
       </c>
       <c r="B146">
-        <v>2.1099952813538849E-2</v>
+        <v>2.5968968428948361E-2</v>
       </c>
       <c r="C146">
-        <v>0.1619183860552996</v>
+        <v>0.17371294929178729</v>
       </c>
       <c r="D146">
-        <v>0.33081128032870838</v>
+        <v>0.28557699094754901</v>
       </c>
       <c r="E146">
-        <v>0.35327941988874129</v>
+        <v>0.35805842484420919</v>
       </c>
       <c r="F146">
-        <v>5.3984872263066128E-2</v>
+        <v>6.8827892433627774E-2</v>
       </c>
       <c r="G146">
-        <v>3.6046453290274408E-2</v>
+        <v>3.7863652571719128E-2</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>4.3027431074172312E-2</v>
+        <v>5.0256600155581199E-2</v>
       </c>
       <c r="B147">
-        <v>2.1123057782148229E-2</v>
+        <v>2.5996914612514379E-2</v>
       </c>
       <c r="C147">
-        <v>0.16208786444791701</v>
+        <v>0.17412830170195859</v>
       </c>
       <c r="D147">
-        <v>0.33230177755339108</v>
+        <v>0.28652331215267918</v>
       </c>
       <c r="E147">
-        <v>0.35134295182886133</v>
+        <v>0.35626972229192772</v>
       </c>
       <c r="F147">
-        <v>5.4010879958961248E-2</v>
+        <v>6.8874148524273607E-2</v>
       </c>
       <c r="G147">
-        <v>3.6106037354543499E-2</v>
+        <v>3.7951000561075143E-2</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>4.3195575143412143E-2</v>
+        <v>5.0522431407548578E-2</v>
       </c>
       <c r="B148">
-        <v>2.114654600494421E-2</v>
+        <v>2.6027299281728439E-2</v>
       </c>
       <c r="C148">
-        <v>0.16224603648948599</v>
+        <v>0.17454677286323569</v>
       </c>
       <c r="D148">
-        <v>0.33376430869589568</v>
+        <v>0.28749872707931923</v>
       </c>
       <c r="E148">
-        <v>0.34945130130060498</v>
+        <v>0.35445104638556518</v>
       </c>
       <c r="F148">
-        <v>5.4032129129939439E-2</v>
+        <v>6.8915691514943395E-2</v>
       </c>
       <c r="G148">
-        <v>3.6164103235712543E-2</v>
+        <v>3.8038031467661687E-2</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149">
-        <v>4.3363968263350101E-2</v>
+        <v>5.0788616819779378E-2</v>
       </c>
       <c r="B149">
-        <v>2.117056598229634E-2</v>
+        <v>2.6060312741203701E-2</v>
       </c>
       <c r="C149">
-        <v>0.1623950247035385</v>
+        <v>0.17496881849741211</v>
       </c>
       <c r="D149">
-        <v>0.33516893157840388</v>
+        <v>0.28848086865951489</v>
       </c>
       <c r="E149">
-        <v>0.34763198361744208</v>
+        <v>0.35262369129865168</v>
       </c>
       <c r="F149">
-        <v>5.4048794796507219E-2</v>
+        <v>6.8953200675053353E-2</v>
       </c>
       <c r="G149">
-        <v>3.6220731058453137E-2</v>
+        <v>3.8124491308391538E-2</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150">
-        <v>4.3532522919218421E-2</v>
+        <v>5.105515797870426E-2</v>
       </c>
       <c r="B150">
-        <v>2.1195222944304919E-2</v>
+        <v>2.6096078418327489E-2</v>
       </c>
       <c r="C150">
-        <v>0.16253700161121271</v>
+        <v>0.175394692467813</v>
       </c>
       <c r="D150">
-        <v>0.33648904129482798</v>
+        <v>0.28944898383057999</v>
       </c>
       <c r="E150">
-        <v>0.34590906950442418</v>
+        <v>0.35080758572727</v>
       </c>
       <c r="F150">
-        <v>5.4061146042803931E-2</v>
+        <v>6.8987373303988492E-2</v>
       </c>
       <c r="G150">
-        <v>3.6275995683215448E-2</v>
+        <v>3.8210128273316581E-2</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>4.3701169136224308E-2</v>
+        <v>5.1322058003493112E-2</v>
       </c>
       <c r="B151">
-        <v>2.122057500531874E-2</v>
+        <v>2.6134646108723882E-2</v>
       </c>
       <c r="C151">
-        <v>0.16267415996223011</v>
+        <v>0.17582441949360819</v>
       </c>
       <c r="D151">
-        <v>0.33770200387168797</v>
+        <v>0.2903843807257549</v>
       </c>
       <c r="E151">
-        <v>0.34430259801903429</v>
+        <v>0.3490208913887885</v>
       </c>
       <c r="F151">
-        <v>5.4069533651841313E-2</v>
+        <v>6.9018908429792553E-2</v>
       </c>
       <c r="G151">
-        <v>3.6329960353659978E-2</v>
+        <v>3.8294695849848258E-2</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152">
-        <v>4.3869858752182238E-2</v>
+        <v>5.1589323074189827E-2</v>
       </c>
       <c r="B152">
-        <v>2.1246632138328871E-2</v>
+        <v>2.6175989042254291E-2</v>
       </c>
       <c r="C152">
-        <v>0.16280867946728869</v>
+        <v>0.17625777411439189</v>
       </c>
       <c r="D152">
-        <v>0.33878957013759198</v>
+        <v>0.29127081906863461</v>
       </c>
       <c r="E152">
-        <v>0.34282821347553571</v>
+        <v>0.34727964940928602</v>
       </c>
       <c r="F152">
-        <v>5.4074374562427252E-2</v>
+        <v>6.904849010376593E-2</v>
       </c>
       <c r="G152">
-        <v>3.6382671466640863E-2</v>
+        <v>3.8377955187472133E-2</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153">
-        <v>4.4038568295813409E-2</v>
+        <v>5.185696396484471E-2</v>
       </c>
       <c r="B153">
-        <v>2.127335765553855E-2</v>
+        <v>2.6220004978498211E-2</v>
       </c>
       <c r="C153">
-        <v>0.16294269050904819</v>
+        <v>0.17669426878744729</v>
       </c>
       <c r="D153">
-        <v>0.33973806283877928</v>
+        <v>0.29209482232220568</v>
       </c>
       <c r="E153">
-        <v>0.34149703145415933</v>
+        <v>0.34559749186628907</v>
       </c>
       <c r="F153">
-        <v>5.4076134203942527E-2</v>
+        <v>6.9076771092809824E-2</v>
       </c>
       <c r="G153">
-        <v>3.643415504270292E-2</v>
+        <v>3.8459676987909773E-2</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154">
-        <v>4.420730066806336E-2</v>
+        <v>5.2124997459712559E-2</v>
       </c>
       <c r="B154">
-        <v>2.1300671821196559E-2</v>
+        <v>2.626652112392696E-2</v>
       </c>
       <c r="C154">
-        <v>0.16307823568852919</v>
+        <v>0.17713315368556909</v>
       </c>
       <c r="D154">
-        <v>0.34053834357185708</v>
+        <v>0.29284589005005368</v>
       </c>
       <c r="E154">
-        <v>0.34031572526755288</v>
+        <v>0.34398543651248342</v>
       </c>
       <c r="F154">
-        <v>5.4075307766939987E-2</v>
+        <v>6.9104357964468843E-2</v>
       </c>
       <c r="G154">
-        <v>3.6484415215866699E-2</v>
+        <v>3.8539643203777819E-2</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155">
-        <v>4.4376085782232767E-2</v>
+        <v>5.2393447496488818E-2</v>
       </c>
       <c r="B155">
-        <v>2.132845721878238E-2</v>
+        <v>2.631530238122988E-2</v>
       </c>
       <c r="C155">
-        <v>0.16321723039568031</v>
+        <v>0.17757343020432939</v>
       </c>
       <c r="D155">
-        <v>0.34118557816538042</v>
+        <v>0.29351659282794468</v>
       </c>
       <c r="E155">
-        <v>0.33928681204412148</v>
+        <v>0.34245177994454368</v>
       </c>
       <c r="F155">
-        <v>5.4072401470098112E-2</v>
+        <v>6.9131798581378578E-2</v>
       </c>
       <c r="G155">
-        <v>3.653343492368992E-2</v>
+        <v>3.861764856408726E-2</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156">
-        <v>4.4544980090826559E-2</v>
+        <v>5.2662345798034103E-2</v>
       </c>
       <c r="B156">
-        <v>2.135656551732263E-2</v>
+        <v>2.6366062196345279E-2</v>
       </c>
       <c r="C156">
-        <v>0.1633614238126031</v>
+        <v>0.17801387915000169</v>
       </c>
       <c r="D156">
-        <v>0.34167882934944538</v>
+        <v>0.29410253902080119</v>
       </c>
       <c r="E156">
-        <v>0.33840910771429789</v>
+        <v>0.34100209883916172</v>
       </c>
       <c r="F156">
-        <v>5.4067914826247447E-2</v>
+        <v>6.9159572827036275E-2</v>
       </c>
       <c r="G156">
-        <v>3.6581178689240913E-2</v>
+        <v>3.8693502168624591E-2</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157">
-        <v>4.4714064718934902E-2</v>
+        <v>5.2931731684447432E-2</v>
       </c>
       <c r="B157">
-        <v>2.1384825257582288E-2</v>
+        <v>2.6418475341095659E-2</v>
       </c>
       <c r="C157">
-        <v>0.16351236202863531</v>
+        <v>0.17845310353935331</v>
       </c>
       <c r="D157">
-        <v>0.34202051348949092</v>
+        <v>0.29460221145250698</v>
       </c>
       <c r="E157">
-        <v>0.33767831245158691</v>
+        <v>0.3396393616661425</v>
       </c>
       <c r="F157">
-        <v>5.4062324826727938E-2</v>
+        <v>6.918808719710122E-2</v>
       </c>
       <c r="G157">
-        <v>3.662759722704121E-2</v>
+        <v>3.8767029119359281E-2</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158">
-        <v>4.4883441965985871E-2</v>
+        <v>5.3201651240680568E-2</v>
       </c>
       <c r="B158">
-        <v>2.141305004880148E-2</v>
+        <v>2.6472191855420681E-2</v>
       </c>
       <c r="C158">
-        <v>0.1636713551825543</v>
+        <v>0.1788895843176749</v>
       </c>
       <c r="D158">
-        <v>0.34221576376630009</v>
+        <v>0.2950166815018006</v>
       </c>
       <c r="E158">
-        <v>0.33708768285163893</v>
+        <v>0.33836414549945459</v>
       </c>
       <c r="F158">
-        <v>5.4056072823364353E-2</v>
+        <v>6.9217673162066951E-2</v>
       </c>
       <c r="G158">
-        <v>3.6672633361358391E-2</v>
+        <v>3.8838072422913927E-2</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159">
-        <v>4.5053230283653822E-2</v>
+        <v>5.3472155285041803E-2</v>
       </c>
       <c r="B159">
-        <v>2.1441046477379301E-2</v>
+        <v>2.652685144418963E-2</v>
       </c>
       <c r="C159">
-        <v>0.1638394502803695</v>
+        <v>0.17932174584557201</v>
       </c>
       <c r="D159">
-        <v>0.34227174496741808</v>
+        <v>0.29534921742750808</v>
       </c>
       <c r="E159">
-        <v>0.33662874482745758</v>
+        <v>0.33717494569264472</v>
       </c>
       <c r="F159">
-        <v>5.404955447029787E-2</v>
+        <v>6.9248589121435555E-2</v>
       </c>
       <c r="G159">
-        <v>3.6716228693415273E-2</v>
+        <v>3.8906495183621367E-2</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160">
-        <v>4.5223558225146752E-2</v>
+        <v>5.3743296539322777E-2</v>
       </c>
       <c r="B160">
-        <v>2.1468621262225259E-2</v>
+        <v>2.6582097565106669E-2</v>
       </c>
       <c r="C160">
-        <v>0.16401741060876621</v>
+        <v>0.17974802665417181</v>
       </c>
       <c r="D160">
-        <v>0.34219696494305102</v>
+        <v>0.29560481110942749</v>
       </c>
       <c r="E160">
-        <v>0.33629200170565687</v>
+        <v>0.33606855992920909</v>
       </c>
       <c r="F160">
-        <v>5.4043112876189368E-2</v>
+        <v>6.9281025171329086E-2</v>
       </c>
       <c r="G160">
-        <v>3.6758330378959349E-2</v>
+        <v>3.8972183031438637E-2</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161">
-        <v>4.5394558001846858E-2</v>
+        <v>5.4015125799995158E-2</v>
       </c>
       <c r="B161">
-        <v>2.1495587611573171E-2</v>
+        <v>2.6637590651216941E-2</v>
       </c>
       <c r="C161">
-        <v>0.16420570192458769</v>
+        <v>0.18016695041511521</v>
       </c>
       <c r="D161">
-        <v>0.34200062539246689</v>
+        <v>0.29578965234242338</v>
       </c>
       <c r="E161">
-        <v>0.33606759478954762</v>
+        <v>0.33504052419655422</v>
       </c>
       <c r="F161">
-        <v>5.4037034932018113E-2</v>
+        <v>6.9315109930069854E-2</v>
       </c>
       <c r="G161">
-        <v>3.6798897347953871E-2</v>
+        <v>3.9035046664622187E-2</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162">
-        <v>4.5566359100891331E-2</v>
+        <v>5.428768760414332E-2</v>
       </c>
       <c r="B162">
-        <v>2.1521770891221471E-2</v>
+        <v>2.6693019911088751E-2</v>
       </c>
       <c r="C162">
-        <v>0.16440448535518931</v>
+        <v>0.18057719167754971</v>
       </c>
       <c r="D162">
-        <v>0.34169204985401452</v>
+        <v>0.29591058210481042</v>
       </c>
       <c r="E162">
-        <v>0.33594587876207932</v>
+        <v>0.33408557566441138</v>
       </c>
       <c r="F162">
-        <v>5.4031550673464122E-2</v>
+        <v>6.9350918499098579E-2</v>
       </c>
       <c r="G162">
-        <v>3.6837905363161602E-2</v>
+        <v>3.9095024538899882E-2</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163">
-        <v>4.5739082199269913E-2</v>
+        <v>5.4561015453034448E-2</v>
       </c>
       <c r="B163">
-        <v>2.1547013612160441E-2</v>
+        <v>2.674811314883804E-2</v>
       </c>
       <c r="C163">
-        <v>0.1646136172053026</v>
+        <v>0.1809776316675637</v>
       </c>
       <c r="D163">
-        <v>0.34128021987284313</v>
+        <v>0.29597455642565101</v>
       </c>
       <c r="E163">
-        <v>0.33591788128703898</v>
+        <v>0.33319811782043829</v>
       </c>
       <c r="F163">
-        <v>5.4026835409598642E-2</v>
+        <v>6.9388480547626363E-2</v>
       </c>
       <c r="G163">
-        <v>3.6875350413790808E-2</v>
+        <v>3.9152084936844918E-2</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164">
-        <v>4.5912833532484709E-2</v>
+        <v>5.4835127311425362E-2</v>
       </c>
       <c r="B164">
-        <v>2.1571179645895971E-2</v>
+        <v>2.6802644258105419E-2</v>
       </c>
       <c r="C164">
-        <v>0.1648326560951803</v>
+        <v>0.1813673999360296</v>
       </c>
       <c r="D164">
-        <v>0.34077344132856979</v>
+        <v>0.29598814984375899</v>
       </c>
       <c r="E164">
-        <v>0.33597562491294652</v>
+        <v>0.33237266316715952</v>
       </c>
       <c r="F164">
-        <v>5.4023014236331407E-2</v>
+        <v>6.9427787897114082E-2</v>
       </c>
       <c r="G164">
-        <v>3.6911250248595477E-2</v>
+        <v>3.9206227586410639E-2</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165">
-        <v>4.608769989289907E-2</v>
+        <v>5.511002129597109E-2</v>
       </c>
       <c r="B165">
-        <v>2.1594157557974392E-2</v>
+        <v>2.6856438073909E-2</v>
       </c>
       <c r="C165">
-        <v>0.16506087789190879</v>
+        <v>0.18174589916251721</v>
       </c>
       <c r="D165">
-        <v>0.34017915310785962</v>
+        <v>0.29595712436481603</v>
       </c>
       <c r="E165">
-        <v>0.33611229924340802</v>
+        <v>0.33160423143168172</v>
       </c>
       <c r="F165">
-        <v>5.4020168390107287E-2</v>
+        <v>6.9468801208079564E-2</v>
       </c>
       <c r="G165">
-        <v>3.694564391585789E-2</v>
+        <v>3.9257484463031837E-2</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166">
-        <v>4.626374442825712E-2</v>
+        <v>5.5385672125353058E-2</v>
       </c>
       <c r="B166">
-        <v>2.1615862996982382E-2</v>
+        <v>2.6909372470413181E-2</v>
       </c>
       <c r="C166">
-        <v>0.1652972987196438</v>
+        <v>0.1821128118429875</v>
       </c>
       <c r="D166">
-        <v>0.33950387980111302</v>
+        <v>0.29588608530602029</v>
       </c>
       <c r="E166">
-        <v>0.33632228176717038</v>
+        <v>0.33088868321068599</v>
       </c>
       <c r="F166">
-        <v>5.4018342826294773E-2</v>
+        <v>6.9511455484554285E-2</v>
       </c>
       <c r="G166">
-        <v>3.6978589460523417E-2</v>
+        <v>3.9305919559980702E-2</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167">
-        <v>4.6441003370131587E-2</v>
+        <v>5.5662028165758923E-2</v>
       </c>
       <c r="B167">
-        <v>2.1636240130130609E-2</v>
+        <v>2.6961377804962199E-2</v>
       </c>
       <c r="C167">
-        <v>0.16554070611438901</v>
+        <v>0.1824680893741448</v>
       </c>
       <c r="D167">
-        <v>0.33875331988300988</v>
+        <v>0.29577824067646158</v>
       </c>
       <c r="E167">
-        <v>0.33660101598563469</v>
+        <v>0.33022297213820329</v>
       </c>
       <c r="F167">
-        <v>5.4017554393932597E-2</v>
+        <v>6.9555664377656645E-2</v>
       </c>
       <c r="G167">
-        <v>3.7010160122757832E-2</v>
+        <v>3.9351627462819123E-2</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168">
-        <v>4.6619483771494802E-2</v>
+        <v>5.5939009236687667E-2</v>
       </c>
       <c r="B168">
-        <v>2.1655262168361049E-2</v>
+        <v>2.7012434035400611E-2</v>
       </c>
       <c r="C168">
-        <v>0.16578969816334671</v>
+        <v>0.1828119252722834</v>
       </c>
       <c r="D168">
-        <v>0.33793255142344619</v>
+        <v>0.29563527501090509</v>
       </c>
       <c r="E168">
-        <v>0.33694476505645782</v>
+        <v>0.32960530178021569</v>
       </c>
       <c r="F168">
-        <v>5.4017799936355658E-2</v>
+        <v>6.9601323494662221E-2</v>
       </c>
       <c r="G168">
-        <v>3.7040439480542253E-2</v>
+        <v>3.9394731169844897E-2</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169">
-        <v>4.6799162261802488E-2</v>
+        <v>5.6216505183912822E-2</v>
       </c>
       <c r="B169">
-        <v>2.1672931078942161E-2</v>
+        <v>2.7062565996433221E-2</v>
       </c>
       <c r="C169">
-        <v>0.16604273011055171</v>
+        <v>0.1831447157099407</v>
       </c>
       <c r="D169">
-        <v>0.33704632959137892</v>
+        <v>0.29545734341955993</v>
       </c>
       <c r="E169">
-        <v>0.33735026725348261</v>
+        <v>0.3290351778676931</v>
       </c>
       <c r="F169">
-        <v>5.401906361729758E-2</v>
+        <v>6.9648312749844038E-2</v>
       </c>
       <c r="G169">
-        <v>3.7069516086547419E-2</v>
+        <v>3.9435379072611777E-2</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170">
-        <v>4.6979984783672858E-2</v>
+        <v>5.649437528685209E-2</v>
       </c>
       <c r="B170">
-        <v>2.1689276602947349E-2</v>
+        <v>2.7111837448081679E-2</v>
       </c>
       <c r="C170">
-        <v>0.166298167447685</v>
+        <v>0.18346701117344291</v>
       </c>
       <c r="D170">
-        <v>0.3360994442103416</v>
+        <v>0.29524318577158049</v>
       </c>
       <c r="E170">
-        <v>0.33781432584167898</v>
+        <v>0.32851335078374733</v>
       </c>
       <c r="F170">
-        <v>5.402132293553772E-2</v>
+        <v>6.9696498045205266E-2</v>
       </c>
       <c r="G170">
-        <v>3.7097478178145099E-2</v>
+        <v>3.9473741491095123E-2</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171">
-        <v>4.7161867234514862E-2</v>
+        <v>5.6772448554972377E-2</v>
       </c>
       <c r="B171">
-        <v>2.1704354726195051E-2</v>
+        <v>2.716034448296498E-2</v>
       </c>
       <c r="C171">
-        <v>0.16655434386976031</v>
+        <v>0.18377946354435301</v>
       </c>
       <c r="D171">
-        <v>0.33509710220168981</v>
+        <v>0.29499035513040178</v>
       </c>
       <c r="E171">
-        <v>0.33833337001602271</v>
+        <v>0.32804164880241138</v>
       </c>
       <c r="F171">
-        <v>5.402455302463436E-2</v>
+        <v>6.9745732473520283E-2</v>
       </c>
       <c r="G171">
-        <v>3.7124408927193417E-2</v>
+        <v>3.951000701137581E-2</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172">
-        <v>4.7344696922655111E-2</v>
+        <v>5.7050525029955217E-2</v>
       </c>
       <c r="B172">
-        <v>2.1718245758120751E-2</v>
+        <v>2.7208208804415018E-2</v>
       </c>
       <c r="C172">
-        <v>0.16680962179949449</v>
+        <v>0.18408277272457721</v>
       </c>
       <c r="D172">
-        <v>0.33404529903730018</v>
+        <v>0.29469554924339247</v>
       </c>
       <c r="E172">
-        <v>0.33890302470789879</v>
+        <v>0.3276227080483784</v>
       </c>
       <c r="F172">
-        <v>5.4028729137678339E-2</v>
+        <v>6.9795857261750902E-2</v>
       </c>
       <c r="G172">
-        <v>3.715038263685886E-2</v>
+        <v>3.9544378887543301E-2</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173">
-        <v>4.7528334745978743E-2</v>
+        <v>5.7328378210085983E-2</v>
       </c>
       <c r="B173">
-        <v>2.1731052178068609E-2</v>
+        <v>2.725557122935942E-2</v>
       </c>
       <c r="C173">
-        <v>0.16706245258357719</v>
+        <v>0.1843776363140168</v>
       </c>
       <c r="D173">
-        <v>0.33295114529909392</v>
+        <v>0.294355028606057</v>
       </c>
       <c r="E173">
-        <v>0.33951772569819572</v>
+        <v>0.3272596112361239</v>
       </c>
       <c r="F173">
-        <v>5.4033827417777867E-2</v>
+        <v>6.984670262432896E-2</v>
       </c>
       <c r="G173">
-        <v>3.7175462077304537E-2</v>
+        <v>3.9577071780029442E-2</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174">
-        <v>4.7712618007264507E-2</v>
+        <v>5.7605758712191563E-2</v>
       </c>
       <c r="B174">
-        <v>2.1742896365052489E-2</v>
+        <v>2.7302585588192329E-2</v>
       </c>
       <c r="C174">
-        <v>0.16731143300758189</v>
+        <v>0.18466470555709269</v>
       </c>
       <c r="D174">
-        <v>0.33182311922083851</v>
+        <v>0.29396509942313709</v>
       </c>
       <c r="E174">
-        <v>0.3401704120061696</v>
+        <v>0.32695545334248249</v>
       </c>
       <c r="F174">
-        <v>5.4039824348801217E-2</v>
+        <v>6.9898088633452315E-2</v>
       </c>
       <c r="G174">
-        <v>3.7199697044296508E-2</v>
+        <v>3.9608308743450518E-2</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175">
-        <v>4.7897363758534907E-2</v>
+        <v>5.7882399213107151E-2</v>
       </c>
       <c r="B175">
-        <v>2.1753918239212619E-2</v>
+        <v>2.7349413022998231E-2</v>
       </c>
       <c r="C175">
-        <v>0.1675553546782983</v>
+        <v>0.1849445496825666</v>
       </c>
       <c r="D175">
-        <v>0.33067122293351692</v>
+        <v>0.29352263490706998</v>
       </c>
       <c r="E175">
-        <v>0.34085232102039048</v>
+        <v>0.32671285819735058</v>
       </c>
       <c r="F175">
-        <v>5.4046695372780333E-2</v>
+        <v>6.9949826367227019E-2</v>
       </c>
       <c r="G175">
-        <v>3.7223123997266648E-2</v>
+        <v>3.9638318609692413E-2</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176">
-        <v>4.8082372523738787E-2</v>
+        <v>5.8158020717537062E-2</v>
       </c>
       <c r="B176">
-        <v>2.176427271982553E-2</v>
+        <v>2.739621654280211E-2</v>
       </c>
       <c r="C176">
-        <v>0.1677932430836323</v>
+        <v>0.18521763059319321</v>
       </c>
       <c r="D176">
-        <v>0.3295070287113735</v>
+        <v>0.29302560416888601</v>
       </c>
       <c r="E176">
-        <v>0.34155290308569458</v>
+        <v>0.32653347515243569</v>
       </c>
       <c r="F176">
-        <v>5.4054413320151498E-2</v>
+        <v>7.0001719329743833E-2</v>
       </c>
       <c r="G176">
-        <v>3.7245766555586812E-2</v>
+        <v>3.9667333495402878E-2</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177">
-        <v>4.8267432212260812E-2</v>
+        <v>5.8432340053725738E-2</v>
       </c>
       <c r="B177">
-        <v>2.1774126792797669E-2</v>
+        <v>2.744315566596589E-2</v>
       </c>
       <c r="C177">
-        <v>0.16802438376249049</v>
+        <v>0.18548428897085631</v>
       </c>
       <c r="D177">
-        <v>0.32834361076240232</v>
+        <v>0.29247357408499752</v>
       </c>
       <c r="E177">
-        <v>0.34225986275236991</v>
+        <v>0.32641748928592368</v>
       </c>
       <c r="F177">
-        <v>5.4062947231406727E-2</v>
+        <v>7.0053565477105673E-2</v>
       </c>
       <c r="G177">
-        <v>3.7267636486268317E-2</v>
+        <v>3.9695586461433882E-2</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178">
-        <v>4.8452322045240311E-2</v>
+        <v>5.8705078488796483E-2</v>
       </c>
       <c r="B178">
-        <v>2.1783655938163501E-2</v>
+        <v>2.74903809598161E-2</v>
       </c>
       <c r="C178">
-        <v>0.1682483338923613</v>
+        <v>0.18574474277255179</v>
       </c>
       <c r="D178">
-        <v>0.32719536719842413</v>
+        <v>0.29186814800024741</v>
       </c>
       <c r="E178">
-        <v>0.34295932400493739</v>
+        <v>0.32636318115617857</v>
       </c>
       <c r="F178">
-        <v>5.4072262078111867E-2</v>
+        <v>7.0105159716702781E-2</v>
       </c>
       <c r="G178">
-        <v>3.7288734842766347E-2</v>
+        <v>3.9723308905706967E-2</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179">
-        <v>4.8636816386516561E-2</v>
+        <v>5.8975971243379582E-2</v>
       </c>
       <c r="B179">
-        <v>2.1793039718531849E-2</v>
+        <v>2.7538028440518642E-2</v>
       </c>
       <c r="C179">
-        <v>0.1684649185497295</v>
+        <v>0.18599909816910251</v>
       </c>
       <c r="D179">
-        <v>0.32607774485416052</v>
+        <v>0.29121330493129521</v>
       </c>
       <c r="E179">
-        <v>0.34363610779591741</v>
+        <v>0.3263665724953918</v>
       </c>
       <c r="F179">
-        <v>5.408231972539846E-2</v>
+        <v>7.015629693814715E-2</v>
       </c>
       <c r="G179">
-        <v>3.7309052969745377E-2</v>
+        <v>3.9750727782170807E-2</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180">
-        <v>4.8820688440334367E-2</v>
+        <v>5.9244777664803863E-2</v>
       </c>
       <c r="B180">
-        <v>2.1802456424521829E-2</v>
+        <v>2.758621393225133E-2</v>
       </c>
       <c r="C180">
-        <v>0.16867421196500881</v>
+        <v>0.18624737252566789</v>
       </c>
       <c r="D180">
-        <v>0.32500688579777448</v>
+        <v>0.2905156063887066</v>
       </c>
       <c r="E180">
-        <v>0.34427410285107007</v>
+        <v>0.32642119192579461</v>
       </c>
       <c r="F180">
-        <v>5.4093081361266698E-2</v>
+        <v>7.020677522573901E-2</v>
       </c>
       <c r="G180">
-        <v>3.7328573160019161E-2</v>
+        <v>3.9778062337038657E-2</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181">
-        <v>4.9003713846629209E-2</v>
+        <v>5.9511291650258293E-2</v>
       </c>
       <c r="B181">
-        <v>2.181207681578521E-2</v>
+        <v>2.7635027674579132E-2</v>
       </c>
       <c r="C181">
-        <v>0.16887650530439621</v>
+        <v>0.18648952778388239</v>
       </c>
       <c r="D181">
-        <v>0.32399921829122408</v>
+        <v>0.28978424406874548</v>
       </c>
       <c r="E181">
-        <v>0.34485670554618092</v>
+        <v>0.32651798926761327</v>
       </c>
       <c r="F181">
-        <v>5.4104511282868112E-2</v>
+        <v>7.025639904135704E-2</v>
       </c>
       <c r="G181">
-        <v>3.7347268912916898E-2</v>
+        <v>3.9805520513561343E-2</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182">
-        <v>4.9185674170628427E-2</v>
+        <v>5.9775351811044992E-2</v>
       </c>
       <c r="B182">
-        <v>2.1822057133332441E-2</v>
+        <v>2.768452953040125E-2</v>
       </c>
       <c r="C182">
-        <v>0.16907226363012981</v>
+        <v>0.1867255116790936</v>
       </c>
       <c r="D182">
-        <v>0.32307101635567559</v>
+        <v>0.28903091168130091</v>
       </c>
       <c r="E182">
-        <v>0.345367302091794</v>
+        <v>0.32664541843232919</v>
       </c>
       <c r="F182">
-        <v>5.4116581801583977E-2</v>
+        <v>7.0304981954017409E-2</v>
       </c>
       <c r="G182">
-        <v>3.7365104816840133E-2</v>
+        <v>3.9833294911816752E-2</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183">
-        <v>4.936636025219894E-2</v>
+        <v>6.0036850730413663E-2</v>
       </c>
       <c r="B183">
-        <v>2.1832531743983662E-2</v>
+        <v>2.7734745163294609E-2</v>
       </c>
       <c r="C183">
-        <v>0.1692620756797496</v>
+        <v>0.18695530319155371</v>
       </c>
       <c r="D183">
-        <v>0.32223795108992898</v>
+        <v>0.28826949661165308</v>
       </c>
       <c r="E183">
-        <v>0.34578976618664808</v>
+        <v>0.32678969704690503</v>
       </c>
       <c r="F183">
-        <v>5.4129278820014531E-2</v>
+        <v>7.0352348719396135E-2</v>
       </c>
       <c r="G183">
-        <v>3.7382036227472402E-2</v>
+        <v>3.9861558536789937E-2</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184">
-        <v>4.954557537124761E-2</v>
+        <v>6.0295742661660233E-2</v>
       </c>
       <c r="B184">
-        <v>2.1843605945588901E-2</v>
+        <v>2.778566345943459E-2</v>
       </c>
       <c r="C184">
-        <v>0.16944660068113099</v>
+        <v>0.18717895841072829</v>
       </c>
       <c r="D184">
-        <v>0.32151465411363278</v>
+        <v>0.28751560114590291</v>
       </c>
       <c r="E184">
-        <v>0.34610894743806669</v>
+        <v>0.32693523732208951</v>
       </c>
       <c r="F184">
-        <v>5.4142607449585912E-2</v>
+        <v>7.0398336475313933E-2</v>
       </c>
       <c r="G184">
-        <v>3.7398009000750743E-2</v>
+        <v>3.9890460524872461E-2</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185">
-        <v>4.9723138188828883E-2</v>
+        <v>6.0552049119262097E-2</v>
       </c>
       <c r="B185">
-        <v>2.1855349578859991E-2</v>
+        <v>2.783723531851064E-2</v>
       </c>
       <c r="C185">
-        <v>0.16962651652820471</v>
+        <v>0.18739665268554281</v>
       </c>
       <c r="D185">
-        <v>0.32091430952383548</v>
+        <v>0.28678591730397168</v>
       </c>
       <c r="E185">
-        <v>0.3463111296139183</v>
+        <v>0.32706522872087979</v>
       </c>
       <c r="F185">
-        <v>5.4156596936500601E-2</v>
+        <v>7.044279474973926E-2</v>
       </c>
       <c r="G185">
-        <v>3.7412959629862359E-2</v>
+        <v>3.9920122102087612E-2</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186">
-        <v>4.9898885469311142E-2</v>
+        <v>6.0805861906404357E-2</v>
       </c>
       <c r="B186">
-        <v>2.186779210972813E-2</v>
+        <v>2.7889373789489601E-2</v>
       </c>
       <c r="C186">
-        <v>0.16980247331113629</v>
+        <v>0.1876087144034119</v>
       </c>
       <c r="D186">
-        <v>0.32044828626804073</v>
+        <v>0.28609749226996922</v>
       </c>
       <c r="E186">
-        <v>0.34638444266938839</v>
+        <v>0.32716234016532419</v>
       </c>
       <c r="F186">
-        <v>5.4171304094572638E-2</v>
+        <v>7.0485584301587412E-2</v>
       </c>
       <c r="G186">
-        <v>3.7426816077814992E-2</v>
+        <v>3.9950633163819797E-2</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187">
-        <v>5.0072674603269987E-2</v>
+        <v>6.1057343359979262E-2</v>
       </c>
       <c r="B187">
-        <v>2.1880919786701779E-2</v>
+        <v>2.794195537882219E-2</v>
       </c>
       <c r="C187">
-        <v>0.16997505555613329</v>
+        <v>0.1878156463650118</v>
       </c>
       <c r="D187">
-        <v>0.32012581855548639</v>
+        <v>0.28546693169446202</v>
       </c>
       <c r="E187">
-        <v>0.34631921737851501</v>
+        <v>0.3272094985657451</v>
       </c>
       <c r="F187">
-        <v>5.4186814506218137E-2</v>
+        <v>7.052657510377533E-2</v>
       </c>
       <c r="G187">
-        <v>3.743949961366879E-2</v>
+        <v>3.9982049532206368E-2</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188">
-        <v>5.024438593088007E-2</v>
+        <v>6.1306723741458728E-2</v>
       </c>
       <c r="B188">
-        <v>2.1894675321350011E-2</v>
+        <v>2.7994822348780691E-2</v>
       </c>
       <c r="C188">
-        <v>0.17014475557721681</v>
+        <v>0.18801813233205911</v>
       </c>
       <c r="D188">
-        <v>0.31995373830634488</v>
+        <v>0.28490959251378561</v>
       </c>
       <c r="E188">
-        <v>0.34610827594350729</v>
+        <v>0.32719069328537731</v>
       </c>
       <c r="F188">
-        <v>5.420324114574511E-2</v>
+        <v>7.0565644553926846E-2</v>
       </c>
       <c r="G188">
-        <v>3.7450927774964581E-2</v>
+        <v>4.0014391224623219E-2</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189">
-        <v>5.0413924828708462E-2</v>
+        <v>6.1554295887945212E-2</v>
       </c>
       <c r="B189">
-        <v>2.1908960347203979E-2</v>
+        <v>2.8047785819640569E-2</v>
       </c>
       <c r="C189">
-        <v>0.1703119592257466</v>
+        <v>0.18821702795348841</v>
       </c>
       <c r="D189">
-        <v>0.31993626105462392</v>
+        <v>0.28443881666786608</v>
       </c>
       <c r="E189">
-        <v>0.34574715569823239</v>
+        <v>0.32709175533006363</v>
       </c>
       <c r="F189">
-        <v>5.4220720367934107E-2</v>
+        <v>7.0602676462990788E-2</v>
       </c>
       <c r="G189">
-        <v>3.746101847753578E-2</v>
+        <v>4.0047641878000147E-2</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190">
-        <v>5.0581223483051073E-2</v>
+        <v>6.1800407422598062E-2</v>
       </c>
       <c r="B190">
-        <v>2.192364066536159E-2</v>
+        <v>2.810062957972146E-2</v>
       </c>
       <c r="C190">
-        <v>0.17047694409112771</v>
+        <v>0.18841333653333439</v>
       </c>
       <c r="D190">
-        <v>0.32007482537577642</v>
+        <v>0.28406525238296543</v>
       </c>
       <c r="E190">
-        <v>0.34523426583485062</v>
+        <v>0.32690106370867472</v>
       </c>
       <c r="F190">
-        <v>5.423940541806363E-2</v>
+        <v>7.0637560975161023E-2</v>
       </c>
       <c r="G190">
-        <v>3.746969513176885E-2</v>
+        <v>4.0081749397545142E-2</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191">
-        <v>5.0746242256573537E-2</v>
+        <v>6.2045450884853248E-2</v>
       </c>
       <c r="B191">
-        <v>2.1938554034902861E-2</v>
+        <v>2.8153114605927381E-2</v>
       </c>
       <c r="C191">
-        <v>0.1706398890218242</v>
+        <v>0.18860817150925069</v>
       </c>
       <c r="D191">
-        <v>0.32036798553631501</v>
+        <v>0.28379630063770228</v>
       </c>
       <c r="E191">
-        <v>0.34457097887823868</v>
+        <v>0.32661013892161023</v>
       </c>
       <c r="F191">
-        <v>5.4259457745623338E-2</v>
+        <v>7.0670195631725885E-2</v>
       </c>
       <c r="G191">
-        <v>3.747689252651297E-2</v>
+        <v>4.0116627808940181E-2</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192">
-        <v>5.0908970501121538E-2</v>
+        <v>6.2289852208158573E-2</v>
       </c>
       <c r="B192">
-        <v>2.1953520008477601E-2</v>
+        <v>2.8204984365057029E-2</v>
       </c>
       <c r="C192">
-        <v>0.17080089287368319</v>
+        <v>0.18880270885460501</v>
       </c>
       <c r="D192">
-        <v>0.32081135753103351</v>
+        <v>0.28363571239290031</v>
       </c>
       <c r="E192">
-        <v>0.34376165932258052</v>
+        <v>0.32621409374578458</v>
       </c>
       <c r="F192">
-        <v>5.4281036666603368E-2</v>
+        <v>7.0700487925308697E-2</v>
       </c>
       <c r="G192">
-        <v>3.7482563096504662E-2</v>
+        <v>4.0152160508196859E-2</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193">
-        <v>5.1069426673214458E-2</v>
+        <v>6.2534057980714264E-2</v>
       </c>
       <c r="B193">
-        <v>2.196835110824881E-2</v>
+        <v>2.8255971006278451E-2</v>
       </c>
       <c r="C193">
-        <v>0.17095999966506839</v>
+        <v>0.1889981336819623</v>
       </c>
       <c r="D193">
-        <v>0.32139761959788032</v>
+        <v>0.28358334986987749</v>
       </c>
       <c r="E193">
-        <v>0.34281363179221208</v>
+        <v>0.32571192381137037</v>
       </c>
       <c r="F193">
-        <v>5.4304288103183343E-2</v>
+        <v>7.0728359032932619E-2</v>
       </c>
       <c r="G193">
-        <v>3.7486683060187528E-2</v>
+        <v>4.0188204616867507E-2</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194">
-        <v>5.1227657582894347E-2</v>
+        <v>6.277852194112879E-2</v>
       </c>
       <c r="B194">
-        <v>2.1982864480454889E-2</v>
+        <v>2.830580251624943E-2</v>
       </c>
       <c r="C194">
-        <v>0.17111722692532011</v>
+        <v>0.18919558537066</v>
       </c>
       <c r="D194">
-        <v>0.32211656923544718</v>
+        <v>0.28363511379253009</v>
       </c>
       <c r="E194">
-        <v>0.34173709055107099</v>
+        <v>0.32510663166380638</v>
       </c>
       <c r="F194">
-        <v>5.4329333329769122E-2</v>
+        <v>7.0753748436170327E-2</v>
       </c>
       <c r="G194">
-        <v>3.7489257895035877E-2</v>
+        <v>4.0224596279460491E-2</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195">
-        <v>5.1383736653293821E-2</v>
+        <v>6.3023691173345345E-2</v>
       </c>
       <c r="B195">
-        <v>2.1996893112256749E-2</v>
+        <v>2.8354210854412622E-2</v>
       </c>
       <c r="C195">
-        <v>0.17127259395055949</v>
+        <v>0.1893961055466189</v>
       </c>
       <c r="D195">
-        <v>0.32295523955315258</v>
+        <v>0.2837830294897527</v>
       </c>
       <c r="E195">
-        <v>0.34054495145605479</v>
+        <v>0.32440518727065371</v>
       </c>
       <c r="F195">
-        <v>5.4356258680169113E-2</v>
+        <v>7.0776618913920689E-2</v>
       </c>
       <c r="G195">
-        <v>3.7490326594526342E-2</v>
+        <v>4.0261156751298467E-2</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196">
-        <v>5.1537761152155678E-2</v>
+        <v>6.3269992467495983E-2</v>
       </c>
       <c r="B196">
-        <v>2.2010295730902091E-2</v>
+        <v>2.8400940902631521E-2</v>
       </c>
       <c r="C196">
-        <v>0.17142614694178579</v>
+        <v>0.1896005926618467</v>
       </c>
       <c r="D196">
-        <v>0.3238980779669044</v>
+        <v>0.28401547885897049</v>
       </c>
       <c r="E196">
-        <v>0.33925264684230488</v>
+        <v>0.32361833493040959</v>
       </c>
       <c r="F196">
-        <v>5.4385107136102007E-2</v>
+        <v>7.079696131685019E-2</v>
       </c>
       <c r="G196">
-        <v>3.7489964229838461E-2</v>
+        <v>4.0297698861802643E-2</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197">
-        <v>5.1689848466558733E-2</v>
+        <v>6.3517819380573201E-2</v>
       </c>
       <c r="B197">
-        <v>2.2022964638188959E-2</v>
+        <v>2.8445759954899862E-2</v>
       </c>
       <c r="C197">
-        <v>0.171577978455142</v>
+        <v>0.1898097659759756</v>
       </c>
       <c r="D197">
-        <v>0.32492718983166502</v>
+        <v>0.28431756177724848</v>
       </c>
       <c r="E197">
-        <v>0.33787786364385702</v>
+        <v>0.32276026042462908</v>
       </c>
       <c r="F197">
-        <v>5.4415872513772258E-2</v>
+        <v>7.0814798741551221E-2</v>
       </c>
       <c r="G197">
-        <v>3.7488282450825097E-2</v>
+        <v>4.0334033745124412E-2</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198">
-        <v>5.1840131644311817E-2</v>
+        <v>6.3767520546705453E-2</v>
       </c>
       <c r="B198">
-        <v>2.203483095773115E-2</v>
+        <v>2.8488467264402632E-2</v>
       </c>
       <c r="C198">
-        <v>0.17172823926570779</v>
+        <v>0.1900241407119489</v>
       </c>
       <c r="D198">
-        <v>0.32602264846406193</v>
+        <v>0.28467156988612657</v>
       </c>
       <c r="E198">
-        <v>0.33644022517774308</v>
+        <v>0.32184813513731581</v>
       </c>
       <c r="F198">
-        <v>5.4448496746540967E-2</v>
+        <v>7.0830189485714651E-2</v>
       </c>
       <c r="G198">
-        <v>3.7485427743907652E-2</v>
+        <v>4.0369976967788213E-2</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199">
-        <v>5.1988754516469407E-2</v>
+        <v>6.4019389724594339E-2</v>
       </c>
       <c r="B199">
-        <v>2.2045867052683649E-2</v>
+        <v>2.8528903055635321E-2</v>
       </c>
       <c r="C199">
-        <v>0.17187714147324709</v>
+        <v>0.19024401475410371</v>
       </c>
       <c r="D199">
-        <v>0.32716287117232778</v>
+        <v>0.28505755541528771</v>
       </c>
       <c r="E199">
-        <v>0.33496091782776188</v>
+        <v>0.32090155389207953</v>
       </c>
       <c r="F199">
-        <v>5.4482870496667807E-2</v>
+        <v>7.0843228730015223E-2</v>
       </c>
       <c r="G199">
-        <v>3.7481577460840979E-2</v>
+        <v>4.040535442829743E-2</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200">
-        <v>5.213586680301191E-2</v>
+        <v>6.4273658025943259E-2</v>
       </c>
       <c r="B200">
-        <v>2.2056086181759121E-2</v>
+        <v>2.856695634634759E-2</v>
       </c>
       <c r="C200">
-        <v>0.17202495248010979</v>
+        <v>0.19046946634463099</v>
       </c>
       <c r="D200">
-        <v>0.32832505864993788</v>
+        <v>0.28545397860471983</v>
       </c>
       <c r="E200">
-        <v>0.33346226502053261</v>
+        <v>0.31994188482783248</v>
       </c>
       <c r="F200">
-        <v>5.4518837050639153E-2</v>
+        <v>7.0854048659030916E-2</v>
       </c>
       <c r="G200">
-        <v>3.7476933814020973E-2</v>
+        <v>4.0440007191507581E-2</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201">
-        <v>5.228161960279918E-2</v>
+        <v>6.4530488598368352E-2</v>
       </c>
       <c r="B201">
-        <v>2.206553971288604E-2</v>
+        <v>2.8602570908109051E-2</v>
       </c>
       <c r="C201">
-        <v>0.1721719802184799</v>
+        <v>0.19070036127748979</v>
       </c>
       <c r="D201">
-        <v>0.32948569247499959</v>
+        <v>0.28583841667543269</v>
       </c>
       <c r="E201">
-        <v>0.33196725251726011</v>
+        <v>0.31899155006395008</v>
       </c>
       <c r="F201">
-        <v>5.4556199234920957E-2</v>
+        <v>7.086281709819231E-2</v>
       </c>
       <c r="G201">
-        <v>3.7471716238661433E-2</v>
+        <v>4.0473795378446017E-2</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202">
-        <v>5.2426161612467347E-2</v>
+        <v>6.4789973891528851E-2</v>
       </c>
       <c r="B202">
-        <v>2.207431237189451E-2</v>
+        <v>2.8635748812628939E-2</v>
       </c>
       <c r="C202">
-        <v>0.17231855074121599</v>
+        <v>0.19093636757722099</v>
       </c>
       <c r="D202">
-        <v>0.33062108273304769</v>
+        <v>0.28618831591727978</v>
       </c>
       <c r="E202">
-        <v>0.33049901102123858</v>
+        <v>0.31807325829704203</v>
       </c>
       <c r="F202">
-        <v>5.4594728869723233E-2</v>
+        <v>7.0869734847196886E-2</v>
       </c>
       <c r="G202">
-        <v>3.746615265042251E-2</v>
+        <v>4.0506600657099802E-2</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203">
-        <v>5.2569636325406913E-2</v>
+        <v>6.5052135494690647E-2</v>
       </c>
       <c r="B203">
-        <v>2.2082516060711571E-2</v>
+        <v>2.866655119602142E-2</v>
       </c>
       <c r="C203">
-        <v>0.1724649799409021</v>
+        <v>0.1911769755516641</v>
       </c>
       <c r="D203">
-        <v>0.33170795502431383</v>
+        <v>0.28648176543439052</v>
       </c>
       <c r="E203">
-        <v>0.32908026428901271</v>
+        <v>0.31720921266219348</v>
       </c>
       <c r="F203">
-        <v>5.4634178115714867E-2</v>
+        <v>7.0875031915117542E-2</v>
       </c>
       <c r="G203">
-        <v>3.7460470243946928E-2</v>
+        <v>4.0538327745934348E-2</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204">
-        <v>5.2712180339771632E-2</v>
+        <v>6.531692646784526E-2</v>
       </c>
       <c r="B204">
-        <v>2.2090282778214461E-2</v>
+        <v>2.8695096118505889E-2</v>
       </c>
       <c r="C204">
-        <v>0.1726115417491971</v>
+        <v>0.19142152125315429</v>
       </c>
       <c r="D204">
-        <v>0.33272406326867482</v>
+        <v>0.28669826806210108</v>
       </c>
       <c r="E204">
-        <v>0.32773275339769892</v>
+        <v>0.31642032082981519</v>
       </c>
       <c r="F204">
-        <v>5.4674291977391751E-2</v>
+        <v>7.0878962893972511E-2</v>
       </c>
       <c r="G204">
-        <v>3.7454886489062721E-2</v>
+        <v>4.0568904374601741E-2</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205">
-        <v>5.2853922791888337E-2</v>
+        <v>6.558423591645586E-2</v>
       </c>
       <c r="B205">
-        <v>2.2097757145001479E-2</v>
+        <v>2.8721553664970059E-2</v>
       </c>
       <c r="C205">
-        <v>0.17275843556754969</v>
+        <v>0.19166921153129021</v>
       </c>
       <c r="D205">
-        <v>0.33364881184934397</v>
+        <v>0.28681947999669433</v>
       </c>
       <c r="E205">
-        <v>0.32647665050359648</v>
+        <v>0.31572543681316212</v>
       </c>
       <c r="F205">
-        <v>5.4714821179906732E-2</v>
+        <v>7.0881801678702908E-2</v>
       </c>
       <c r="G205">
-        <v>3.7449600962708489E-2</v>
+        <v>4.0598280398728592E-2</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206">
-        <v>5.29949858474855E-2</v>
+        <v>6.5853895568131357E-2</v>
       </c>
       <c r="B206">
-        <v>2.2105088965039401E-2</v>
+        <v>2.8746138668119359E-2</v>
       </c>
       <c r="C206">
-        <v>0.1729057558275281</v>
+        <v>0.19191914949042599</v>
       </c>
       <c r="D206">
-        <v>0.33446386774904729</v>
+        <v>0.28682988881197469</v>
       </c>
       <c r="E206">
-        <v>0.32532997845959749</v>
+        <v>0.31514066625563969</v>
       </c>
       <c r="F206">
-        <v>5.4755534604049687E-2</v>
+        <v>7.0883835581186438E-2</v>
       </c>
       <c r="G206">
-        <v>3.7444788547227673E-2</v>
+        <v>4.0626425624524773E-2</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207">
-        <v>5.3135486127553089E-2</v>
+        <v>6.6125687944193545E-2</v>
       </c>
       <c r="B207">
-        <v>2.2112426143457278E-2</v>
+        <v>2.876910156958197E-2</v>
       </c>
       <c r="C207">
-        <v>0.17305346646882239</v>
+        <v>0.19217035929344589</v>
       </c>
       <c r="D207">
-        <v>0.33515374043411922</v>
+        <v>0.28671739857709172</v>
       </c>
       <c r="E207">
-        <v>0.32430805589187162</v>
+        <v>0.31467876648184678</v>
       </c>
       <c r="F207">
-        <v>5.4796230543791569E-2</v>
+        <v>7.0885359049360885E-2</v>
       </c>
       <c r="G207">
-        <v>3.744059439039818E-2</v>
+        <v>4.0653327084489037E-2</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208">
-        <v>5.3275536921686309E-2</v>
+        <v>6.6399355733165438E-2</v>
       </c>
       <c r="B208">
-        <v>2.211990815005363E-2</v>
+        <v>2.87907180722109E-2</v>
       </c>
       <c r="C208">
-        <v>0.17320138276649771</v>
+        <v>0.19242180978300469</v>
       </c>
       <c r="D208">
-        <v>0.33570630470086682</v>
+        <v>0.28647379319079258</v>
       </c>
       <c r="E208">
-        <v>0.32342299037654548</v>
+        <v>0.31434867062898031</v>
       </c>
       <c r="F208">
-        <v>5.4836746171555407E-2</v>
+        <v>7.0886666943697912E-2</v>
       </c>
       <c r="G208">
-        <v>3.7437130912786623E-2</v>
+        <v>4.0678985648155239E-2</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209">
-        <v>5.3415251010923703E-2</v>
+        <v>6.6674611881397075E-2</v>
       </c>
       <c r="B209">
-        <v>2.212766010537634E-2</v>
+        <v>2.881127823356713E-2</v>
       </c>
       <c r="C209">
-        <v>0.17334916243598311</v>
+        <v>0.19267243654891461</v>
       </c>
       <c r="D209">
-        <v>0.33611324007738752</v>
+        <v>0.28609505359806392</v>
       </c>
       <c r="E209">
-        <v>0.32268324475129562</v>
+        <v>0.31415515968209701</v>
       </c>
       <c r="F209">
-        <v>5.4876964684980087E-2</v>
+        <v>7.0888047579447305E-2</v>
       </c>
       <c r="G209">
-        <v>3.7434476934047001E-2</v>
+        <v>4.0703412476516702E-2</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210">
-        <v>5.3554743884353197E-2</v>
+        <v>6.6951149943693417E-2</v>
       </c>
       <c r="B210">
-        <v>2.2135787497200739E-2</v>
+        <v>2.8831075677473169E-2</v>
       </c>
       <c r="C210">
-        <v>0.1734963072249312</v>
+        <v>0.19292116239797141</v>
       </c>
       <c r="D210">
-        <v>0.33637036009871191</v>
+        <v>0.28558151221833139</v>
       </c>
       <c r="E210">
-        <v>0.32209330256097668</v>
+        <v>0.31409869879585128</v>
       </c>
       <c r="F210">
-        <v>5.4916819832016593E-2</v>
+        <v>7.0889775604320554E-2</v>
       </c>
       <c r="G210">
-        <v>3.7432678901800721E-2</v>
+        <v>4.0726625362355412E-2</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211">
-        <v>5.3694137108229727E-2</v>
+        <v>6.7228654198845134E-2</v>
       </c>
       <c r="B211">
-        <v>2.214437153614281E-2</v>
+        <v>2.885039748535468E-2</v>
       </c>
       <c r="C211">
-        <v>0.17364217541882221</v>
+        <v>0.19316691620986101</v>
       </c>
       <c r="D211">
-        <v>0.33647780687186352</v>
+        <v>0.28493783707261322</v>
       </c>
       <c r="E211">
-        <v>0.32165345747190438</v>
+        <v>0.31417544440332529</v>
       </c>
       <c r="F211">
-        <v>5.4956297601872137E-2</v>
+        <v>7.0892105027137275E-2</v>
       </c>
       <c r="G211">
-        <v>3.7431753991167042E-2</v>
+        <v>4.0748645602855842E-2</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212">
-        <v>5.3833561580155329E-2</v>
+        <v>6.7506809095148224E-2</v>
       </c>
       <c r="B212">
-        <v>2.2153465187314241E-2</v>
+        <v>2.886951524276218E-2</v>
       </c>
       <c r="C212">
-        <v>0.1737860048161991</v>
+        <v>0.19340865055783271</v>
       </c>
       <c r="D212">
-        <v>0.33644009079889109</v>
+        <v>0.28417284863394282</v>
       </c>
       <c r="E212">
-        <v>0.32135974769603248</v>
+        <v>0.31437741850843731</v>
       </c>
       <c r="F212">
-        <v>5.4995435105918207E-2</v>
+        <v>7.0895262700464742E-2</v>
       </c>
       <c r="G212">
-        <v>3.7431694815488227E-2</v>
+        <v>4.0769495261413907E-2</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213">
-        <v>5.3973160402142978E-2</v>
+        <v>6.7785307585974147E-2</v>
       </c>
       <c r="B213">
-        <v>2.2163089987591401E-2</v>
+        <v>2.888867754484125E-2</v>
       </c>
       <c r="C213">
-        <v>0.1739269448976821</v>
+        <v>0.19364535837667621</v>
       </c>
       <c r="D213">
-        <v>0.33626596281141058</v>
+        <v>0.28329918219830053</v>
       </c>
       <c r="E213">
-        <v>0.32120404987295681</v>
+        <v>0.31469283649245888</v>
       </c>
       <c r="F213">
-        <v>5.5034316746907563E-2</v>
+        <v>7.0899442545488994E-2</v>
       </c>
       <c r="G213">
-        <v>3.743247528130101E-2</v>
+        <v>4.0789195256256919E-2</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214">
-        <v>5.4113091095772392E-2</v>
+        <v>6.8063858049016074E-2</v>
       </c>
       <c r="B214">
-        <v>2.2173233807921001E-2</v>
+        <v>2.890810413257414E-2</v>
       </c>
       <c r="C214">
-        <v>0.1740640961798664</v>
+        <v>0.19387608927598179</v>
       </c>
       <c r="D214">
-        <v>0.33596811594140391</v>
+        <v>0.28233281711449559</v>
       </c>
       <c r="E214">
-        <v>0.32117433779630589</v>
+        <v>0.31510656636185819</v>
       </c>
       <c r="F214">
-        <v>5.5073068014046198E-2</v>
+        <v>7.0904800789818964E-2</v>
       </c>
       <c r="G214">
-        <v>3.7434057164666537E-2</v>
+        <v>4.0807764276257971E-2</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215">
-        <v>5.4253526891810157E-2</v>
+        <v>6.8342189661314404E-2</v>
       </c>
       <c r="B215">
-        <v>2.218384975891927E-2</v>
+        <v>2.892798173290706E-2</v>
       </c>
       <c r="C215">
-        <v>0.1741965541511962</v>
+        <v>0.19409996634177201</v>
       </c>
       <c r="D215">
-        <v>0.33556272425870398</v>
+        <v>0.28129250005329431</v>
       </c>
       <c r="E215">
-        <v>0.32125510073671731</v>
+        <v>0.31560069120379353</v>
       </c>
       <c r="F215">
-        <v>5.5111847327204359E-2</v>
+        <v>7.0911452181764173E-2</v>
       </c>
       <c r="G215">
-        <v>3.7436396875442687E-2</v>
+        <v>4.0825218825148897E-2</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216">
-        <v>5.4394656845198439E-2</v>
+        <v>6.8620056157718698E-2</v>
       </c>
       <c r="B216">
-        <v>2.2194856430313669E-2</v>
+        <v>2.8948461565742611E-2</v>
       </c>
       <c r="C216">
-        <v>0.1743234548402221</v>
+        <v>0.19431620367003841</v>
       </c>
       <c r="D216">
-        <v>0.33506883849403107</v>
+        <v>0.28019909274874272</v>
       </c>
       <c r="E216">
-        <v>0.3214279050526212</v>
+        <v>0.31615514437494008</v>
       </c>
       <c r="F216">
-        <v>5.5150836454494867E-2</v>
+        <v>7.0919467324932789E-2</v>
       </c>
       <c r="G216">
-        <v>3.7439451883119083E-2</v>
+        <v>4.0841574157887382E-2</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217">
-        <v>5.4536684587189098E-2</v>
+        <v>6.8897237951868195E-2</v>
       </c>
       <c r="B217">
-        <v>2.2206139601633829E-2</v>
+        <v>2.8969658387194119E-2</v>
       </c>
       <c r="C217">
-        <v>0.17444401899897979</v>
+        <v>0.1945241242529295</v>
       </c>
       <c r="D217">
-        <v>0.33450766773699081</v>
+        <v>0.27907487509208889</v>
       </c>
       <c r="E217">
-        <v>0.32167207268101261</v>
+        <v>0.3167483866905525</v>
       </c>
       <c r="F217">
-        <v>5.5190230071547462E-2</v>
+        <v>7.0928871670368293E-2</v>
       </c>
       <c r="G217">
-        <v>3.7443186322648883E-2</v>
+        <v>4.0856845955006063E-2</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218">
-        <v>5.4679825630205507E-2</v>
+        <v>6.9173542753772257E-2</v>
       </c>
       <c r="B218">
-        <v>2.221755547614641E-2</v>
+        <v>2.899165093348368E-2</v>
       </c>
       <c r="C218">
-        <v>0.17455759209589539</v>
+        <v>0.19472317774552059</v>
       </c>
       <c r="D218">
-        <v>0.33390178425083711</v>
+        <v>0.27794283254886598</v>
       </c>
       <c r="E218">
-        <v>0.32196544211484718</v>
+        <v>0.31735809693998851</v>
       </c>
       <c r="F218">
-        <v>5.5230224994247602E-2</v>
+        <v>7.0939646448882843E-2</v>
       </c>
       <c r="G218">
-        <v>3.7447575437838228E-2</v>
+        <v>4.0871052629488661E-2</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219">
-        <v>5.4824303245360251E-2</v>
+        <v>6.9448804984502205E-2</v>
       </c>
       <c r="B219">
-        <v>2.2228935373013809E-2</v>
+        <v>2.901448360753095E-2</v>
       </c>
       <c r="C219">
-        <v>0.1746636776417487</v>
+        <v>0.19491295762667701</v>
       </c>
       <c r="D219">
-        <v>0.333274292747334</v>
+        <v>0.27682595390442449</v>
       </c>
       <c r="E219">
-        <v>0.32228517287436431</v>
+        <v>0.3179618507092169</v>
       </c>
       <c r="F219">
-        <v>5.5271009567187293E-2</v>
+        <v>7.0951731468487253E-2</v>
       </c>
       <c r="G219">
-        <v>3.745260855099234E-2</v>
+        <v>4.0884217699177078E-2</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220">
-        <v>5.4970343049204312E-2</v>
+        <v>6.9722884319491543E-2</v>
       </c>
       <c r="B220">
-        <v>2.2240091710008621E-2</v>
+        <v>2.903816928454131E-2</v>
       </c>
       <c r="C220">
-        <v>0.1747619618570837</v>
+        <v>0.19509321682950109</v>
       </c>
       <c r="D220">
-        <v>0.33264800604196842</v>
+        <v>0.27574656116429042</v>
       </c>
       <c r="E220">
-        <v>0.32260855331110488</v>
+        <v>0.31853776673481782</v>
       </c>
       <c r="F220">
-        <v>5.5312753648328751E-2</v>
+        <v>7.0965029609444411E-2</v>
       </c>
       <c r="G220">
-        <v>3.7458290382292883E-2</v>
+        <v>4.0896372057913688E-2</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221">
-        <v>5.5118166562751099E-2</v>
+        <v>6.9995663678719816E-2</v>
       </c>
       <c r="B221">
-        <v>2.2250825047962362E-2</v>
+        <v>2.906269310489119E-2</v>
       </c>
       <c r="C221">
-        <v>0.17485232837337489</v>
+        <v>0.19526388060629529</v>
       </c>
       <c r="D221">
-        <v>0.33204466586766451</v>
+        <v>0.27472568964003041</v>
       </c>
       <c r="E221">
-        <v>0.32291377391049192</v>
+        <v>0.31906510436130092</v>
       </c>
       <c r="F221">
-        <v>5.5355599543289287E-2</v>
+        <v>7.09794126297493E-2</v>
       </c>
       <c r="G221">
-        <v>3.7464640694468927E-2</v>
+        <v>4.0907555979018587E-2</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222">
-        <v>5.5267984109561782E-2</v>
+        <v>7.0267046989798562E-2</v>
       </c>
       <c r="B222">
-        <v>2.2260931937044849E-2</v>
+        <v>2.9088017113656859E-2</v>
       </c>
       <c r="C222">
-        <v>0.17493486232385849</v>
+        <v>0.195425055387697</v>
       </c>
       <c r="D222">
-        <v>0.33148424184354569</v>
+        <v>0.27378253273238978</v>
       </c>
       <c r="E222">
-        <v>0.32318063318495149</v>
+        <v>0.31952479945524592</v>
       </c>
       <c r="F222">
-        <v>5.5399654220286233E-2</v>
+        <v>7.0994727865827861E-2</v>
       </c>
       <c r="G222">
-        <v>3.747169238074665E-2</v>
+        <v>4.0917820455385848E-2</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223">
-        <v>5.5419987515613042E-2</v>
+        <v>7.0536956940880885E-2</v>
       </c>
       <c r="B223">
-        <v>2.227021329774629E-2</v>
+        <v>2.911408560235575E-2</v>
       </c>
       <c r="C223">
-        <v>0.17500984393657351</v>
+        <v>0.1955770323421156</v>
       </c>
       <c r="D223">
-        <v>0.33098433375696068</v>
+        <v>0.27293396263645298</v>
       </c>
       <c r="E223">
-        <v>0.32339115037785271</v>
+        <v>0.31989992917247062</v>
       </c>
       <c r="F223">
-        <v>5.5444982936359882E-2</v>
+        <v>7.1010805479829575E-2</v>
       </c>
       <c r="G223">
-        <v>3.7479488178892822E-2</v>
+        <v>4.0927227825893198E-2</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224">
-        <v>5.5574343087952331E-2</v>
+        <v>7.0805332964590212E-2</v>
       </c>
       <c r="B224">
-        <v>2.2278483032907161E-2</v>
+        <v>2.9140831039924129E-2</v>
       </c>
       <c r="C224">
-        <v>0.17507773229508819</v>
+        <v>0.19572028480961959</v>
       </c>
       <c r="D224">
-        <v>0.33055969367180599</v>
+        <v>0.27219413563349443</v>
       </c>
       <c r="E224">
-        <v>0.32353006711948101</v>
+        <v>0.32017609844720379</v>
       </c>
       <c r="F224">
-        <v>5.5491604388854469E-2</v>
+        <v>7.1027465627312769E-2</v>
       </c>
       <c r="G224">
-        <v>3.7488076403903052E-2</v>
+        <v>4.0935851477862682E-2</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225">
-        <v>5.5731185355745359E-2</v>
+        <v>7.1072129525494354E-2</v>
       </c>
       <c r="B225">
-        <v>2.2285576547043721E-2</v>
+        <v>2.9168180389185939E-2</v>
       </c>
       <c r="C225">
-        <v>0.17513914056231469</v>
+        <v>0.19585545880481681</v>
       </c>
       <c r="D225">
-        <v>0.33022187623608329</v>
+        <v>0.27157418802995242</v>
       </c>
       <c r="E225">
-        <v>0.3235852278334197</v>
+        <v>0.32034174325245202</v>
       </c>
       <c r="F225">
-        <v>5.5539487386830358E-2</v>
+        <v>7.1044525172283254E-2</v>
       </c>
       <c r="G225">
-        <v>3.7497506078561262E-2</v>
+        <v>4.0943774825820338E-2</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226">
-        <v>5.589061195577822E-2</v>
+        <v>7.1337314828903237E-2</v>
       </c>
       <c r="B226">
-        <v>2.2291358797735999E-2</v>
+        <v>2.919606159208497E-2</v>
       </c>
       <c r="C226">
-        <v>0.17519480437209889</v>
+        <v>0.19598335656527879</v>
       </c>
       <c r="D226">
-        <v>0.32997901840385352</v>
+        <v>0.27108202658190078</v>
       </c>
       <c r="E226">
-        <v>0.32354783550722671</v>
+        <v>0.32038834747584</v>
       </c>
       <c r="F226">
-        <v>5.5588549033818047E-2</v>
+        <v>7.1061803410605182E-2</v>
       </c>
       <c r="G226">
-        <v>3.7507821929492313E-2</v>
+        <v>4.0951089545386253E-2</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227">
-        <v>5.6052679963482378E-2</v>
+        <v>7.1600869948285656E-2</v>
       </c>
       <c r="B227">
-        <v>2.2295731500543401E-2</v>
+        <v>2.9224409907966181E-2</v>
       </c>
       <c r="C227">
-        <v>0.17524554554350441</v>
+        <v>0.19610491341497879</v>
       </c>
       <c r="D227">
-        <v>0.32983574429546048</v>
+        <v>0.27072221483735259</v>
       </c>
       <c r="E227">
-        <v>0.32341258469934459</v>
+        <v>0.32031057199550161</v>
       </c>
       <c r="F227">
-        <v>5.5638654368805787E-2</v>
+        <v>7.1079126515225841E-2</v>
       </c>
       <c r="G227">
-        <v>3.751905962884737E-2</v>
+        <v>4.0957893380694832E-2</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228">
-        <v>5.6217403801902183E-2</v>
+        <v>7.1862788403561431E-2</v>
       </c>
       <c r="B228">
-        <v>2.2298639094373979E-2</v>
+        <v>2.9253173787392572E-2</v>
       </c>
       <c r="C228">
-        <v>0.1752922334065343</v>
+        <v>0.1962211690261397</v>
       </c>
       <c r="D228">
-        <v>0.3297931871402322</v>
+        <v>0.27049595471098831</v>
       </c>
       <c r="E228">
-        <v>0.32317767730489622</v>
+        <v>0.32010629599177759</v>
       </c>
       <c r="F228">
-        <v>5.5689617526489772E-2</v>
+        <v>7.1096330487172954E-2</v>
       </c>
       <c r="G228">
-        <v>3.7531241725565809E-2</v>
+        <v>4.0964287592981243E-2</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229">
-        <v>5.6384754756537141E-2</v>
+        <v>7.2123076117216883E-2</v>
       </c>
       <c r="B229">
-        <v>2.230007312077514E-2</v>
+        <v>2.928231990173517E-2</v>
       </c>
       <c r="C229">
-        <v>0.17533574610236219</v>
+        <v>0.19633323438483249</v>
       </c>
       <c r="D229">
-        <v>0.32984911808963352</v>
+        <v>0.27040116042660373</v>
       </c>
       <c r="E229">
-        <v>0.32284472893388988</v>
+        <v>0.31977657195597459</v>
       </c>
       <c r="F229">
-        <v>5.5741204453492052E-2</v>
+        <v>7.1113262663889287E-2</v>
       </c>
       <c r="G229">
-        <v>3.7544374543311727E-2</v>
+        <v>4.0970374549742387E-2</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230">
-        <v>5.6554662008293857E-2</v>
+        <v>7.2381751722962434E-2</v>
       </c>
       <c r="B230">
-        <v>2.2300074727034849E-2</v>
+        <v>2.931183697529606E-2</v>
       </c>
       <c r="C230">
-        <v>0.17537693410678859</v>
+        <v>0.19644225629299891</v>
       </c>
       <c r="D230">
-        <v>0.3299981705891803</v>
+        <v>0.27043262039711963</v>
       </c>
       <c r="E230">
-        <v>0.32241857503267002</v>
+        <v>0.31932549735618909</v>
       </c>
       <c r="F230">
-        <v>5.5793137287220032E-2</v>
+        <v>7.1129781972502651E-2</v>
       </c>
       <c r="G230">
-        <v>3.7558446248808462E-2</v>
+        <v>4.0976255282930321E-2</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231">
-        <v>5.6727014985859733E-2</v>
+        <v>7.2638847153156688E-2</v>
       </c>
       <c r="B231">
-        <v>2.2298735073884361E-2</v>
+        <v>2.934173812535807E-2</v>
       </c>
       <c r="C231">
-        <v>0.17541658798341939</v>
+        <v>0.19654938129329369</v>
       </c>
       <c r="D231">
-        <v>0.33023214836494658</v>
+        <v>0.27058224074962289</v>
       </c>
       <c r="E231">
-        <v>0.32190698688824593</v>
+        <v>0.31876000700246132</v>
       </c>
       <c r="F231">
-        <v>5.5845100513456397E-2</v>
+        <v>7.1145758217976668E-2</v>
       </c>
       <c r="G231">
-        <v>3.7573426190186388E-2</v>
+        <v>4.0982027458121927E-2</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232">
-        <v>5.6901666775214368E-2</v>
+        <v>7.2894408402949057E-2</v>
       </c>
       <c r="B232">
-        <v>2.229619352030723E-2</v>
+        <v>2.9372061435510421E-2</v>
       </c>
       <c r="C232">
-        <v>0.17545541202894699</v>
+        <v>0.19665572081468941</v>
       </c>
       <c r="D232">
-        <v>0.33054040451703459</v>
+        <v>0.2708393630018483</v>
       </c>
       <c r="E232">
-        <v>0.32132030867376182</v>
+        <v>0.31808959181433089</v>
       </c>
       <c r="F232">
-        <v>5.5896748978711927E-2</v>
+        <v>7.1161070921617789E-2</v>
       </c>
       <c r="G232">
-        <v>3.7589265506020271E-2</v>
+        <v>4.0987783609053668E-2</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233">
-        <v>5.7078438265336977E-2</v>
+        <v>7.3148496391346171E-2</v>
       </c>
       <c r="B233">
-        <v>2.2292633557858672E-2</v>
+        <v>2.9402868694799071E-2</v>
       </c>
       <c r="C233">
-        <v>0.17549400502436999</v>
+        <v>0.19676231921804849</v>
       </c>
       <c r="D233">
-        <v>0.33091027826121588</v>
+        <v>0.27119114664179778</v>
       </c>
       <c r="E233">
-        <v>0.32067102821668148</v>
+        <v>0.31732595109840872</v>
       </c>
       <c r="F233">
-        <v>5.5947717747414791E-2</v>
+        <v>7.1175608120584599E-2</v>
       </c>
       <c r="G233">
-        <v>3.7605898927133972E-2</v>
+        <v>4.099360983500977E-2</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234">
-        <v>5.7257122712342789E-2</v>
+        <v>7.3401187803229767E-2</v>
       </c>
       <c r="B234">
-        <v>2.2288276590093178E-2</v>
+        <v>2.94342423444077E-2</v>
       </c>
       <c r="C234">
-        <v>0.1755328487872011</v>
+        <v>0.19687012614740909</v>
       </c>
       <c r="D234">
-        <v>0.33132757472899421</v>
+        <v>0.27162300581770271</v>
       </c>
       <c r="E234">
-        <v>0.3199732960357427</v>
+        <v>0.31648258765707687</v>
       </c>
       <c r="F234">
-        <v>5.5997633624917588E-2</v>
+        <v>7.1189265528578904E-2</v>
       </c>
       <c r="G234">
-        <v>3.7623247520707281E-2</v>
+        <v>4.0999584701591478E-2</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235">
-        <v>5.7437490413992397E-2</v>
+        <v>7.3652575812362175E-2</v>
       </c>
       <c r="B235">
-        <v>2.2283373776998301E-2</v>
+        <v>2.9466280829019309E-2</v>
       </c>
       <c r="C235">
-        <v>0.17557230453481279</v>
+        <v>0.19697997413157589</v>
       </c>
       <c r="D235">
-        <v>0.33177707154840641</v>
+        <v>0.27211908735046658</v>
       </c>
       <c r="E235">
-        <v>0.31924240944956689</v>
+        <v>0.31557435708464382</v>
       </c>
       <c r="F235">
-        <v>5.6046128027361822E-2</v>
+        <v>7.120194636384064E-2</v>
       </c>
       <c r="G235">
-        <v>3.7641222248853447E-2</v>
+        <v>4.100577842809331E-2</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236">
-        <v>5.7619293301324093E-2</v>
+        <v>7.3902770541845658E-2</v>
       </c>
       <c r="B236">
-        <v>2.2278196329650179E-2</v>
+        <v>2.949909266232385E-2</v>
       </c>
       <c r="C236">
-        <v>0.175612616586868</v>
+        <v>0.19709256194826091</v>
       </c>
       <c r="D236">
-        <v>0.33224303488997081</v>
+        <v>0.27266277525650989</v>
       </c>
       <c r="E236">
-        <v>0.31849428024789678</v>
+        <v>0.31461698534050581</v>
       </c>
       <c r="F236">
-        <v>5.6092850679796788E-2</v>
+        <v>7.1213562082928838E-2</v>
       </c>
       <c r="G236">
-        <v>3.765972796449088E-2</v>
+        <v>4.1012252167630742E-2</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237">
-        <v>5.780226926304248E-2</v>
+        <v>7.415189914474582E-2</v>
       </c>
       <c r="B237">
-        <v>2.2273024745832089E-2</v>
+        <v>2.953278962020978E-2</v>
       </c>
       <c r="C237">
-        <v>0.17565392223834009</v>
+        <v>0.197208443877918</v>
       </c>
       <c r="D237">
-        <v>0.33270972693549999</v>
+        <v>0.27323720505616711</v>
       </c>
       <c r="E237">
-        <v>0.31774490568601171</v>
+        <v>0.31362657099906599</v>
       </c>
       <c r="F237">
-        <v>5.6137483468021741E-2</v>
+        <v>7.1224034018550889E-2</v>
       </c>
       <c r="G237">
-        <v>3.7678667663240503E-2</v>
+        <v>4.1019057283343693E-2</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238">
-        <v>5.7986146139626493E-2</v>
+        <v>7.4400105359207533E-2</v>
       </c>
       <c r="B238">
-        <v>2.2268137598531759E-2</v>
+        <v>2.9567479521917201E-2</v>
       </c>
       <c r="C238">
-        <v>0.17569626634493621</v>
+        <v>0.19732802458133741</v>
       </c>
       <c r="D238">
-        <v>0.33316188711873013</v>
+        <v>0.27382576945014131</v>
       </c>
       <c r="E238">
-        <v>0.31700986238632578</v>
+        <v>0.31261909048083969</v>
       </c>
       <c r="F238">
-        <v>5.617975370459883E-2</v>
+        <v>7.1233295925717213E-2</v>
       </c>
       <c r="G238">
-        <v>3.7697946707258977E-2</v>
+        <v>4.102623468082596E-2</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A239">
-        <v>5.8170645382546918E-2</v>
+        <v>7.4647548373673336E-2</v>
       </c>
       <c r="B239">
-        <v>2.2263800534331291E-2</v>
+        <v>2.9603259000870338E-2</v>
       </c>
       <c r="C239">
-        <v>0.1757396189585177</v>
+        <v>0.19745155902866721</v>
       </c>
       <c r="D239">
-        <v>0.33358517123985693</v>
+        <v>0.27441259655954431</v>
       </c>
       <c r="E239">
-        <v>0.31630384110063781</v>
+        <v>0.3116099258215656</v>
       </c>
       <c r="F239">
-        <v>5.6219445991503643E-2</v>
+        <v>7.1241297179042262E-2</v>
       </c>
       <c r="G239">
-        <v>3.7717476792612732E-2</v>
+        <v>4.1033814036631942E-2</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A240">
-        <v>5.8355485409444227E-2</v>
+        <v>7.4894400889003149E-2</v>
       </c>
       <c r="B240">
-        <v>2.226025613391357E-2</v>
+        <v>2.9640206724919259E-2</v>
       </c>
       <c r="C240">
-        <v>0.17578389435260661</v>
+        <v>0.19757915670683271</v>
       </c>
       <c r="D240">
-        <v>0.33396653525328712</v>
+        <v>0.27498298203892629</v>
       </c>
       <c r="E240">
-        <v>0.31564023741579789</v>
+        <v>0.31061343420562132</v>
       </c>
       <c r="F240">
-        <v>5.6256411960723049E-2</v>
+        <v>7.1248006364098407E-2</v>
       </c>
       <c r="G240">
-        <v>3.7737179474206892E-2</v>
+        <v>4.1041813070602437E-2</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A241">
-        <v>5.8540384719939179E-2</v>
+        <v>7.5140846302578529E-2</v>
       </c>
       <c r="B241">
-        <v>2.2257715216175759E-2</v>
+        <v>2.967837738271252E-2</v>
       </c>
       <c r="C241">
-        <v>0.17582897000156811</v>
+        <v>0.19771078917693841</v>
       </c>
       <c r="D241">
-        <v>0.33429455420775561</v>
+        <v>0.27552375831694598</v>
       </c>
       <c r="E241">
-        <v>0.3150308095989921</v>
+        <v>0.30964257699151748</v>
       </c>
       <c r="F241">
-        <v>5.6290577201091027E-2</v>
+        <v>7.1253414843094012E-2</v>
       </c>
       <c r="G241">
-        <v>3.7756989054466263E-2</v>
+        <v>4.1050236986200847E-2</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A242">
-        <v>5.8725064836180597E-2</v>
+        <v>7.5387075081540689E-2</v>
       </c>
       <c r="B242">
-        <v>2.225635004232953E-2</v>
+        <v>2.9717796785816049E-2</v>
       </c>
       <c r="C242">
-        <v>0.1758747043071669</v>
+        <v>0.19784630004595799</v>
       </c>
       <c r="D242">
-        <v>0.33455967075308229</v>
+        <v>0.27602358716642628</v>
       </c>
       <c r="E242">
-        <v>0.31448541026701021</v>
+        <v>0.30870862289151879</v>
       </c>
       <c r="F242">
-        <v>5.6321945016005369E-2</v>
+        <v>7.125753990503006E-2</v>
       </c>
       <c r="G242">
-        <v>3.7776854778226267E-2</v>
+        <v>4.1059078123705461E-2</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A243">
-        <v>5.8909253146153653E-2</v>
+        <v>7.5633280458080376E-2</v>
       </c>
       <c r="B243">
-        <v>2.2256289732368938E-2</v>
+        <v>2.9758458356173679E-2</v>
       </c>
       <c r="C243">
-        <v>0.17592095224451121</v>
+        <v>0.19798541630680799</v>
       </c>
       <c r="D243">
-        <v>0.33475437156854371</v>
+        <v>0.27647316587632148</v>
       </c>
       <c r="E243">
-        <v>0.31401179446624911</v>
+        <v>0.30782093569862568</v>
       </c>
       <c r="F243">
-        <v>5.6350596720169593E-2</v>
+        <v>7.1260427220080622E-2</v>
       </c>
       <c r="G243">
-        <v>3.7796742122002139E-2</v>
+        <v>4.1068316083915438E-2</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A244">
-        <v>5.9092685683596352E-2</v>
+        <v>7.5879653740903011E-2</v>
       </c>
       <c r="B244">
-        <v>2.225761803026044E-2</v>
+        <v>2.980032125170785E-2</v>
       </c>
       <c r="C244">
-        <v>0.17596757833384161</v>
+        <v>0.1981277603045403</v>
       </c>
       <c r="D244">
-        <v>0.33487329320414988</v>
+        <v>0.27686534247726668</v>
       </c>
       <c r="E244">
-        <v>0.31361550301377911</v>
+        <v>0.30698685212339999</v>
       </c>
       <c r="F244">
-        <v>5.6376688538110953E-2</v>
+        <v>7.126215182683697E-2</v>
       </c>
       <c r="G244">
-        <v>3.7816633196245363E-2</v>
+        <v>4.1077918275350803E-2</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A245">
-        <v>5.9275109853173052E-2</v>
+        <v>7.6126379576353181E-2</v>
       </c>
       <c r="B245">
-        <v>2.2260373389818539E-2</v>
+        <v>2.984331024333655E-2</v>
       </c>
       <c r="C245">
-        <v>0.17601446660712169</v>
+        <v>0.19827286184007969</v>
       </c>
       <c r="D245">
-        <v>0.33491326122042331</v>
+        <v>0.27719514022015518</v>
       </c>
       <c r="E245">
-        <v>0.3132998173849908</v>
+        <v>0.30621164931713502</v>
       </c>
       <c r="F245">
-        <v>5.6400445295095587E-2</v>
+        <v>7.1262817612116253E-2</v>
       </c>
       <c r="G245">
-        <v>3.7836526249388179E-2</v>
+        <v>4.1087841190835007E-2</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A246">
-        <v>5.9456287067864447E-2</v>
+        <v>7.6373631460086633E-2</v>
       </c>
       <c r="B246">
-        <v>2.2264551202246931E-2</v>
+        <v>2.988731739256088E-2</v>
       </c>
       <c r="C246">
-        <v>0.17606152745513859</v>
+        <v>0.19842017029055539</v>
       </c>
       <c r="D246">
-        <v>0.33487326800285572</v>
+        <v>0.27745969665586728</v>
       </c>
       <c r="E246">
-        <v>0.31306578070931568</v>
+        <v>0.30549859662642193</v>
       </c>
       <c r="F246">
-        <v>5.6422151307123587E-2</v>
+        <v>7.1262555221104057E-2</v>
       </c>
       <c r="G246">
-        <v>3.7856434255452827E-2</v>
+        <v>4.1098032353406123E-2</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A247">
-        <v>5.9635995241707061E-2</v>
+        <v>7.6621567746189168E-2</v>
       </c>
       <c r="B247">
-        <v>2.2270107846444991E-2</v>
+        <v>2.9932205365442052E-2</v>
       </c>
       <c r="C247">
-        <v>0.176108701342514</v>
+        <v>0.1985690666490976</v>
       </c>
       <c r="D247">
-        <v>0.33475439518954392</v>
+        <v>0.27765812710187349</v>
       </c>
       <c r="E247">
-        <v>0.31291227857744419</v>
+        <v>0.30484908171438019</v>
       </c>
       <c r="F247">
-        <v>5.6442139041120581E-2</v>
+        <v>7.1261518789307851E-2</v>
       </c>
       <c r="G247">
-        <v>3.7876382761229302E-2</v>
+        <v>4.1108432633715039E-2</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A248">
-        <v>5.9814031043275442E-2</v>
+        <v>7.6870328293945883E-2</v>
       </c>
       <c r="B248">
-        <v>2.22769661310908E-2</v>
+        <v>2.9977812169318881E-2</v>
       </c>
       <c r="C248">
-        <v>0.17615595947970669</v>
+        <v>0.19871887558187681</v>
       </c>
       <c r="D248">
-        <v>0.3345596868596874</v>
+        <v>0.27779132500358927</v>
       </c>
       <c r="E248">
-        <v>0.31283617320700441</v>
+        <v>0.3042627978137073</v>
       </c>
       <c r="F248">
-        <v>5.6460776213536512E-2</v>
+        <v>7.1259881772037653E-2</v>
       </c>
       <c r="G248">
-        <v>3.7896407065696351E-2</v>
+        <v>4.1118979365527629E-2</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A249">
-        <v>5.9990211828523557E-2</v>
+        <v>7.7120031988732476E-2</v>
       </c>
       <c r="B249">
-        <v>2.2285021637758869E-2</v>
+        <v>3.0023956958363681E-2</v>
       </c>
       <c r="C249">
-        <v>0.17620330161541789</v>
+        <v>0.19886887792971181</v>
       </c>
       <c r="D249">
-        <v>0.33429397947988831</v>
+        <v>0.2778617146294392</v>
       </c>
       <c r="E249">
-        <v>0.31283248437767192</v>
+        <v>0.30373797714330458</v>
       </c>
       <c r="F249">
-        <v>5.6478452148309433E-2</v>
+        <v>7.1257831883254033E-2</v>
       </c>
       <c r="G249">
-        <v>3.791654891243066E-2</v>
+        <v>4.1129609467203031E-2</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A250">
-        <v>6.0164377157700587E-2</v>
+        <v>7.7370775217941112E-2</v>
       </c>
       <c r="B250">
-        <v>2.2294149444043371E-2</v>
+        <v>3.007044648723407E-2</v>
       </c>
       <c r="C250">
-        <v>0.1762507512056512</v>
+        <v>0.19901832394562799</v>
       </c>
       <c r="D250">
-        <v>0.33396369448929247</v>
+        <v>0.27787297158558127</v>
       </c>
       <c r="E250">
-        <v>0.31289461065222762</v>
+        <v>0.30327165425006097</v>
       </c>
       <c r="F250">
-        <v>5.6495564129310602E-2</v>
+        <v>7.1255565743939181E-2</v>
       </c>
       <c r="G250">
-        <v>3.7936852921772297E-2</v>
+        <v>4.1140262769625242E-2</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A251">
-        <v>6.0336389835087413E-2</v>
+        <v>7.7622631375098936E-2</v>
       </c>
       <c r="B251">
-        <v>2.2304210737338789E-2</v>
+        <v>3.0117081812644431E-2</v>
       </c>
       <c r="C251">
-        <v>0.17629834838198319</v>
+        <v>0.19916644756482799</v>
       </c>
       <c r="D251">
-        <v>0.33357659965271569</v>
+        <v>0.27782972688424279</v>
       </c>
       <c r="E251">
-        <v>0.31301458396338538</v>
+        <v>0.30285994371155678</v>
       </c>
       <c r="F251">
-        <v>5.6512504478618053E-2</v>
+        <v>7.1253283530006123E-2</v>
       </c>
       <c r="G251">
-        <v>3.7957362950875033E-2</v>
+        <v>4.1150885121620628E-2</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A252">
-        <v>6.0506136419419633E-2</v>
+        <v>7.7875651342432906E-2</v>
       </c>
       <c r="B252">
-        <v>2.231505889264877E-2</v>
+        <v>3.0163664815910689E-2</v>
       </c>
       <c r="C252">
-        <v>0.17634614127282361</v>
+        <v>0.1993124817878216</v>
       </c>
       <c r="D252">
-        <v>0.33314154573120441</v>
+        <v>0.27773726906075752</v>
       </c>
       <c r="E252">
-        <v>0.31318335015498039</v>
+        <v>0.30249831789077358</v>
       </c>
       <c r="F252">
-        <v>5.6529648932890919E-2</v>
+        <v>7.1251183930652606E-2</v>
       </c>
       <c r="G252">
-        <v>3.7978118596031153E-2</v>
+        <v>4.1161431171649381E-2</v>
       </c>
     </row>
   </sheetData>
